--- a/docs/OpenBudget.xlsx
+++ b/docs/OpenBudget.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nodir\open-budget-checker\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C543C8-2F1D-40DD-9DA0-4240BEC03FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF0D9DC-8D36-43A3-B9E1-222EAAE62E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{83070EB0-F3E9-4F09-9EA5-B85425558D79}"/>
   </bookViews>
@@ -7950,13 +7950,13 @@
       <c r="A502" s="4">
         <v>501</v>
       </c>
-      <c r="B502" s="7">
+      <c r="B502" s="2">
         <v>912230676</v>
       </c>
-      <c r="C502" s="8">
+      <c r="C502" s="4">
         <v>1626</v>
       </c>
-      <c r="D502" s="6" t="str">
+      <c r="D502" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "912230676", "voteDate": "2026-03-20 16:26"},</v>
       </c>
@@ -7965,13 +7965,13 @@
       <c r="A503" s="4">
         <v>502</v>
       </c>
-      <c r="B503" s="7">
+      <c r="B503" s="2">
         <v>955540730</v>
       </c>
-      <c r="C503" s="8">
+      <c r="C503" s="4">
         <v>1634</v>
       </c>
-      <c r="D503" s="6" t="str">
+      <c r="D503" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "955540730", "voteDate": "2026-03-20 16:34"},</v>
       </c>
@@ -7980,13 +7980,13 @@
       <c r="A504" s="4">
         <v>503</v>
       </c>
-      <c r="B504" s="7">
+      <c r="B504" s="2">
         <v>930750741</v>
       </c>
-      <c r="C504" s="8">
+      <c r="C504" s="4">
         <v>1631</v>
       </c>
-      <c r="D504" s="6" t="str">
+      <c r="D504" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "930750741", "voteDate": "2026-03-20 16:31"},</v>
       </c>
@@ -7995,13 +7995,13 @@
       <c r="A505" s="4">
         <v>504</v>
       </c>
-      <c r="B505" s="7">
+      <c r="B505" s="2">
         <v>500153230</v>
       </c>
-      <c r="C505" s="8">
+      <c r="C505" s="4">
         <v>1632</v>
       </c>
-      <c r="D505" s="6" t="str">
+      <c r="D505" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "500153230", "voteDate": "2026-03-20 16:32"},</v>
       </c>
@@ -8010,13 +8010,13 @@
       <c r="A506" s="4">
         <v>505</v>
       </c>
-      <c r="B506" s="7">
+      <c r="B506" s="2">
         <v>952306098</v>
       </c>
-      <c r="C506" s="8">
+      <c r="C506" s="4">
         <v>1634</v>
       </c>
-      <c r="D506" s="6" t="str">
+      <c r="D506" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "952306098", "voteDate": "2026-03-20 16:34"},</v>
       </c>
@@ -8025,13 +8025,13 @@
       <c r="A507" s="4">
         <v>506</v>
       </c>
-      <c r="B507" s="7">
+      <c r="B507" s="2">
         <v>944193666</v>
       </c>
-      <c r="C507" s="8">
+      <c r="C507" s="4">
         <v>1634</v>
       </c>
-      <c r="D507" s="6" t="str">
+      <c r="D507" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "944193666", "voteDate": "2026-03-20 16:34"},</v>
       </c>
@@ -8040,13 +8040,13 @@
       <c r="A508" s="4">
         <v>507</v>
       </c>
-      <c r="B508" s="7">
+      <c r="B508" s="2">
         <v>942002186</v>
       </c>
-      <c r="C508" s="8">
+      <c r="C508" s="4">
         <v>1616</v>
       </c>
-      <c r="D508" s="6" t="str">
+      <c r="D508" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "942002186", "voteDate": "2026-03-20 16:16"},</v>
       </c>
@@ -8055,13 +8055,13 @@
       <c r="A509" s="4">
         <v>508</v>
       </c>
-      <c r="B509" s="7">
+      <c r="B509" s="2">
         <v>955698383</v>
       </c>
-      <c r="C509" s="8">
+      <c r="C509" s="4">
         <v>1617</v>
       </c>
-      <c r="D509" s="6" t="str">
+      <c r="D509" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "955698383", "voteDate": "2026-03-20 16:17"},</v>
       </c>
@@ -8070,13 +8070,13 @@
       <c r="A510" s="4">
         <v>509</v>
       </c>
-      <c r="B510" s="7">
+      <c r="B510" s="2">
         <v>880767737</v>
       </c>
-      <c r="C510" s="8">
+      <c r="C510" s="4">
         <v>1635</v>
       </c>
-      <c r="D510" s="6" t="str">
+      <c r="D510" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "880767737", "voteDate": "2026-03-20 16:35"},</v>
       </c>
@@ -8085,13 +8085,13 @@
       <c r="A511" s="4">
         <v>510</v>
       </c>
-      <c r="B511" s="7">
+      <c r="B511" s="2">
         <v>902722900</v>
       </c>
-      <c r="C511" s="8">
+      <c r="C511" s="4">
         <v>1541</v>
       </c>
-      <c r="D511" s="6" t="str">
+      <c r="D511" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "902722900", "voteDate": "2026-03-20 15:41"},</v>
       </c>
@@ -8100,13 +8100,13 @@
       <c r="A512" s="4">
         <v>511</v>
       </c>
-      <c r="B512" s="7">
+      <c r="B512" s="2">
         <v>932911028</v>
       </c>
-      <c r="C512" s="8">
+      <c r="C512" s="4">
         <v>1545</v>
       </c>
-      <c r="D512" s="6" t="str">
+      <c r="D512" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "932911028", "voteDate": "2026-03-20 15:45"},</v>
       </c>
@@ -8115,13 +8115,13 @@
       <c r="A513" s="4">
         <v>512</v>
       </c>
-      <c r="B513" s="7">
+      <c r="B513" s="2">
         <v>906340104</v>
       </c>
-      <c r="C513" s="8">
+      <c r="C513" s="4">
         <v>1617</v>
       </c>
-      <c r="D513" s="6" t="str">
+      <c r="D513" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "906340104", "voteDate": "2026-03-20 16:17"},</v>
       </c>
@@ -8130,13 +8130,13 @@
       <c r="A514" s="4">
         <v>513</v>
       </c>
-      <c r="B514" s="7">
+      <c r="B514" s="2">
         <v>916564532</v>
       </c>
-      <c r="C514" s="8">
+      <c r="C514" s="4">
         <v>1620</v>
       </c>
-      <c r="D514" s="6" t="str">
+      <c r="D514" t="str">
         <f t="shared" si="7"/>
         <v>{"phoneNumber": "916564532", "voteDate": "2026-03-20 16:20"},</v>
       </c>
@@ -8145,13 +8145,13 @@
       <c r="A515" s="4">
         <v>514</v>
       </c>
-      <c r="B515" s="7">
+      <c r="B515" s="2">
         <v>910492729</v>
       </c>
-      <c r="C515" s="8">
+      <c r="C515" s="4">
         <v>1625</v>
       </c>
-      <c r="D515" s="6" t="str">
+      <c r="D515" t="str">
         <f t="shared" ref="D515:D578" si="8">"{""phoneNumber"": """&amp;B515&amp;""", ""voteDate"": """&amp;TEXT(DATE(2026,3,20),"yyyy-mm-dd")&amp;" "&amp;TEXT(C515,"00\:00")&amp;"""},"</f>
         <v>{"phoneNumber": "910492729", "voteDate": "2026-03-20 16:25"},</v>
       </c>
@@ -8160,13 +8160,13 @@
       <c r="A516" s="4">
         <v>515</v>
       </c>
-      <c r="B516" s="7">
+      <c r="B516" s="2">
         <v>972801784</v>
       </c>
-      <c r="C516" s="8">
+      <c r="C516" s="4">
         <v>1543</v>
       </c>
-      <c r="D516" s="6" t="str">
+      <c r="D516" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "972801784", "voteDate": "2026-03-20 15:43"},</v>
       </c>
@@ -8175,13 +8175,13 @@
       <c r="A517" s="4">
         <v>516</v>
       </c>
-      <c r="B517" s="7">
+      <c r="B517" s="2">
         <v>915116498</v>
       </c>
-      <c r="C517" s="8">
+      <c r="C517" s="4">
         <v>1624</v>
       </c>
-      <c r="D517" s="6" t="str">
+      <c r="D517" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "915116498", "voteDate": "2026-03-20 16:24"},</v>
       </c>
@@ -8190,13 +8190,13 @@
       <c r="A518" s="4">
         <v>517</v>
       </c>
-      <c r="B518" s="7">
+      <c r="B518" s="2">
         <v>953657292</v>
       </c>
-      <c r="C518" s="8">
+      <c r="C518" s="4">
         <v>1632</v>
       </c>
-      <c r="D518" s="6" t="str">
+      <c r="D518" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "953657292", "voteDate": "2026-03-20 16:32"},</v>
       </c>
@@ -8205,13 +8205,13 @@
       <c r="A519" s="4">
         <v>518</v>
       </c>
-      <c r="B519" s="7">
+      <c r="B519" s="2">
         <v>905712002</v>
       </c>
-      <c r="C519" s="8">
+      <c r="C519" s="4">
         <v>1616</v>
       </c>
-      <c r="D519" s="6" t="str">
+      <c r="D519" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "905712002", "voteDate": "2026-03-20 16:16"},</v>
       </c>
@@ -8220,13 +8220,13 @@
       <c r="A520" s="4">
         <v>519</v>
       </c>
-      <c r="B520" s="7">
+      <c r="B520" s="2">
         <v>990769504</v>
       </c>
-      <c r="C520" s="8">
+      <c r="C520" s="4">
         <v>1620</v>
       </c>
-      <c r="D520" s="6" t="str">
+      <c r="D520" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "990769504", "voteDate": "2026-03-20 16:20"},</v>
       </c>
@@ -8235,13 +8235,13 @@
       <c r="A521" s="4">
         <v>520</v>
       </c>
-      <c r="B521" s="7">
+      <c r="B521" s="2">
         <v>993520640</v>
       </c>
-      <c r="C521" s="8">
+      <c r="C521" s="4">
         <v>1624</v>
       </c>
-      <c r="D521" s="6" t="str">
+      <c r="D521" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "993520640", "voteDate": "2026-03-20 16:24"},</v>
       </c>
@@ -8250,13 +8250,13 @@
       <c r="A522" s="4">
         <v>521</v>
       </c>
-      <c r="B522" s="7">
+      <c r="B522" s="2">
         <v>907811173</v>
       </c>
-      <c r="C522" s="8">
+      <c r="C522" s="4">
         <v>1633</v>
       </c>
-      <c r="D522" s="6" t="str">
+      <c r="D522" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "907811173", "voteDate": "2026-03-20 16:33"},</v>
       </c>
@@ -8265,13 +8265,13 @@
       <c r="A523" s="4">
         <v>522</v>
       </c>
-      <c r="B523" s="7">
+      <c r="B523" s="2">
         <v>770561411</v>
       </c>
-      <c r="C523" s="8">
+      <c r="C523" s="4">
         <v>1531</v>
       </c>
-      <c r="D523" s="6" t="str">
+      <c r="D523" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "770561411", "voteDate": "2026-03-20 15:31"},</v>
       </c>
@@ -8280,13 +8280,13 @@
       <c r="A524" s="4">
         <v>523</v>
       </c>
-      <c r="B524" s="7">
+      <c r="B524" s="2">
         <v>912405065</v>
       </c>
-      <c r="C524" s="8">
+      <c r="C524" s="4">
         <v>1535</v>
       </c>
-      <c r="D524" s="6" t="str">
+      <c r="D524" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "912405065", "voteDate": "2026-03-20 15:35"},</v>
       </c>
@@ -8295,13 +8295,13 @@
       <c r="A525" s="4">
         <v>524</v>
       </c>
-      <c r="B525" s="7">
+      <c r="B525" s="2">
         <v>902333302</v>
       </c>
-      <c r="C525" s="8">
+      <c r="C525" s="4">
         <v>1547</v>
       </c>
-      <c r="D525" s="6" t="str">
+      <c r="D525" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "902333302", "voteDate": "2026-03-20 15:47"},</v>
       </c>
@@ -8310,13 +8310,13 @@
       <c r="A526" s="4">
         <v>525</v>
       </c>
-      <c r="B526" s="7">
+      <c r="B526" s="2">
         <v>971887100</v>
       </c>
-      <c r="C526" s="8">
+      <c r="C526" s="4">
         <v>1550</v>
       </c>
-      <c r="D526" s="6" t="str">
+      <c r="D526" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "971887100", "voteDate": "2026-03-20 15:50"},</v>
       </c>
@@ -8325,13 +8325,13 @@
       <c r="A527" s="4">
         <v>526</v>
       </c>
-      <c r="B527" s="7">
+      <c r="B527" s="2">
         <v>905002390</v>
       </c>
-      <c r="C527" s="8">
+      <c r="C527" s="4">
         <v>1551</v>
       </c>
-      <c r="D527" s="6" t="str">
+      <c r="D527" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "905002390", "voteDate": "2026-03-20 15:51"},</v>
       </c>
@@ -8340,13 +8340,13 @@
       <c r="A528" s="4">
         <v>527</v>
       </c>
-      <c r="B528" s="7">
+      <c r="B528" s="2">
         <v>907323302</v>
       </c>
-      <c r="C528" s="8">
+      <c r="C528" s="4">
         <v>1553</v>
       </c>
-      <c r="D528" s="6" t="str">
+      <c r="D528" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "907323302", "voteDate": "2026-03-20 15:53"},</v>
       </c>
@@ -8355,13 +8355,13 @@
       <c r="A529" s="4">
         <v>528</v>
       </c>
-      <c r="B529" s="7">
+      <c r="B529" s="2">
         <v>945549931</v>
       </c>
-      <c r="C529" s="8">
+      <c r="C529" s="4">
         <v>1555</v>
       </c>
-      <c r="D529" s="6" t="str">
+      <c r="D529" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "945549931", "voteDate": "2026-03-20 15:55"},</v>
       </c>
@@ -8370,13 +8370,13 @@
       <c r="A530" s="4">
         <v>529</v>
       </c>
-      <c r="B530" s="7">
+      <c r="B530" s="2">
         <v>906301520</v>
       </c>
-      <c r="C530" s="8">
+      <c r="C530" s="4">
         <v>1558</v>
       </c>
-      <c r="D530" s="6" t="str">
+      <c r="D530" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "906301520", "voteDate": "2026-03-20 15:58"},</v>
       </c>
@@ -8385,13 +8385,13 @@
       <c r="A531" s="4">
         <v>530</v>
       </c>
-      <c r="B531" s="7">
+      <c r="B531" s="2">
         <v>773392928</v>
       </c>
-      <c r="C531" s="8">
+      <c r="C531" s="4">
         <v>1609</v>
       </c>
-      <c r="D531" s="6" t="str">
+      <c r="D531" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "773392928", "voteDate": "2026-03-20 16:09"},</v>
       </c>
@@ -8400,13 +8400,13 @@
       <c r="A532" s="4">
         <v>531</v>
       </c>
-      <c r="B532" s="7">
+      <c r="B532" s="2">
         <v>934340995</v>
       </c>
-      <c r="C532" s="8">
+      <c r="C532" s="4">
         <v>1616</v>
       </c>
-      <c r="D532" s="6" t="str">
+      <c r="D532" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "934340995", "voteDate": "2026-03-20 16:16"},</v>
       </c>
@@ -8415,13 +8415,13 @@
       <c r="A533" s="4">
         <v>532</v>
       </c>
-      <c r="B533" s="7">
+      <c r="B533" s="2">
         <v>918322230</v>
       </c>
-      <c r="C533" s="8">
+      <c r="C533" s="4">
         <v>1625</v>
       </c>
-      <c r="D533" s="6" t="str">
+      <c r="D533" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "918322230", "voteDate": "2026-03-20 16:25"},</v>
       </c>
@@ -8430,13 +8430,13 @@
       <c r="A534" s="4">
         <v>533</v>
       </c>
-      <c r="B534" s="7">
+      <c r="B534" s="2">
         <v>914141464</v>
       </c>
-      <c r="C534" s="8">
+      <c r="C534" s="4">
         <v>1626</v>
       </c>
-      <c r="D534" s="6" t="str">
+      <c r="D534" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "914141464", "voteDate": "2026-03-20 16:26"},</v>
       </c>
@@ -8445,13 +8445,13 @@
       <c r="A535" s="4">
         <v>534</v>
       </c>
-      <c r="B535" s="7">
+      <c r="B535" s="2">
         <v>913389582</v>
       </c>
-      <c r="C535" s="8">
+      <c r="C535" s="4">
         <v>1628</v>
       </c>
-      <c r="D535" s="6" t="str">
+      <c r="D535" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "913389582", "voteDate": "2026-03-20 16:28"},</v>
       </c>
@@ -8460,13 +8460,13 @@
       <c r="A536" s="4">
         <v>535</v>
       </c>
-      <c r="B536" s="7">
+      <c r="B536" s="2">
         <v>938207076</v>
       </c>
-      <c r="C536" s="8">
+      <c r="C536" s="4">
         <v>1629</v>
       </c>
-      <c r="D536" s="6" t="str">
+      <c r="D536" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "938207076", "voteDate": "2026-03-20 16:29"},</v>
       </c>
@@ -8475,13 +8475,13 @@
       <c r="A537" s="4">
         <v>536</v>
       </c>
-      <c r="B537" s="7">
+      <c r="B537" s="2">
         <v>916499737</v>
       </c>
-      <c r="C537" s="8">
+      <c r="C537" s="4">
         <v>1634</v>
       </c>
-      <c r="D537" s="6" t="str">
+      <c r="D537" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "916499737", "voteDate": "2026-03-20 16:34"},</v>
       </c>
@@ -8490,13 +8490,13 @@
       <c r="A538" s="4">
         <v>537</v>
       </c>
-      <c r="B538" s="7">
+      <c r="B538" s="2">
         <v>933336767</v>
       </c>
-      <c r="C538" s="8">
+      <c r="C538" s="4">
         <v>1634</v>
       </c>
-      <c r="D538" s="6" t="str">
+      <c r="D538" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "933336767", "voteDate": "2026-03-20 16:34"},</v>
       </c>
@@ -8505,13 +8505,13 @@
       <c r="A539" s="4">
         <v>538</v>
       </c>
-      <c r="B539" s="7">
+      <c r="B539" s="2">
         <v>701079422</v>
       </c>
-      <c r="C539" s="8">
+      <c r="C539" s="4">
         <v>1637</v>
       </c>
-      <c r="D539" s="6" t="str">
+      <c r="D539" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "701079422", "voteDate": "2026-03-20 16:37"},</v>
       </c>
@@ -8520,13 +8520,13 @@
       <c r="A540" s="4">
         <v>539</v>
       </c>
-      <c r="B540" s="7">
+      <c r="B540" s="2">
         <v>993771244</v>
       </c>
-      <c r="C540" s="8">
+      <c r="C540" s="4">
         <v>1639</v>
       </c>
-      <c r="D540" s="6" t="str">
+      <c r="D540" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "993771244", "voteDate": "2026-03-20 16:39"},</v>
       </c>
@@ -8535,13 +8535,13 @@
       <c r="A541" s="4">
         <v>540</v>
       </c>
-      <c r="B541" s="7">
+      <c r="B541" s="2">
         <v>979409295</v>
       </c>
-      <c r="C541" s="8">
+      <c r="C541" s="4">
         <v>1636</v>
       </c>
-      <c r="D541" s="6" t="str">
+      <c r="D541" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "979409295", "voteDate": "2026-03-20 16:36"},</v>
       </c>
@@ -8550,13 +8550,13 @@
       <c r="A542" s="4">
         <v>541</v>
       </c>
-      <c r="B542" s="7">
+      <c r="B542" s="2">
         <v>907110484</v>
       </c>
-      <c r="C542" s="8">
+      <c r="C542" s="4">
         <v>1632</v>
       </c>
-      <c r="D542" s="6" t="str">
+      <c r="D542" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "907110484", "voteDate": "2026-03-20 16:32"},</v>
       </c>
@@ -8565,13 +8565,13 @@
       <c r="A543" s="4">
         <v>542</v>
       </c>
-      <c r="B543" s="7">
+      <c r="B543" s="2">
         <v>501254983</v>
       </c>
-      <c r="C543" s="8">
+      <c r="C543" s="4">
         <v>1635</v>
       </c>
-      <c r="D543" s="6" t="str">
+      <c r="D543" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "501254983", "voteDate": "2026-03-20 16:35"},</v>
       </c>
@@ -8580,13 +8580,13 @@
       <c r="A544" s="4">
         <v>543</v>
       </c>
-      <c r="B544" s="7">
+      <c r="B544" s="2">
         <v>336534444</v>
       </c>
-      <c r="C544" s="8">
+      <c r="C544" s="4">
         <v>1636</v>
       </c>
-      <c r="D544" s="6" t="str">
+      <c r="D544" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "336534444", "voteDate": "2026-03-20 16:36"},</v>
       </c>
@@ -8595,13 +8595,13 @@
       <c r="A545" s="4">
         <v>544</v>
       </c>
-      <c r="B545" s="7">
+      <c r="B545" s="2">
         <v>941876111</v>
       </c>
-      <c r="C545" s="8">
+      <c r="C545" s="4">
         <v>1637</v>
       </c>
-      <c r="D545" s="6" t="str">
+      <c r="D545" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "941876111", "voteDate": "2026-03-20 16:37"},</v>
       </c>
@@ -8610,13 +8610,13 @@
       <c r="A546" s="4">
         <v>545</v>
       </c>
-      <c r="B546" s="7">
+      <c r="B546" s="2">
         <v>947470205</v>
       </c>
-      <c r="C546" s="8">
+      <c r="C546" s="4">
         <v>1639</v>
       </c>
-      <c r="D546" s="6" t="str">
+      <c r="D546" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "947470205", "voteDate": "2026-03-20 16:39"},</v>
       </c>
@@ -8625,13 +8625,13 @@
       <c r="A547" s="4">
         <v>546</v>
       </c>
-      <c r="B547" s="7">
+      <c r="B547" s="2">
         <v>936620231</v>
       </c>
-      <c r="C547" s="8">
+      <c r="C547" s="4">
         <v>1641</v>
       </c>
-      <c r="D547" s="6" t="str">
+      <c r="D547" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "936620231", "voteDate": "2026-03-20 16:41"},</v>
       </c>
@@ -8640,13 +8640,13 @@
       <c r="A548" s="4">
         <v>547</v>
       </c>
-      <c r="B548" s="7">
+      <c r="B548" s="2">
         <v>879070721</v>
       </c>
-      <c r="C548" s="8">
+      <c r="C548" s="4">
         <v>1639</v>
       </c>
-      <c r="D548" s="6" t="str">
+      <c r="D548" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "879070721", "voteDate": "2026-03-20 16:39"},</v>
       </c>
@@ -8655,13 +8655,13 @@
       <c r="A549" s="4">
         <v>548</v>
       </c>
-      <c r="B549" s="7">
+      <c r="B549" s="2">
         <v>903654998</v>
       </c>
-      <c r="C549" s="8">
+      <c r="C549" s="4">
         <v>1633</v>
       </c>
-      <c r="D549" s="6" t="str">
+      <c r="D549" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "903654998", "voteDate": "2026-03-20 16:33"},</v>
       </c>
@@ -8670,13 +8670,13 @@
       <c r="A550" s="4">
         <v>549</v>
       </c>
-      <c r="B550" s="7">
+      <c r="B550" s="2">
         <v>912031025</v>
       </c>
-      <c r="C550" s="8">
+      <c r="C550" s="4">
         <v>1636</v>
       </c>
-      <c r="D550" s="6" t="str">
+      <c r="D550" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "912031025", "voteDate": "2026-03-20 16:36"},</v>
       </c>
@@ -8685,13 +8685,13 @@
       <c r="A551" s="4">
         <v>550</v>
       </c>
-      <c r="B551" s="7">
+      <c r="B551" s="2">
         <v>905649817</v>
       </c>
-      <c r="C551" s="8">
+      <c r="C551" s="4">
         <v>1638</v>
       </c>
-      <c r="D551" s="6" t="str">
+      <c r="D551" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "905649817", "voteDate": "2026-03-20 16:38"},</v>
       </c>
@@ -8700,13 +8700,13 @@
       <c r="A552" s="4">
         <v>551</v>
       </c>
-      <c r="B552" s="7">
+      <c r="B552" s="2">
         <v>911228556</v>
       </c>
-      <c r="C552" s="8">
+      <c r="C552" s="4">
         <v>1637</v>
       </c>
-      <c r="D552" s="6" t="str">
+      <c r="D552" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "911228556", "voteDate": "2026-03-20 16:37"},</v>
       </c>
@@ -8715,13 +8715,13 @@
       <c r="A553" s="4">
         <v>552</v>
       </c>
-      <c r="B553" s="7">
+      <c r="B553" s="2">
         <v>917385810</v>
       </c>
-      <c r="C553" s="8">
+      <c r="C553" s="4">
         <v>1634</v>
       </c>
-      <c r="D553" s="6" t="str">
+      <c r="D553" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "917385810", "voteDate": "2026-03-20 16:34"},</v>
       </c>
@@ -8730,13 +8730,13 @@
       <c r="A554" s="4">
         <v>553</v>
       </c>
-      <c r="B554" s="7">
+      <c r="B554" s="2">
         <v>916926356</v>
       </c>
-      <c r="C554" s="8">
+      <c r="C554" s="4">
         <v>1642</v>
       </c>
-      <c r="D554" s="6" t="str">
+      <c r="D554" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "916926356", "voteDate": "2026-03-20 16:42"},</v>
       </c>
@@ -8745,13 +8745,13 @@
       <c r="A555" s="4">
         <v>554</v>
       </c>
-      <c r="B555" s="7">
+      <c r="B555" s="2">
         <v>930565807</v>
       </c>
-      <c r="C555" s="8">
+      <c r="C555" s="4">
         <v>1642</v>
       </c>
-      <c r="D555" s="6" t="str">
+      <c r="D555" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "930565807", "voteDate": "2026-03-20 16:42"},</v>
       </c>
@@ -8760,13 +8760,13 @@
       <c r="A556" s="4">
         <v>555</v>
       </c>
-      <c r="B556" s="7">
+      <c r="B556" s="2">
         <v>912018747</v>
       </c>
-      <c r="C556" s="8">
+      <c r="C556" s="4">
         <v>1639</v>
       </c>
-      <c r="D556" s="6" t="str">
+      <c r="D556" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "912018747", "voteDate": "2026-03-20 16:39"},</v>
       </c>
@@ -8775,13 +8775,13 @@
       <c r="A557" s="4">
         <v>556</v>
       </c>
-      <c r="B557" s="7">
+      <c r="B557" s="2">
         <v>996242102</v>
       </c>
-      <c r="C557" s="8">
+      <c r="C557" s="4">
         <v>1642</v>
       </c>
-      <c r="D557" s="6" t="str">
+      <c r="D557" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "996242102", "voteDate": "2026-03-20 16:42"},</v>
       </c>
@@ -8790,13 +8790,13 @@
       <c r="A558" s="4">
         <v>557</v>
       </c>
-      <c r="B558" s="7">
+      <c r="B558" s="2">
         <v>944351222</v>
       </c>
-      <c r="C558" s="8">
+      <c r="C558" s="4">
         <v>1639</v>
       </c>
-      <c r="D558" s="6" t="str">
+      <c r="D558" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "944351222", "voteDate": "2026-03-20 16:39"},</v>
       </c>
@@ -8805,13 +8805,13 @@
       <c r="A559" s="4">
         <v>558</v>
       </c>
-      <c r="B559" s="7">
+      <c r="B559" s="2">
         <v>887800364</v>
       </c>
-      <c r="C559" s="8">
+      <c r="C559" s="4">
         <v>1638</v>
       </c>
-      <c r="D559" s="6" t="str">
+      <c r="D559" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "887800364", "voteDate": "2026-03-20 16:38"},</v>
       </c>
@@ -8820,13 +8820,13 @@
       <c r="A560" s="4">
         <v>559</v>
       </c>
-      <c r="B560" s="7">
+      <c r="B560" s="2">
         <v>934799495</v>
       </c>
-      <c r="C560" s="8">
+      <c r="C560" s="4">
         <v>1640</v>
       </c>
-      <c r="D560" s="6" t="str">
+      <c r="D560" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "934799495", "voteDate": "2026-03-20 16:40"},</v>
       </c>
@@ -8835,13 +8835,13 @@
       <c r="A561" s="4">
         <v>560</v>
       </c>
-      <c r="B561" s="7">
+      <c r="B561" s="2">
         <v>992952608</v>
       </c>
-      <c r="C561" s="8">
+      <c r="C561" s="4">
         <v>1644</v>
       </c>
-      <c r="D561" s="6" t="str">
+      <c r="D561" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "992952608", "voteDate": "2026-03-20 16:44"},</v>
       </c>
@@ -8850,13 +8850,13 @@
       <c r="A562" s="4">
         <v>561</v>
       </c>
-      <c r="B562" s="7">
+      <c r="B562" s="2">
         <v>337780102</v>
       </c>
-      <c r="C562" s="8">
+      <c r="C562" s="4">
         <v>1643</v>
       </c>
-      <c r="D562" s="6" t="str">
+      <c r="D562" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "337780102", "voteDate": "2026-03-20 16:43"},</v>
       </c>
@@ -8865,13 +8865,13 @@
       <c r="A563" s="4">
         <v>562</v>
       </c>
-      <c r="B563" s="7">
+      <c r="B563" s="2">
         <v>999795043</v>
       </c>
-      <c r="C563" s="8">
+      <c r="C563" s="4">
         <v>1644</v>
       </c>
-      <c r="D563" s="6" t="str">
+      <c r="D563" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "999795043", "voteDate": "2026-03-20 16:44"},</v>
       </c>
@@ -8880,13 +8880,13 @@
       <c r="A564" s="4">
         <v>563</v>
       </c>
-      <c r="B564" s="7">
+      <c r="B564" s="2">
         <v>947991961</v>
       </c>
-      <c r="C564" s="8">
+      <c r="C564" s="4">
         <v>1644</v>
       </c>
-      <c r="D564" s="6" t="str">
+      <c r="D564" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "947991961", "voteDate": "2026-03-20 16:44"},</v>
       </c>
@@ -8895,13 +8895,13 @@
       <c r="A565" s="4">
         <v>564</v>
       </c>
-      <c r="B565" s="7">
+      <c r="B565" s="2">
         <v>996359388</v>
       </c>
-      <c r="C565" s="8">
+      <c r="C565" s="4">
         <v>1643</v>
       </c>
-      <c r="D565" s="6" t="str">
+      <c r="D565" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "996359388", "voteDate": "2026-03-20 16:43"},</v>
       </c>
@@ -8910,13 +8910,13 @@
       <c r="A566" s="4">
         <v>565</v>
       </c>
-      <c r="B566" s="7">
+      <c r="B566" s="2">
         <v>880055141</v>
       </c>
-      <c r="C566" s="8">
+      <c r="C566" s="4">
         <v>1644</v>
       </c>
-      <c r="D566" s="6" t="str">
+      <c r="D566" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "880055141", "voteDate": "2026-03-20 16:44"},</v>
       </c>
@@ -8925,13 +8925,13 @@
       <c r="A567" s="4">
         <v>566</v>
       </c>
-      <c r="B567" s="7">
+      <c r="B567" s="2">
         <v>951307818</v>
       </c>
-      <c r="C567" s="8">
+      <c r="C567" s="4">
         <v>1644</v>
       </c>
-      <c r="D567" s="6" t="str">
+      <c r="D567" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "951307818", "voteDate": "2026-03-20 16:44"},</v>
       </c>
@@ -8940,13 +8940,13 @@
       <c r="A568" s="4">
         <v>567</v>
       </c>
-      <c r="B568" s="7">
+      <c r="B568" s="2">
         <v>903628114</v>
       </c>
-      <c r="C568" s="8">
+      <c r="C568" s="4">
         <v>1644</v>
       </c>
-      <c r="D568" s="6" t="str">
+      <c r="D568" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "903628114", "voteDate": "2026-03-20 16:44"},</v>
       </c>
@@ -8955,13 +8955,13 @@
       <c r="A569" s="4">
         <v>568</v>
       </c>
-      <c r="B569" s="7">
+      <c r="B569" s="2">
         <v>908324246</v>
       </c>
-      <c r="C569" s="8">
+      <c r="C569" s="4">
         <v>1649</v>
       </c>
-      <c r="D569" s="6" t="str">
+      <c r="D569" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "908324246", "voteDate": "2026-03-20 16:49"},</v>
       </c>
@@ -8970,13 +8970,13 @@
       <c r="A570" s="4">
         <v>569</v>
       </c>
-      <c r="B570" s="7">
+      <c r="B570" s="2">
         <v>773576757</v>
       </c>
-      <c r="C570" s="8">
+      <c r="C570" s="4">
         <v>1651</v>
       </c>
-      <c r="D570" s="6" t="str">
+      <c r="D570" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "773576757", "voteDate": "2026-03-20 16:51"},</v>
       </c>
@@ -8985,13 +8985,13 @@
       <c r="A571" s="4">
         <v>570</v>
       </c>
-      <c r="B571" s="7">
+      <c r="B571" s="2">
         <v>943737608</v>
       </c>
-      <c r="C571" s="8">
+      <c r="C571" s="4">
         <v>1644</v>
       </c>
-      <c r="D571" s="6" t="str">
+      <c r="D571" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "943737608", "voteDate": "2026-03-20 16:44"},</v>
       </c>
@@ -9000,13 +9000,13 @@
       <c r="A572" s="4">
         <v>571</v>
       </c>
-      <c r="B572" s="7">
+      <c r="B572" s="2">
         <v>995657876</v>
       </c>
-      <c r="C572" s="8">
+      <c r="C572" s="4">
         <v>1645</v>
       </c>
-      <c r="D572" s="6" t="str">
+      <c r="D572" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "995657876", "voteDate": "2026-03-20 16:45"},</v>
       </c>
@@ -9015,13 +9015,13 @@
       <c r="A573" s="4">
         <v>572</v>
       </c>
-      <c r="B573" s="7">
+      <c r="B573" s="2">
         <v>951556966</v>
       </c>
-      <c r="C573" s="8">
+      <c r="C573" s="4">
         <v>1646</v>
       </c>
-      <c r="D573" s="6" t="str">
+      <c r="D573" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "951556966", "voteDate": "2026-03-20 16:46"},</v>
       </c>
@@ -9030,13 +9030,13 @@
       <c r="A574" s="4">
         <v>573</v>
       </c>
-      <c r="B574" s="7">
+      <c r="B574" s="2">
         <v>999581384</v>
       </c>
-      <c r="C574" s="8">
+      <c r="C574" s="4">
         <v>1650</v>
       </c>
-      <c r="D574" s="6" t="str">
+      <c r="D574" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "999581384", "voteDate": "2026-03-20 16:50"},</v>
       </c>
@@ -9045,13 +9045,13 @@
       <c r="A575" s="4">
         <v>574</v>
       </c>
-      <c r="B575" s="7">
+      <c r="B575" s="2">
         <v>944014884</v>
       </c>
-      <c r="C575" s="8">
+      <c r="C575" s="4">
         <v>1633</v>
       </c>
-      <c r="D575" s="6" t="str">
+      <c r="D575" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "944014884", "voteDate": "2026-03-20 16:33"},</v>
       </c>
@@ -9060,13 +9060,13 @@
       <c r="A576" s="4">
         <v>575</v>
       </c>
-      <c r="B576" s="7">
+      <c r="B576" s="2">
         <v>931681033</v>
       </c>
-      <c r="C576" s="8">
+      <c r="C576" s="4">
         <v>1637</v>
       </c>
-      <c r="D576" s="6" t="str">
+      <c r="D576" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "931681033", "voteDate": "2026-03-20 16:37"},</v>
       </c>
@@ -9075,13 +9075,13 @@
       <c r="A577" s="4">
         <v>576</v>
       </c>
-      <c r="B577" s="7">
+      <c r="B577" s="2">
         <v>970293311</v>
       </c>
-      <c r="C577" s="8">
+      <c r="C577" s="4">
         <v>1616</v>
       </c>
-      <c r="D577" s="6" t="str">
+      <c r="D577" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "970293311", "voteDate": "2026-03-20 16:16"},</v>
       </c>
@@ -9090,13 +9090,13 @@
       <c r="A578" s="4">
         <v>577</v>
       </c>
-      <c r="B578" s="7">
+      <c r="B578" s="2">
         <v>931908208</v>
       </c>
-      <c r="C578" s="8">
+      <c r="C578" s="4">
         <v>1636</v>
       </c>
-      <c r="D578" s="6" t="str">
+      <c r="D578" t="str">
         <f t="shared" si="8"/>
         <v>{"phoneNumber": "931908208", "voteDate": "2026-03-20 16:36"},</v>
       </c>
@@ -9105,13 +9105,13 @@
       <c r="A579" s="4">
         <v>578</v>
       </c>
-      <c r="B579" s="7">
+      <c r="B579" s="2">
         <v>886040501</v>
       </c>
-      <c r="C579" s="8">
+      <c r="C579" s="4">
         <v>1647</v>
       </c>
-      <c r="D579" s="6" t="str">
+      <c r="D579" t="str">
         <f t="shared" ref="D579:D642" si="9">"{""phoneNumber"": """&amp;B579&amp;""", ""voteDate"": """&amp;TEXT(DATE(2026,3,20),"yyyy-mm-dd")&amp;" "&amp;TEXT(C579,"00\:00")&amp;"""},"</f>
         <v>{"phoneNumber": "886040501", "voteDate": "2026-03-20 16:47"},</v>
       </c>
@@ -9120,13 +9120,13 @@
       <c r="A580" s="4">
         <v>579</v>
       </c>
-      <c r="B580" s="7">
+      <c r="B580" s="2">
         <v>945741570</v>
       </c>
-      <c r="C580" s="8">
+      <c r="C580" s="4">
         <v>1649</v>
       </c>
-      <c r="D580" s="6" t="str">
+      <c r="D580" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "945741570", "voteDate": "2026-03-20 16:49"},</v>
       </c>
@@ -9135,13 +9135,13 @@
       <c r="A581" s="4">
         <v>580</v>
       </c>
-      <c r="B581" s="7">
+      <c r="B581" s="2">
         <v>935310147</v>
       </c>
-      <c r="C581" s="8">
+      <c r="C581" s="4">
         <v>1650</v>
       </c>
-      <c r="D581" s="6" t="str">
+      <c r="D581" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "935310147", "voteDate": "2026-03-20 16:50"},</v>
       </c>
@@ -9150,13 +9150,13 @@
       <c r="A582" s="4">
         <v>581</v>
       </c>
-      <c r="B582" s="7">
+      <c r="B582" s="2">
         <v>936035212</v>
       </c>
-      <c r="C582" s="8">
+      <c r="C582" s="4">
         <v>1644</v>
       </c>
-      <c r="D582" s="6" t="str">
+      <c r="D582" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "936035212", "voteDate": "2026-03-20 16:44"},</v>
       </c>
@@ -9165,13 +9165,13 @@
       <c r="A583" s="4">
         <v>582</v>
       </c>
-      <c r="B583" s="7">
+      <c r="B583" s="2">
         <v>945839598</v>
       </c>
-      <c r="C583" s="8">
+      <c r="C583" s="4">
         <v>1633</v>
       </c>
-      <c r="D583" s="6" t="str">
+      <c r="D583" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "945839598", "voteDate": "2026-03-20 16:33"},</v>
       </c>
@@ -9180,13 +9180,13 @@
       <c r="A584" s="4">
         <v>583</v>
       </c>
-      <c r="B584" s="7">
+      <c r="B584" s="2">
         <v>910941173</v>
       </c>
-      <c r="C584" s="8">
+      <c r="C584" s="4">
         <v>1636</v>
       </c>
-      <c r="D584" s="6" t="str">
+      <c r="D584" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "910941173", "voteDate": "2026-03-20 16:36"},</v>
       </c>
@@ -9195,13 +9195,13 @@
       <c r="A585" s="4">
         <v>584</v>
       </c>
-      <c r="B585" s="7">
+      <c r="B585" s="2">
         <v>940882594</v>
       </c>
-      <c r="C585" s="8">
+      <c r="C585" s="4">
         <v>1651</v>
       </c>
-      <c r="D585" s="6" t="str">
+      <c r="D585" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "940882594", "voteDate": "2026-03-20 16:51"},</v>
       </c>
@@ -9210,13 +9210,13 @@
       <c r="A586" s="4">
         <v>585</v>
       </c>
-      <c r="B586" s="7">
+      <c r="B586" s="2">
         <v>950857601</v>
       </c>
-      <c r="C586" s="8">
+      <c r="C586" s="4">
         <v>1621</v>
       </c>
-      <c r="D586" s="6" t="str">
+      <c r="D586" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "950857601", "voteDate": "2026-03-20 16:21"},</v>
       </c>
@@ -9225,13 +9225,13 @@
       <c r="A587" s="4">
         <v>586</v>
       </c>
-      <c r="B587" s="7">
+      <c r="B587" s="2">
         <v>941945582</v>
       </c>
-      <c r="C587" s="8">
+      <c r="C587" s="4">
         <v>1625</v>
       </c>
-      <c r="D587" s="6" t="str">
+      <c r="D587" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "941945582", "voteDate": "2026-03-20 16:25"},</v>
       </c>
@@ -9240,13 +9240,13 @@
       <c r="A588" s="4">
         <v>587</v>
       </c>
-      <c r="B588" s="7">
+      <c r="B588" s="2">
         <v>948022698</v>
       </c>
-      <c r="C588" s="8">
+      <c r="C588" s="4">
         <v>1539</v>
       </c>
-      <c r="D588" s="6" t="str">
+      <c r="D588" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "948022698", "voteDate": "2026-03-20 15:39"},</v>
       </c>
@@ -9255,13 +9255,13 @@
       <c r="A589" s="4">
         <v>588</v>
       </c>
-      <c r="B589" s="7">
+      <c r="B589" s="2">
         <v>917935299</v>
       </c>
-      <c r="C589" s="8">
+      <c r="C589" s="4">
         <v>1555</v>
       </c>
-      <c r="D589" s="6" t="str">
+      <c r="D589" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "917935299", "voteDate": "2026-03-20 15:55"},</v>
       </c>
@@ -9270,13 +9270,13 @@
       <c r="A590" s="4">
         <v>589</v>
       </c>
-      <c r="B590" s="7">
+      <c r="B590" s="2">
         <v>900049597</v>
       </c>
-      <c r="C590" s="8">
+      <c r="C590" s="4">
         <v>1557</v>
       </c>
-      <c r="D590" s="6" t="str">
+      <c r="D590" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "900049597", "voteDate": "2026-03-20 15:57"},</v>
       </c>
@@ -9285,13 +9285,13 @@
       <c r="A591" s="4">
         <v>590</v>
       </c>
-      <c r="B591" s="7">
+      <c r="B591" s="2">
         <v>937980372</v>
       </c>
-      <c r="C591" s="8">
+      <c r="C591" s="4">
         <v>1605</v>
       </c>
-      <c r="D591" s="6" t="str">
+      <c r="D591" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "937980372", "voteDate": "2026-03-20 16:05"},</v>
       </c>
@@ -9300,13 +9300,13 @@
       <c r="A592" s="4">
         <v>591</v>
       </c>
-      <c r="B592" s="7">
+      <c r="B592" s="2">
         <v>914671391</v>
       </c>
-      <c r="C592" s="8">
+      <c r="C592" s="4">
         <v>1604</v>
       </c>
-      <c r="D592" s="6" t="str">
+      <c r="D592" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "914671391", "voteDate": "2026-03-20 16:04"},</v>
       </c>
@@ -9315,13 +9315,13 @@
       <c r="A593" s="4">
         <v>592</v>
       </c>
-      <c r="B593" s="7">
+      <c r="B593" s="2">
         <v>877702698</v>
       </c>
-      <c r="C593" s="8">
+      <c r="C593" s="4">
         <v>1612</v>
       </c>
-      <c r="D593" s="6" t="str">
+      <c r="D593" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "877702698", "voteDate": "2026-03-20 16:12"},</v>
       </c>
@@ -9330,13 +9330,13 @@
       <c r="A594" s="4">
         <v>593</v>
       </c>
-      <c r="B594" s="7">
+      <c r="B594" s="2">
         <v>940031972</v>
       </c>
-      <c r="C594" s="8">
+      <c r="C594" s="4">
         <v>1609</v>
       </c>
-      <c r="D594" s="6" t="str">
+      <c r="D594" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "940031972", "voteDate": "2026-03-20 16:09"},</v>
       </c>
@@ -9345,13 +9345,13 @@
       <c r="A595" s="4">
         <v>594</v>
       </c>
-      <c r="B595" s="7">
+      <c r="B595" s="2">
         <v>946812009</v>
       </c>
-      <c r="C595" s="8">
+      <c r="C595" s="4">
         <v>1615</v>
       </c>
-      <c r="D595" s="6" t="str">
+      <c r="D595" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "946812009", "voteDate": "2026-03-20 16:15"},</v>
       </c>
@@ -9360,13 +9360,13 @@
       <c r="A596" s="4">
         <v>595</v>
       </c>
-      <c r="B596" s="7">
+      <c r="B596" s="2">
         <v>937340712</v>
       </c>
-      <c r="C596" s="8">
+      <c r="C596" s="4">
         <v>1620</v>
       </c>
-      <c r="D596" s="6" t="str">
+      <c r="D596" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "937340712", "voteDate": "2026-03-20 16:20"},</v>
       </c>
@@ -9375,13 +9375,13 @@
       <c r="A597" s="4">
         <v>596</v>
       </c>
-      <c r="B597" s="7">
+      <c r="B597" s="2">
         <v>941975758</v>
       </c>
-      <c r="C597" s="8">
+      <c r="C597" s="4">
         <v>1628</v>
       </c>
-      <c r="D597" s="6" t="str">
+      <c r="D597" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "941975758", "voteDate": "2026-03-20 16:28"},</v>
       </c>
@@ -9390,13 +9390,13 @@
       <c r="A598" s="4">
         <v>597</v>
       </c>
-      <c r="B598" s="7">
+      <c r="B598" s="2">
         <v>937340712</v>
       </c>
-      <c r="C598" s="8">
+      <c r="C598" s="4">
         <v>1620</v>
       </c>
-      <c r="D598" s="6" t="str">
+      <c r="D598" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "937340712", "voteDate": "2026-03-20 16:20"},</v>
       </c>
@@ -9405,13 +9405,13 @@
       <c r="A599" s="4">
         <v>598</v>
       </c>
-      <c r="B599" s="7">
+      <c r="B599" s="2">
         <v>993226680</v>
       </c>
-      <c r="C599" s="8">
+      <c r="C599" s="4">
         <v>1618</v>
       </c>
-      <c r="D599" s="6" t="str">
+      <c r="D599" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "993226680", "voteDate": "2026-03-20 16:18"},</v>
       </c>
@@ -9420,13 +9420,13 @@
       <c r="A600" s="4">
         <v>599</v>
       </c>
-      <c r="B600" s="7">
+      <c r="B600" s="2">
         <v>905702877</v>
       </c>
-      <c r="C600" s="8">
+      <c r="C600" s="4">
         <v>1617</v>
       </c>
-      <c r="D600" s="6" t="str">
+      <c r="D600" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "905702877", "voteDate": "2026-03-20 16:17"},</v>
       </c>
@@ -9435,13 +9435,13 @@
       <c r="A601" s="4">
         <v>600</v>
       </c>
-      <c r="B601" s="7">
+      <c r="B601" s="2">
         <v>500792881</v>
       </c>
-      <c r="C601" s="8">
+      <c r="C601" s="4">
         <v>1621</v>
       </c>
-      <c r="D601" s="6" t="str">
+      <c r="D601" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "500792881", "voteDate": "2026-03-20 16:21"},</v>
       </c>
@@ -9450,801 +9450,1501 @@
       <c r="A602" s="4">
         <v>601</v>
       </c>
-      <c r="B602" s="2"/>
-      <c r="C602" s="4"/>
-      <c r="D602" s="6"/>
+      <c r="B602" s="7">
+        <v>997984958</v>
+      </c>
+      <c r="C602" s="8">
+        <v>1623</v>
+      </c>
+      <c r="D602" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "997984958", "voteDate": "2026-03-20 16:23"},</v>
+      </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A603" s="4">
         <v>602</v>
       </c>
-      <c r="B603" s="2"/>
-      <c r="C603" s="4"/>
-      <c r="D603" s="6"/>
+      <c r="B603" s="7">
+        <v>942698844</v>
+      </c>
+      <c r="C603" s="8">
+        <v>1649</v>
+      </c>
+      <c r="D603" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "942698844", "voteDate": "2026-03-20 16:49"},</v>
+      </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A604" s="4">
         <v>603</v>
       </c>
-      <c r="B604" s="2"/>
-      <c r="C604" s="4"/>
-      <c r="D604" s="6"/>
+      <c r="B604" s="7">
+        <v>951055257</v>
+      </c>
+      <c r="C604" s="8">
+        <v>1652</v>
+      </c>
+      <c r="D604" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "951055257", "voteDate": "2026-03-20 16:52"},</v>
+      </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A605" s="4">
         <v>604</v>
       </c>
-      <c r="B605" s="2"/>
-      <c r="C605" s="4"/>
-      <c r="D605" s="6"/>
+      <c r="B605" s="7">
+        <v>770935459</v>
+      </c>
+      <c r="C605" s="8">
+        <v>1651</v>
+      </c>
+      <c r="D605" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "770935459", "voteDate": "2026-03-20 16:51"},</v>
+      </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A606" s="4">
         <v>605</v>
       </c>
-      <c r="B606" s="2"/>
-      <c r="C606" s="4"/>
-      <c r="D606" s="6"/>
+      <c r="B606" s="7">
+        <v>938008694</v>
+      </c>
+      <c r="C606" s="8">
+        <v>1645</v>
+      </c>
+      <c r="D606" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "938008694", "voteDate": "2026-03-20 16:45"},</v>
+      </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A607" s="4">
         <v>606</v>
       </c>
-      <c r="B607" s="2"/>
-      <c r="C607" s="4"/>
-      <c r="D607" s="6"/>
+      <c r="B607" s="7">
+        <v>775503072</v>
+      </c>
+      <c r="C607" s="8">
+        <v>1651</v>
+      </c>
+      <c r="D607" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "775503072", "voteDate": "2026-03-20 16:51"},</v>
+      </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A608" s="4">
         <v>607</v>
       </c>
-      <c r="B608" s="2"/>
-      <c r="C608" s="4"/>
-      <c r="D608" s="6"/>
+      <c r="B608" s="7">
+        <v>905557846</v>
+      </c>
+      <c r="C608" s="8">
+        <v>1653</v>
+      </c>
+      <c r="D608" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "905557846", "voteDate": "2026-03-20 16:53"},</v>
+      </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A609" s="4">
         <v>608</v>
       </c>
-      <c r="B609" s="2"/>
-      <c r="C609" s="4"/>
-      <c r="D609" s="6"/>
+      <c r="B609" s="7">
+        <v>939041058</v>
+      </c>
+      <c r="C609" s="8">
+        <v>1653</v>
+      </c>
+      <c r="D609" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "939041058", "voteDate": "2026-03-20 16:53"},</v>
+      </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A610" s="4">
         <v>609</v>
       </c>
-      <c r="B610" s="2"/>
-      <c r="C610" s="4"/>
-      <c r="D610" s="6"/>
+      <c r="B610" s="7">
+        <v>777134373</v>
+      </c>
+      <c r="C610" s="8">
+        <v>1654</v>
+      </c>
+      <c r="D610" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "777134373", "voteDate": "2026-03-20 16:54"},</v>
+      </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A611" s="4">
         <v>610</v>
       </c>
-      <c r="B611" s="2"/>
-      <c r="C611" s="4"/>
-      <c r="D611" s="6"/>
+      <c r="B611" s="7">
+        <v>773576727</v>
+      </c>
+      <c r="C611" s="8">
+        <v>1651</v>
+      </c>
+      <c r="D611" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "773576727", "voteDate": "2026-03-20 16:51"},</v>
+      </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A612" s="4">
         <v>611</v>
       </c>
-      <c r="B612" s="2"/>
-      <c r="C612" s="4"/>
-      <c r="D612" s="6"/>
+      <c r="B612" s="7">
+        <v>939041058</v>
+      </c>
+      <c r="C612" s="8">
+        <v>1653</v>
+      </c>
+      <c r="D612" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "939041058", "voteDate": "2026-03-20 16:53"},</v>
+      </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A613" s="4">
         <v>612</v>
       </c>
-      <c r="B613" s="2"/>
-      <c r="C613" s="4"/>
-      <c r="D613" s="6"/>
+      <c r="B613" s="7">
+        <v>930709299</v>
+      </c>
+      <c r="C613" s="8">
+        <v>1654</v>
+      </c>
+      <c r="D613" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "930709299", "voteDate": "2026-03-20 16:54"},</v>
+      </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A614" s="4">
         <v>613</v>
       </c>
-      <c r="B614" s="2"/>
-      <c r="C614" s="4"/>
-      <c r="D614" s="6"/>
+      <c r="B614" s="7">
+        <v>911222031</v>
+      </c>
+      <c r="C614" s="8">
+        <v>1657</v>
+      </c>
+      <c r="D614" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "911222031", "voteDate": "2026-03-20 16:57"},</v>
+      </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A615" s="4">
         <v>614</v>
       </c>
-      <c r="B615" s="2"/>
-      <c r="C615" s="4"/>
-      <c r="D615" s="6"/>
+      <c r="B615" s="7">
+        <v>935310147</v>
+      </c>
+      <c r="C615" s="8">
+        <v>1650</v>
+      </c>
+      <c r="D615" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "935310147", "voteDate": "2026-03-20 16:50"},</v>
+      </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A616" s="4">
         <v>615</v>
       </c>
-      <c r="B616" s="2"/>
-      <c r="C616" s="4"/>
-      <c r="D616" s="6"/>
+      <c r="B616" s="7">
+        <v>942570343</v>
+      </c>
+      <c r="C616" s="8">
+        <v>1656</v>
+      </c>
+      <c r="D616" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "942570343", "voteDate": "2026-03-20 16:56"},</v>
+      </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A617" s="4">
         <v>616</v>
       </c>
-      <c r="B617" s="2"/>
-      <c r="C617" s="4"/>
-      <c r="D617" s="6"/>
+      <c r="B617" s="7">
+        <v>884081018</v>
+      </c>
+      <c r="C617" s="8">
+        <v>1657</v>
+      </c>
+      <c r="D617" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "884081018", "voteDate": "2026-03-20 16:57"},</v>
+      </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A618" s="4">
         <v>617</v>
       </c>
-      <c r="B618" s="2"/>
-      <c r="C618" s="4"/>
-      <c r="D618" s="6"/>
+      <c r="B618" s="7">
+        <v>996279684</v>
+      </c>
+      <c r="C618" s="8">
+        <v>1658</v>
+      </c>
+      <c r="D618" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "996279684", "voteDate": "2026-03-20 16:58"},</v>
+      </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A619" s="4">
         <v>618</v>
       </c>
-      <c r="B619" s="2"/>
-      <c r="C619" s="4"/>
-      <c r="D619" s="6"/>
+      <c r="B619" s="7">
+        <v>885027371</v>
+      </c>
+      <c r="C619" s="8">
+        <v>1658</v>
+      </c>
+      <c r="D619" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "885027371", "voteDate": "2026-03-20 16:58"},</v>
+      </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A620" s="4">
         <v>619</v>
       </c>
-      <c r="B620" s="2"/>
-      <c r="C620" s="4"/>
-      <c r="D620" s="6"/>
+      <c r="B620" s="7">
+        <v>918207800</v>
+      </c>
+      <c r="C620" s="8">
+        <v>1654</v>
+      </c>
+      <c r="D620" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "918207800", "voteDate": "2026-03-20 16:54"},</v>
+      </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A621" s="4">
         <v>620</v>
       </c>
-      <c r="B621" s="2"/>
-      <c r="C621" s="4"/>
-      <c r="D621" s="6"/>
+      <c r="B621" s="7">
+        <v>995432911</v>
+      </c>
+      <c r="C621" s="8">
+        <v>1655</v>
+      </c>
+      <c r="D621" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "995432911", "voteDate": "2026-03-20 16:55"},</v>
+      </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A622" s="4">
         <v>621</v>
       </c>
-      <c r="B622" s="2"/>
-      <c r="C622" s="4"/>
-      <c r="D622" s="6"/>
+      <c r="B622" s="7">
+        <v>931169992</v>
+      </c>
+      <c r="C622" s="8">
+        <v>1700</v>
+      </c>
+      <c r="D622" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "931169992", "voteDate": "2026-03-20 17:00"},</v>
+      </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A623" s="4">
         <v>622</v>
       </c>
-      <c r="B623" s="2"/>
-      <c r="C623" s="4"/>
-      <c r="D623" s="6"/>
+      <c r="B623" s="7">
+        <v>951826332</v>
+      </c>
+      <c r="C623" s="8">
+        <v>1701</v>
+      </c>
+      <c r="D623" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "951826332", "voteDate": "2026-03-20 17:01"},</v>
+      </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A624" s="4">
         <v>623</v>
       </c>
-      <c r="B624" s="2"/>
-      <c r="C624" s="4"/>
-      <c r="D624" s="6"/>
+      <c r="B624" s="7">
+        <v>991288391</v>
+      </c>
+      <c r="C624" s="8">
+        <v>1703</v>
+      </c>
+      <c r="D624" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "991288391", "voteDate": "2026-03-20 17:03"},</v>
+      </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A625" s="4">
         <v>624</v>
       </c>
-      <c r="B625" s="2"/>
-      <c r="C625" s="4"/>
-      <c r="D625" s="6"/>
+      <c r="B625" s="7">
+        <v>931373111</v>
+      </c>
+      <c r="C625" s="8">
+        <v>1701</v>
+      </c>
+      <c r="D625" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "931373111", "voteDate": "2026-03-20 17:01"},</v>
+      </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A626" s="4">
         <v>625</v>
       </c>
-      <c r="B626" s="2"/>
-      <c r="C626" s="4"/>
-      <c r="D626" s="6"/>
+      <c r="B626" s="7">
+        <v>930858823</v>
+      </c>
+      <c r="C626" s="8">
+        <v>1702</v>
+      </c>
+      <c r="D626" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "930858823", "voteDate": "2026-03-20 17:02"},</v>
+      </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A627" s="4">
         <v>626</v>
       </c>
-      <c r="B627" s="2"/>
-      <c r="C627" s="4"/>
-      <c r="D627" s="6"/>
+      <c r="B627" s="7">
+        <v>948184868</v>
+      </c>
+      <c r="C627" s="8">
+        <v>1704</v>
+      </c>
+      <c r="D627" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "948184868", "voteDate": "2026-03-20 17:04"},</v>
+      </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A628" s="4">
         <v>627</v>
       </c>
-      <c r="B628" s="2"/>
-      <c r="C628" s="4"/>
-      <c r="D628" s="6"/>
+      <c r="B628" s="7">
+        <v>941983030</v>
+      </c>
+      <c r="C628" s="8">
+        <v>1702</v>
+      </c>
+      <c r="D628" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "941983030", "voteDate": "2026-03-20 17:02"},</v>
+      </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A629" s="4">
         <v>628</v>
       </c>
-      <c r="B629" s="2"/>
-      <c r="C629" s="4"/>
-      <c r="D629" s="6"/>
+      <c r="B629" s="7">
+        <v>912864686</v>
+      </c>
+      <c r="C629" s="8">
+        <v>1702</v>
+      </c>
+      <c r="D629" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "912864686", "voteDate": "2026-03-20 17:02"},</v>
+      </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A630" s="4">
         <v>629</v>
       </c>
-      <c r="B630" s="2"/>
-      <c r="C630" s="4"/>
-      <c r="D630" s="6"/>
+      <c r="B630" s="7">
+        <v>910690855</v>
+      </c>
+      <c r="C630" s="8">
+        <v>1702</v>
+      </c>
+      <c r="D630" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "910690855", "voteDate": "2026-03-20 17:02"},</v>
+      </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A631" s="4">
         <v>630</v>
       </c>
-      <c r="B631" s="2"/>
-      <c r="C631" s="4"/>
-      <c r="D631" s="6"/>
+      <c r="B631" s="7">
+        <v>955200125</v>
+      </c>
+      <c r="C631" s="8">
+        <v>1708</v>
+      </c>
+      <c r="D631" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "955200125", "voteDate": "2026-03-20 17:08"},</v>
+      </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A632" s="4">
         <v>631</v>
       </c>
-      <c r="B632" s="2"/>
-      <c r="C632" s="4"/>
-      <c r="D632" s="6"/>
+      <c r="B632" s="7">
+        <v>991288391</v>
+      </c>
+      <c r="C632" s="8">
+        <v>1703</v>
+      </c>
+      <c r="D632" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "991288391", "voteDate": "2026-03-20 17:03"},</v>
+      </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A633" s="4">
         <v>632</v>
       </c>
-      <c r="B633" s="2"/>
-      <c r="C633" s="4"/>
-      <c r="D633" s="6"/>
+      <c r="B633" s="7">
+        <v>703600891</v>
+      </c>
+      <c r="C633" s="8">
+        <v>1708</v>
+      </c>
+      <c r="D633" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "703600891", "voteDate": "2026-03-20 17:08"},</v>
+      </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A634" s="4">
         <v>633</v>
       </c>
-      <c r="B634" s="2"/>
-      <c r="C634" s="4"/>
-      <c r="D634" s="6"/>
+      <c r="B634" s="7">
+        <v>955322803</v>
+      </c>
+      <c r="C634" s="8">
+        <v>1709</v>
+      </c>
+      <c r="D634" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "955322803", "voteDate": "2026-03-20 17:09"},</v>
+      </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A635" s="4">
         <v>634</v>
       </c>
-      <c r="B635" s="2"/>
-      <c r="C635" s="4"/>
-      <c r="D635" s="6"/>
+      <c r="B635" s="7">
+        <v>994638594</v>
+      </c>
+      <c r="C635" s="8">
+        <v>1708</v>
+      </c>
+      <c r="D635" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "994638594", "voteDate": "2026-03-20 17:08"},</v>
+      </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A636" s="4">
         <v>635</v>
       </c>
-      <c r="B636" s="2"/>
-      <c r="C636" s="4"/>
-      <c r="D636" s="6"/>
+      <c r="B636" s="7">
+        <v>509002213</v>
+      </c>
+      <c r="C636" s="8">
+        <v>1710</v>
+      </c>
+      <c r="D636" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "509002213", "voteDate": "2026-03-20 17:10"},</v>
+      </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A637" s="4">
         <v>636</v>
       </c>
-      <c r="B637" s="2"/>
-      <c r="C637" s="4"/>
-      <c r="D637" s="6"/>
+      <c r="B637" s="7">
+        <v>931565582</v>
+      </c>
+      <c r="C637" s="8">
+        <v>1708</v>
+      </c>
+      <c r="D637" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "931565582", "voteDate": "2026-03-20 17:08"},</v>
+      </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A638" s="4">
         <v>637</v>
       </c>
-      <c r="B638" s="2"/>
-      <c r="C638" s="4"/>
-      <c r="D638" s="6"/>
+      <c r="B638" s="7">
+        <v>905140998</v>
+      </c>
+      <c r="C638" s="8">
+        <v>1710</v>
+      </c>
+      <c r="D638" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "905140998", "voteDate": "2026-03-20 17:10"},</v>
+      </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A639" s="4">
         <v>638</v>
       </c>
-      <c r="B639" s="2"/>
-      <c r="C639" s="4"/>
-      <c r="D639" s="6"/>
+      <c r="B639" s="7">
+        <v>889335023</v>
+      </c>
+      <c r="C639" s="8">
+        <v>1709</v>
+      </c>
+      <c r="D639" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "889335023", "voteDate": "2026-03-20 17:09"},</v>
+      </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A640" s="4">
         <v>639</v>
       </c>
-      <c r="B640" s="2"/>
-      <c r="C640" s="4"/>
-      <c r="D640" s="6"/>
+      <c r="B640" s="7">
+        <v>938267782</v>
+      </c>
+      <c r="C640" s="8">
+        <v>1714</v>
+      </c>
+      <c r="D640" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "938267782", "voteDate": "2026-03-20 17:14"},</v>
+      </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A641" s="4">
         <v>640</v>
       </c>
-      <c r="B641" s="2"/>
-      <c r="C641" s="4"/>
-      <c r="D641" s="6"/>
+      <c r="B641" s="7">
+        <v>336063072</v>
+      </c>
+      <c r="C641" s="8">
+        <v>1656</v>
+      </c>
+      <c r="D641" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "336063072", "voteDate": "2026-03-20 16:56"},</v>
+      </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A642" s="4">
         <v>641</v>
       </c>
-      <c r="B642" s="2"/>
-      <c r="C642" s="4"/>
-      <c r="D642" s="6"/>
+      <c r="B642" s="7">
+        <v>990150303</v>
+      </c>
+      <c r="C642" s="8">
+        <v>1702</v>
+      </c>
+      <c r="D642" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v>{"phoneNumber": "990150303", "voteDate": "2026-03-20 17:02"},</v>
+      </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A643" s="4">
         <v>642</v>
       </c>
-      <c r="B643" s="2"/>
-      <c r="C643" s="4"/>
-      <c r="D643" s="6"/>
+      <c r="B643" s="7">
+        <v>502771477</v>
+      </c>
+      <c r="C643" s="8">
+        <v>1701</v>
+      </c>
+      <c r="D643" s="6" t="str">
+        <f t="shared" ref="D643:D701" si="10">"{""phoneNumber"": """&amp;B643&amp;""", ""voteDate"": """&amp;TEXT(DATE(2026,3,20),"yyyy-mm-dd")&amp;" "&amp;TEXT(C643,"00\:00")&amp;"""},"</f>
+        <v>{"phoneNumber": "502771477", "voteDate": "2026-03-20 17:01"},</v>
+      </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A644" s="4">
         <v>643</v>
       </c>
-      <c r="B644" s="2"/>
-      <c r="C644" s="4"/>
-      <c r="D644" s="6"/>
+      <c r="B644" s="7">
+        <v>950674323</v>
+      </c>
+      <c r="C644" s="8">
+        <v>1708</v>
+      </c>
+      <c r="D644" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "950674323", "voteDate": "2026-03-20 17:08"},</v>
+      </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A645" s="4">
         <v>644</v>
       </c>
-      <c r="B645" s="2"/>
-      <c r="C645" s="4"/>
-      <c r="D645" s="6"/>
+      <c r="B645" s="7">
+        <v>507171593</v>
+      </c>
+      <c r="C645" s="8">
+        <v>1713</v>
+      </c>
+      <c r="D645" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "507171593", "voteDate": "2026-03-20 17:13"},</v>
+      </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A646" s="4">
         <v>645</v>
       </c>
-      <c r="B646" s="2"/>
-      <c r="C646" s="4"/>
-      <c r="D646" s="6"/>
+      <c r="B646" s="7">
+        <v>505810925</v>
+      </c>
+      <c r="C646" s="8">
+        <v>1636</v>
+      </c>
+      <c r="D646" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "505810925", "voteDate": "2026-03-20 16:36"},</v>
+      </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A647" s="4">
         <v>646</v>
       </c>
-      <c r="B647" s="2"/>
-      <c r="C647" s="4"/>
-      <c r="D647" s="6"/>
+      <c r="B647" s="7">
+        <v>915392525</v>
+      </c>
+      <c r="C647" s="8">
+        <v>1703</v>
+      </c>
+      <c r="D647" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "915392525", "voteDate": "2026-03-20 17:03"},</v>
+      </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A648" s="4">
         <v>647</v>
       </c>
-      <c r="B648" s="2"/>
-      <c r="C648" s="4"/>
-      <c r="D648" s="6"/>
+      <c r="B648" s="7">
+        <v>994934097</v>
+      </c>
+      <c r="C648" s="8">
+        <v>1705</v>
+      </c>
+      <c r="D648" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "994934097", "voteDate": "2026-03-20 17:05"},</v>
+      </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A649" s="4">
         <v>648</v>
       </c>
-      <c r="B649" s="2"/>
-      <c r="C649" s="4"/>
-      <c r="D649" s="6"/>
+      <c r="B649" s="7">
+        <v>902275989</v>
+      </c>
+      <c r="C649" s="8">
+        <v>1719</v>
+      </c>
+      <c r="D649" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "902275989", "voteDate": "2026-03-20 17:19"},</v>
+      </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A650" s="4">
         <v>649</v>
       </c>
-      <c r="B650" s="2"/>
-      <c r="C650" s="4"/>
-      <c r="D650" s="6"/>
+      <c r="B650" s="7">
+        <v>955200125</v>
+      </c>
+      <c r="C650" s="8">
+        <v>1708</v>
+      </c>
+      <c r="D650" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "955200125", "voteDate": "2026-03-20 17:08"},</v>
+      </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A651" s="4">
         <v>650</v>
       </c>
-      <c r="B651" s="2"/>
-      <c r="C651" s="4"/>
-      <c r="D651" s="6"/>
+      <c r="B651" s="7">
+        <v>777561133</v>
+      </c>
+      <c r="C651" s="8">
+        <v>1710</v>
+      </c>
+      <c r="D651" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "777561133", "voteDate": "2026-03-20 17:10"},</v>
+      </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A652" s="4">
         <v>651</v>
       </c>
-      <c r="B652" s="2"/>
-      <c r="C652" s="4"/>
-      <c r="D652" s="6"/>
+      <c r="B652" s="7">
+        <v>931939314</v>
+      </c>
+      <c r="C652" s="8">
+        <v>1715</v>
+      </c>
+      <c r="D652" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "931939314", "voteDate": "2026-03-20 17:15"},</v>
+      </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A653" s="4">
         <v>652</v>
       </c>
-      <c r="B653" s="2"/>
-      <c r="C653" s="4"/>
-      <c r="D653" s="6"/>
+      <c r="B653" s="7">
+        <v>911941394</v>
+      </c>
+      <c r="C653" s="8">
+        <v>1712</v>
+      </c>
+      <c r="D653" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "911941394", "voteDate": "2026-03-20 17:12"},</v>
+      </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A654" s="4">
         <v>653</v>
       </c>
-      <c r="B654" s="2"/>
-      <c r="C654" s="4"/>
-      <c r="D654" s="6"/>
+      <c r="B654" s="7">
+        <v>975450906</v>
+      </c>
+      <c r="C654" s="8">
+        <v>1721</v>
+      </c>
+      <c r="D654" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "975450906", "voteDate": "2026-03-20 17:21"},</v>
+      </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A655" s="4">
         <v>654</v>
       </c>
-      <c r="B655" s="2"/>
-      <c r="C655" s="4"/>
-      <c r="D655" s="6"/>
+      <c r="B655" s="7">
+        <v>901255989</v>
+      </c>
+      <c r="C655" s="8">
+        <v>1724</v>
+      </c>
+      <c r="D655" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "901255989", "voteDate": "2026-03-20 17:24"},</v>
+      </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A656" s="4">
         <v>655</v>
       </c>
-      <c r="B656" s="2"/>
-      <c r="C656" s="4"/>
-      <c r="D656" s="6"/>
+      <c r="B656" s="7">
+        <v>905976525</v>
+      </c>
+      <c r="C656" s="8">
+        <v>1724</v>
+      </c>
+      <c r="D656" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "905976525", "voteDate": "2026-03-20 17:24"},</v>
+      </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A657" s="4">
         <v>656</v>
       </c>
-      <c r="B657" s="2"/>
-      <c r="C657" s="4"/>
-      <c r="D657" s="6"/>
+      <c r="B657" s="7">
+        <v>877945355</v>
+      </c>
+      <c r="C657" s="8">
+        <v>1713</v>
+      </c>
+      <c r="D657" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "877945355", "voteDate": "2026-03-20 17:13"},</v>
+      </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A658" s="4">
         <v>657</v>
       </c>
-      <c r="B658" s="2"/>
-      <c r="C658" s="4"/>
-      <c r="D658" s="6"/>
+      <c r="B658" s="7">
+        <v>953748121</v>
+      </c>
+      <c r="C658" s="8">
+        <v>1713</v>
+      </c>
+      <c r="D658" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "953748121", "voteDate": "2026-03-20 17:13"},</v>
+      </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A659" s="4">
         <v>658</v>
       </c>
-      <c r="B659" s="2"/>
-      <c r="C659" s="4"/>
-      <c r="D659" s="6"/>
+      <c r="B659" s="7">
+        <v>932780008</v>
+      </c>
+      <c r="C659" s="8">
+        <v>1718</v>
+      </c>
+      <c r="D659" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "932780008", "voteDate": "2026-03-20 17:18"},</v>
+      </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A660" s="4">
         <v>659</v>
       </c>
-      <c r="B660" s="2"/>
-      <c r="C660" s="4"/>
-      <c r="D660" s="6"/>
+      <c r="B660" s="7">
+        <v>933180528</v>
+      </c>
+      <c r="C660" s="8">
+        <v>1719</v>
+      </c>
+      <c r="D660" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "933180528", "voteDate": "2026-03-20 17:19"},</v>
+      </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A661" s="4">
         <v>660</v>
       </c>
-      <c r="B661" s="2"/>
-      <c r="C661" s="4"/>
-      <c r="D661" s="6"/>
+      <c r="B661" s="7">
+        <v>882844393</v>
+      </c>
+      <c r="C661" s="8">
+        <v>1720</v>
+      </c>
+      <c r="D661" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "882844393", "voteDate": "2026-03-20 17:20"},</v>
+      </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A662" s="4">
         <v>661</v>
       </c>
-      <c r="B662" s="2"/>
-      <c r="C662" s="4"/>
-      <c r="D662" s="6"/>
+      <c r="B662" s="7">
+        <v>507707580</v>
+      </c>
+      <c r="C662" s="8">
+        <v>1723</v>
+      </c>
+      <c r="D662" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "507707580", "voteDate": "2026-03-20 17:23"},</v>
+      </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A663" s="4">
         <v>662</v>
       </c>
-      <c r="B663" s="2"/>
-      <c r="C663" s="4"/>
-      <c r="D663" s="6"/>
+      <c r="B663" s="7">
+        <v>905206747</v>
+      </c>
+      <c r="C663" s="8">
+        <v>1728</v>
+      </c>
+      <c r="D663" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "905206747", "voteDate": "2026-03-20 17:28"},</v>
+      </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A664" s="4">
         <v>663</v>
       </c>
-      <c r="B664" s="2"/>
-      <c r="C664" s="4"/>
-      <c r="D664" s="6"/>
+      <c r="B664" s="7">
+        <v>947449678</v>
+      </c>
+      <c r="C664" s="8">
+        <v>1733</v>
+      </c>
+      <c r="D664" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "947449678", "voteDate": "2026-03-20 17:33"},</v>
+      </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A665" s="4">
         <v>664</v>
       </c>
-      <c r="B665" s="2"/>
-      <c r="C665" s="4"/>
-      <c r="D665" s="6"/>
+      <c r="B665" s="7">
+        <v>508891631</v>
+      </c>
+      <c r="C665" s="8">
+        <v>1639</v>
+      </c>
+      <c r="D665" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "508891631", "voteDate": "2026-03-20 16:39"},</v>
+      </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A666" s="4">
         <v>665</v>
       </c>
-      <c r="B666" s="2"/>
-      <c r="C666" s="4"/>
-      <c r="D666" s="6"/>
+      <c r="B666" s="7">
+        <v>945080599</v>
+      </c>
+      <c r="C666" s="8">
+        <v>1637</v>
+      </c>
+      <c r="D666" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "945080599", "voteDate": "2026-03-20 16:37"},</v>
+      </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A667" s="4">
         <v>666</v>
       </c>
-      <c r="B667" s="2"/>
-      <c r="C667" s="4"/>
-      <c r="D667" s="6"/>
+      <c r="B667" s="7">
+        <v>934361718</v>
+      </c>
+      <c r="C667" s="8">
+        <v>1731</v>
+      </c>
+      <c r="D667" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "934361718", "voteDate": "2026-03-20 17:31"},</v>
+      </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A668" s="4">
         <v>667</v>
       </c>
-      <c r="B668" s="2"/>
-      <c r="C668" s="4"/>
-      <c r="D668" s="6"/>
+      <c r="B668" s="7">
+        <v>949780816</v>
+      </c>
+      <c r="C668" s="8">
+        <v>1732</v>
+      </c>
+      <c r="D668" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "949780816", "voteDate": "2026-03-20 17:32"},</v>
+      </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A669" s="4">
         <v>668</v>
       </c>
-      <c r="B669" s="2"/>
-      <c r="C669" s="4"/>
-      <c r="D669" s="6"/>
+      <c r="B669" s="7">
+        <v>911202272</v>
+      </c>
+      <c r="C669" s="8">
+        <v>1727</v>
+      </c>
+      <c r="D669" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "911202272", "voteDate": "2026-03-20 17:27"},</v>
+      </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A670" s="4">
         <v>669</v>
       </c>
-      <c r="B670" s="2"/>
-      <c r="C670" s="4"/>
-      <c r="D670" s="6"/>
+      <c r="B670" s="7">
+        <v>975900274</v>
+      </c>
+      <c r="C670" s="8">
+        <v>1731</v>
+      </c>
+      <c r="D670" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "975900274", "voteDate": "2026-03-20 17:31"},</v>
+      </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A671" s="4">
         <v>670</v>
       </c>
-      <c r="B671" s="2"/>
-      <c r="C671" s="4"/>
-      <c r="D671" s="6"/>
+      <c r="B671" s="7">
+        <v>931144597</v>
+      </c>
+      <c r="C671" s="8">
+        <v>1736</v>
+      </c>
+      <c r="D671" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "931144597", "voteDate": "2026-03-20 17:36"},</v>
+      </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A672" s="4">
         <v>671</v>
       </c>
-      <c r="B672" s="2"/>
-      <c r="C672" s="4"/>
-      <c r="D672" s="6"/>
+      <c r="B672" s="7">
+        <v>944237080</v>
+      </c>
+      <c r="C672" s="8">
+        <v>1736</v>
+      </c>
+      <c r="D672" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "944237080", "voteDate": "2026-03-20 17:36"},</v>
+      </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A673" s="4">
         <v>672</v>
       </c>
-      <c r="B673" s="2"/>
-      <c r="C673" s="4"/>
-      <c r="D673" s="6"/>
+      <c r="B673" s="7">
+        <v>902927121</v>
+      </c>
+      <c r="C673" s="8">
+        <v>1736</v>
+      </c>
+      <c r="D673" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "902927121", "voteDate": "2026-03-20 17:36"},</v>
+      </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A674" s="4">
         <v>673</v>
       </c>
-      <c r="B674" s="2"/>
-      <c r="C674" s="4"/>
-      <c r="D674" s="6"/>
+      <c r="B674" s="7">
+        <v>917471992</v>
+      </c>
+      <c r="C674" s="8">
+        <v>1744</v>
+      </c>
+      <c r="D674" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "917471992", "voteDate": "2026-03-20 17:44"},</v>
+      </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A675" s="4">
         <v>674</v>
       </c>
-      <c r="B675" s="2"/>
-      <c r="C675" s="4"/>
-      <c r="D675" s="6"/>
+      <c r="B675" s="7">
+        <v>700391929</v>
+      </c>
+      <c r="C675" s="8">
+        <v>1743</v>
+      </c>
+      <c r="D675" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "700391929", "voteDate": "2026-03-20 17:43"},</v>
+      </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A676" s="4">
         <v>675</v>
       </c>
-      <c r="B676" s="2"/>
-      <c r="C676" s="4"/>
-      <c r="D676" s="6"/>
+      <c r="B676" s="7">
+        <v>904959850</v>
+      </c>
+      <c r="C676" s="8">
+        <v>1726</v>
+      </c>
+      <c r="D676" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "904959850", "voteDate": "2026-03-20 17:26"},</v>
+      </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A677" s="4">
         <v>676</v>
       </c>
-      <c r="B677" s="2"/>
-      <c r="C677" s="4"/>
-      <c r="D677" s="6"/>
+      <c r="B677" s="7">
+        <v>919472212</v>
+      </c>
+      <c r="C677" s="8">
+        <v>1737</v>
+      </c>
+      <c r="D677" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "919472212", "voteDate": "2026-03-20 17:37"},</v>
+      </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A678" s="4">
         <v>677</v>
       </c>
-      <c r="B678" s="2"/>
-      <c r="C678" s="4"/>
-      <c r="D678" s="6"/>
+      <c r="B678" s="7">
+        <v>958390102</v>
+      </c>
+      <c r="C678" s="8">
+        <v>1748</v>
+      </c>
+      <c r="D678" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "958390102", "voteDate": "2026-03-20 17:48"},</v>
+      </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A679" s="4">
         <v>678</v>
       </c>
-      <c r="B679" s="2"/>
-      <c r="C679" s="4"/>
-      <c r="D679" s="6"/>
+      <c r="B679" s="7">
+        <v>912851252</v>
+      </c>
+      <c r="C679" s="8">
+        <v>1749</v>
+      </c>
+      <c r="D679" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "912851252", "voteDate": "2026-03-20 17:49"},</v>
+      </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A680" s="4">
         <v>679</v>
       </c>
-      <c r="B680" s="2"/>
-      <c r="C680" s="4"/>
-      <c r="D680" s="6"/>
+      <c r="B680" s="7">
+        <v>913207880</v>
+      </c>
+      <c r="C680" s="8">
+        <v>1718</v>
+      </c>
+      <c r="D680" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "913207880", "voteDate": "2026-03-20 17:18"},</v>
+      </c>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A681" s="4">
         <v>680</v>
       </c>
-      <c r="B681" s="2"/>
-      <c r="C681" s="4"/>
-      <c r="D681" s="6"/>
+      <c r="B681" s="7">
+        <v>973802526</v>
+      </c>
+      <c r="C681" s="8">
+        <v>1748</v>
+      </c>
+      <c r="D681" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "973802526", "voteDate": "2026-03-20 17:48"},</v>
+      </c>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A682" s="4">
         <v>681</v>
       </c>
-      <c r="B682" s="2"/>
-      <c r="C682" s="4"/>
-      <c r="D682" s="6"/>
+      <c r="B682" s="7">
+        <v>889529858</v>
+      </c>
+      <c r="C682" s="8">
+        <v>1750</v>
+      </c>
+      <c r="D682" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "889529858", "voteDate": "2026-03-20 17:50"},</v>
+      </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A683" s="4">
         <v>682</v>
       </c>
-      <c r="B683" s="2"/>
-      <c r="C683" s="4"/>
-      <c r="D683" s="6"/>
+      <c r="B683" s="7">
+        <v>903448579</v>
+      </c>
+      <c r="C683" s="8">
+        <v>1749</v>
+      </c>
+      <c r="D683" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "903448579", "voteDate": "2026-03-20 17:49"},</v>
+      </c>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A684" s="4">
         <v>683</v>
       </c>
-      <c r="B684" s="2"/>
-      <c r="C684" s="4"/>
-      <c r="D684" s="6"/>
+      <c r="B684" s="7">
+        <v>905632007</v>
+      </c>
+      <c r="C684" s="8">
+        <v>1748</v>
+      </c>
+      <c r="D684" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "905632007", "voteDate": "2026-03-20 17:48"},</v>
+      </c>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A685" s="4">
         <v>684</v>
       </c>
-      <c r="B685" s="2"/>
-      <c r="C685" s="4"/>
-      <c r="D685" s="6"/>
+      <c r="B685" s="7">
+        <v>917407515</v>
+      </c>
+      <c r="C685" s="8">
+        <v>1746</v>
+      </c>
+      <c r="D685" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "917407515", "voteDate": "2026-03-20 17:46"},</v>
+      </c>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A686" s="4">
         <v>685</v>
       </c>
-      <c r="B686" s="2"/>
-      <c r="C686" s="4"/>
-      <c r="D686" s="6"/>
+      <c r="B686" s="7">
+        <v>941210921</v>
+      </c>
+      <c r="C686" s="8">
+        <v>1751</v>
+      </c>
+      <c r="D686" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "941210921", "voteDate": "2026-03-20 17:51"},</v>
+      </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A687" s="4">
         <v>686</v>
       </c>
-      <c r="B687" s="2"/>
-      <c r="C687" s="4"/>
-      <c r="D687" s="6"/>
+      <c r="B687" s="7">
+        <v>948286655</v>
+      </c>
+      <c r="C687" s="8">
+        <v>1751</v>
+      </c>
+      <c r="D687" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "948286655", "voteDate": "2026-03-20 17:51"},</v>
+      </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A688" s="4">
         <v>687</v>
       </c>
-      <c r="B688" s="2"/>
-      <c r="C688" s="4"/>
-      <c r="D688" s="6"/>
+      <c r="B688" s="7">
+        <v>900595755</v>
+      </c>
+      <c r="C688" s="8">
+        <v>1740</v>
+      </c>
+      <c r="D688" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "900595755", "voteDate": "2026-03-20 17:40"},</v>
+      </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A689" s="4">
         <v>688</v>
       </c>
-      <c r="B689" s="2"/>
-      <c r="C689" s="4"/>
-      <c r="D689" s="6"/>
+      <c r="B689" s="7">
+        <v>903072942</v>
+      </c>
+      <c r="C689" s="8">
+        <v>1748</v>
+      </c>
+      <c r="D689" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "903072942", "voteDate": "2026-03-20 17:48"},</v>
+      </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A690" s="4">
         <v>689</v>
       </c>
-      <c r="B690" s="2"/>
-      <c r="C690" s="4"/>
-      <c r="D690" s="6"/>
+      <c r="B690" s="7">
+        <v>940592062</v>
+      </c>
+      <c r="C690" s="8">
+        <v>1744</v>
+      </c>
+      <c r="D690" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "940592062", "voteDate": "2026-03-20 17:44"},</v>
+      </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A691" s="4">
         <v>690</v>
       </c>
-      <c r="B691" s="2"/>
-      <c r="C691" s="4"/>
-      <c r="D691" s="6"/>
+      <c r="B691" s="7">
+        <v>941506595</v>
+      </c>
+      <c r="C691" s="8">
+        <v>1722</v>
+      </c>
+      <c r="D691" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "941506595", "voteDate": "2026-03-20 17:22"},</v>
+      </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A692" s="4">
         <v>691</v>
       </c>
-      <c r="B692" s="2"/>
-      <c r="C692" s="4"/>
-      <c r="D692" s="6"/>
+      <c r="B692" s="7">
+        <v>508852919</v>
+      </c>
+      <c r="C692" s="8">
+        <v>1739</v>
+      </c>
+      <c r="D692" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "508852919", "voteDate": "2026-03-20 17:39"},</v>
+      </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A693" s="4">
         <v>692</v>
       </c>
-      <c r="B693" s="2"/>
-      <c r="C693" s="4"/>
-      <c r="D693" s="6"/>
+      <c r="B693" s="7">
+        <v>919646331</v>
+      </c>
+      <c r="C693" s="8">
+        <v>1757</v>
+      </c>
+      <c r="D693" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "919646331", "voteDate": "2026-03-20 17:57"},</v>
+      </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A694" s="4">
         <v>693</v>
       </c>
-      <c r="B694" s="2"/>
-      <c r="C694" s="4"/>
-      <c r="D694" s="6"/>
+      <c r="B694" s="7">
+        <v>911066451</v>
+      </c>
+      <c r="C694" s="8">
+        <v>1749</v>
+      </c>
+      <c r="D694" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "911066451", "voteDate": "2026-03-20 17:49"},</v>
+      </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A695" s="4">
         <v>694</v>
       </c>
-      <c r="B695" s="2"/>
-      <c r="C695" s="4"/>
-      <c r="D695" s="6"/>
+      <c r="B695" s="7">
+        <v>916634439</v>
+      </c>
+      <c r="C695" s="8">
+        <v>1753</v>
+      </c>
+      <c r="D695" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "916634439", "voteDate": "2026-03-20 17:53"},</v>
+      </c>
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A696" s="4">
         <v>695</v>
       </c>
-      <c r="B696" s="2"/>
-      <c r="C696" s="4"/>
-      <c r="D696" s="6"/>
+      <c r="B696" s="7">
+        <v>934562809</v>
+      </c>
+      <c r="C696" s="8">
+        <v>1753</v>
+      </c>
+      <c r="D696" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "934562809", "voteDate": "2026-03-20 17:53"},</v>
+      </c>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A697" s="4">
         <v>696</v>
       </c>
-      <c r="B697" s="2"/>
-      <c r="C697" s="4"/>
-      <c r="D697" s="6"/>
+      <c r="B697" s="7">
+        <v>999570502</v>
+      </c>
+      <c r="C697" s="8">
+        <v>1756</v>
+      </c>
+      <c r="D697" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "999570502", "voteDate": "2026-03-20 17:56"},</v>
+      </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A698" s="4">
         <v>697</v>
       </c>
-      <c r="B698" s="2"/>
-      <c r="C698" s="4"/>
-      <c r="D698" s="6"/>
+      <c r="B698" s="7">
+        <v>931257528</v>
+      </c>
+      <c r="C698" s="8">
+        <v>1803</v>
+      </c>
+      <c r="D698" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "931257528", "voteDate": "2026-03-20 18:03"},</v>
+      </c>
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A699" s="4">
         <v>698</v>
       </c>
-      <c r="B699" s="2"/>
-      <c r="C699" s="4"/>
-      <c r="D699" s="6"/>
+      <c r="B699" s="7">
+        <v>991664122</v>
+      </c>
+      <c r="C699" s="8">
+        <v>1804</v>
+      </c>
+      <c r="D699" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "991664122", "voteDate": "2026-03-20 18:04"},</v>
+      </c>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A700" s="4">
         <v>699</v>
       </c>
-      <c r="B700" s="2"/>
-      <c r="C700" s="4"/>
-      <c r="D700" s="6"/>
+      <c r="B700" s="7">
+        <v>946669850</v>
+      </c>
+      <c r="C700" s="8">
+        <v>1732</v>
+      </c>
+      <c r="D700" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "946669850", "voteDate": "2026-03-20 17:32"},</v>
+      </c>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A701" s="4">
         <v>700</v>
       </c>
-      <c r="B701" s="2"/>
-      <c r="C701" s="4"/>
-      <c r="D701" s="6"/>
+      <c r="B701" s="7">
+        <v>998852730</v>
+      </c>
+      <c r="C701" s="8">
+        <v>1737</v>
+      </c>
+      <c r="D701" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "998852730", "voteDate": "2026-03-20 17:37"},</v>
+      </c>
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A702" s="4">
@@ -10252,7 +10952,6 @@
       </c>
       <c r="B702" s="2"/>
       <c r="C702" s="4"/>
-      <c r="D702" s="6"/>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A703" s="4">
@@ -10260,7 +10959,6 @@
       </c>
       <c r="B703" s="2"/>
       <c r="C703" s="4"/>
-      <c r="D703" s="6"/>
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A704" s="4">
@@ -10268,3983 +10966,3485 @@
       </c>
       <c r="B704" s="2"/>
       <c r="C704" s="4"/>
-      <c r="D704" s="6"/>
-    </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A705" s="4">
         <v>704</v>
       </c>
       <c r="B705" s="2"/>
       <c r="C705" s="4"/>
-      <c r="D705" s="6"/>
-    </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="706" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A706" s="4">
         <v>705</v>
       </c>
       <c r="B706" s="2"/>
       <c r="C706" s="4"/>
-      <c r="D706" s="6"/>
-    </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A707" s="4">
         <v>706</v>
       </c>
       <c r="B707" s="2"/>
       <c r="C707" s="4"/>
-      <c r="D707" s="6"/>
-    </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A708" s="4">
         <v>707</v>
       </c>
       <c r="B708" s="2"/>
       <c r="C708" s="4"/>
-      <c r="D708" s="6"/>
-    </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="709" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A709" s="4">
         <v>708</v>
       </c>
       <c r="B709" s="2"/>
       <c r="C709" s="4"/>
-      <c r="D709" s="6"/>
-    </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A710" s="4">
         <v>709</v>
       </c>
       <c r="B710" s="2"/>
       <c r="C710" s="4"/>
-      <c r="D710" s="6"/>
-    </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="711" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A711" s="4">
         <v>710</v>
       </c>
       <c r="B711" s="2"/>
       <c r="C711" s="4"/>
-      <c r="D711" s="6"/>
-    </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="712" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A712" s="4">
         <v>711</v>
       </c>
       <c r="B712" s="2"/>
       <c r="C712" s="4"/>
-      <c r="D712" s="6"/>
-    </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A713" s="4">
         <v>712</v>
       </c>
       <c r="B713" s="2"/>
       <c r="C713" s="4"/>
-      <c r="D713" s="6"/>
-    </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="714" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A714" s="4">
         <v>713</v>
       </c>
       <c r="B714" s="2"/>
       <c r="C714" s="4"/>
-      <c r="D714" s="6"/>
-    </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="715" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A715" s="4">
         <v>714</v>
       </c>
       <c r="B715" s="2"/>
       <c r="C715" s="4"/>
-      <c r="D715" s="6"/>
-    </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A716" s="4">
         <v>715</v>
       </c>
       <c r="B716" s="2"/>
       <c r="C716" s="4"/>
-      <c r="D716" s="6"/>
-    </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="717" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A717" s="4">
         <v>716</v>
       </c>
       <c r="B717" s="2"/>
       <c r="C717" s="4"/>
-      <c r="D717" s="6"/>
-    </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="718" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A718" s="4">
         <v>717</v>
       </c>
       <c r="B718" s="2"/>
       <c r="C718" s="4"/>
-      <c r="D718" s="6"/>
-    </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A719" s="4">
         <v>718</v>
       </c>
       <c r="B719" s="2"/>
       <c r="C719" s="4"/>
-      <c r="D719" s="6"/>
-    </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="720" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A720" s="4">
         <v>719</v>
       </c>
       <c r="B720" s="2"/>
       <c r="C720" s="4"/>
-      <c r="D720" s="6"/>
-    </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="721" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A721" s="4">
         <v>720</v>
       </c>
       <c r="B721" s="2"/>
       <c r="C721" s="4"/>
-      <c r="D721" s="6"/>
-    </row>
-    <row r="722" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A722" s="4">
         <v>721</v>
       </c>
       <c r="B722" s="2"/>
       <c r="C722" s="4"/>
-      <c r="D722" s="6"/>
-    </row>
-    <row r="723" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="723" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A723" s="4">
         <v>722</v>
       </c>
       <c r="B723" s="2"/>
       <c r="C723" s="4"/>
-      <c r="D723" s="6"/>
-    </row>
-    <row r="724" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="724" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A724" s="4">
         <v>723</v>
       </c>
       <c r="B724" s="2"/>
       <c r="C724" s="4"/>
-      <c r="D724" s="6"/>
-    </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A725" s="4">
         <v>724</v>
       </c>
       <c r="B725" s="2"/>
       <c r="C725" s="4"/>
-      <c r="D725" s="6"/>
-    </row>
-    <row r="726" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="726" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A726" s="4">
         <v>725</v>
       </c>
       <c r="B726" s="2"/>
       <c r="C726" s="4"/>
-      <c r="D726" s="6"/>
-    </row>
-    <row r="727" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="727" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A727" s="4">
         <v>726</v>
       </c>
       <c r="B727" s="2"/>
       <c r="C727" s="4"/>
-      <c r="D727" s="6"/>
-    </row>
-    <row r="728" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A728" s="4">
         <v>727</v>
       </c>
       <c r="B728" s="2"/>
       <c r="C728" s="4"/>
-      <c r="D728" s="6"/>
-    </row>
-    <row r="729" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="729" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A729" s="4">
         <v>728</v>
       </c>
       <c r="B729" s="2"/>
       <c r="C729" s="4"/>
-      <c r="D729" s="6"/>
-    </row>
-    <row r="730" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="730" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A730" s="4">
         <v>729</v>
       </c>
       <c r="B730" s="2"/>
       <c r="C730" s="4"/>
-      <c r="D730" s="6"/>
-    </row>
-    <row r="731" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A731" s="4">
         <v>730</v>
       </c>
       <c r="B731" s="2"/>
       <c r="C731" s="4"/>
-      <c r="D731" s="6"/>
-    </row>
-    <row r="732" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="732" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A732" s="4">
         <v>731</v>
       </c>
       <c r="B732" s="2"/>
       <c r="C732" s="4"/>
-      <c r="D732" s="6"/>
-    </row>
-    <row r="733" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="733" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A733" s="4">
         <v>732</v>
       </c>
       <c r="B733" s="2"/>
       <c r="C733" s="4"/>
-      <c r="D733" s="6"/>
-    </row>
-    <row r="734" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A734" s="4">
         <v>733</v>
       </c>
       <c r="B734" s="2"/>
       <c r="C734" s="4"/>
-      <c r="D734" s="6"/>
-    </row>
-    <row r="735" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="735" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A735" s="4">
         <v>734</v>
       </c>
       <c r="B735" s="2"/>
       <c r="C735" s="4"/>
-      <c r="D735" s="6"/>
-    </row>
-    <row r="736" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A736" s="4">
         <v>735</v>
       </c>
       <c r="B736" s="2"/>
       <c r="C736" s="4"/>
-      <c r="D736" s="6"/>
-    </row>
-    <row r="737" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="737" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A737" s="4">
         <v>736</v>
       </c>
       <c r="B737" s="2"/>
       <c r="C737" s="4"/>
-      <c r="D737" s="6"/>
-    </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="738" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A738" s="4">
         <v>737</v>
       </c>
       <c r="B738" s="2"/>
       <c r="C738" s="4"/>
-      <c r="D738" s="6"/>
-    </row>
-    <row r="739" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A739" s="4">
         <v>738</v>
       </c>
       <c r="B739" s="2"/>
       <c r="C739" s="4"/>
-      <c r="D739" s="6"/>
-    </row>
-    <row r="740" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="740" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A740" s="4">
         <v>739</v>
       </c>
       <c r="B740" s="2"/>
       <c r="C740" s="4"/>
-      <c r="D740" s="6"/>
-    </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="741" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A741" s="4">
         <v>740</v>
       </c>
       <c r="B741" s="2"/>
       <c r="C741" s="4"/>
-      <c r="D741" s="6"/>
-    </row>
-    <row r="742" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A742" s="4">
         <v>741</v>
       </c>
       <c r="B742" s="2"/>
       <c r="C742" s="4"/>
-      <c r="D742" s="6"/>
-    </row>
-    <row r="743" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="743" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A743" s="4">
         <v>742</v>
       </c>
       <c r="B743" s="2"/>
       <c r="C743" s="4"/>
-      <c r="D743" s="6"/>
-    </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="744" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A744" s="4">
         <v>743</v>
       </c>
       <c r="B744" s="2"/>
       <c r="C744" s="4"/>
-      <c r="D744" s="6"/>
-    </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A745" s="4">
         <v>744</v>
       </c>
       <c r="B745" s="2"/>
       <c r="C745" s="4"/>
-      <c r="D745" s="6"/>
-    </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="746" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A746" s="4">
         <v>745</v>
       </c>
       <c r="B746" s="2"/>
       <c r="C746" s="4"/>
-      <c r="D746" s="6"/>
-    </row>
-    <row r="747" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="747" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A747" s="4">
         <v>746</v>
       </c>
       <c r="B747" s="2"/>
       <c r="C747" s="4"/>
-      <c r="D747" s="6"/>
-    </row>
-    <row r="748" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A748" s="4">
         <v>747</v>
       </c>
       <c r="B748" s="2"/>
       <c r="C748" s="4"/>
-      <c r="D748" s="6"/>
-    </row>
-    <row r="749" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="749" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A749" s="4">
         <v>748</v>
       </c>
       <c r="B749" s="2"/>
       <c r="C749" s="4"/>
-      <c r="D749" s="6"/>
-    </row>
-    <row r="750" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="750" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A750" s="4">
         <v>749</v>
       </c>
       <c r="B750" s="2"/>
       <c r="C750" s="4"/>
-      <c r="D750" s="6"/>
-    </row>
-    <row r="751" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="751" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A751" s="4">
         <v>750</v>
       </c>
       <c r="B751" s="2"/>
       <c r="C751" s="4"/>
-      <c r="D751" s="6"/>
-    </row>
-    <row r="752" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="752" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A752" s="4">
         <v>751</v>
       </c>
       <c r="B752" s="2"/>
       <c r="C752" s="4"/>
-      <c r="D752" s="6"/>
-    </row>
-    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="753" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A753" s="4">
         <v>752</v>
       </c>
       <c r="B753" s="2"/>
       <c r="C753" s="4"/>
-      <c r="D753" s="6"/>
-    </row>
-    <row r="754" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="754" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A754" s="4">
         <v>753</v>
       </c>
       <c r="B754" s="2"/>
       <c r="C754" s="4"/>
-      <c r="D754" s="6"/>
-    </row>
-    <row r="755" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="755" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A755" s="4">
         <v>754</v>
       </c>
       <c r="B755" s="2"/>
       <c r="C755" s="4"/>
-      <c r="D755" s="6"/>
-    </row>
-    <row r="756" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="756" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A756" s="4">
         <v>755</v>
       </c>
       <c r="B756" s="2"/>
       <c r="C756" s="4"/>
-      <c r="D756" s="6"/>
-    </row>
-    <row r="757" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="757" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A757" s="4">
         <v>756</v>
       </c>
       <c r="B757" s="2"/>
       <c r="C757" s="4"/>
-      <c r="D757" s="6"/>
-    </row>
-    <row r="758" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="758" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A758" s="4">
         <v>757</v>
       </c>
       <c r="B758" s="2"/>
       <c r="C758" s="4"/>
-      <c r="D758" s="6"/>
-    </row>
-    <row r="759" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="759" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A759" s="4">
         <v>758</v>
       </c>
       <c r="B759" s="2"/>
       <c r="C759" s="4"/>
-      <c r="D759" s="6"/>
-    </row>
-    <row r="760" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="760" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A760" s="4">
         <v>759</v>
       </c>
       <c r="B760" s="2"/>
       <c r="C760" s="4"/>
-      <c r="D760" s="6"/>
-    </row>
-    <row r="761" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="761" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A761" s="4">
         <v>760</v>
       </c>
       <c r="B761" s="2"/>
       <c r="C761" s="4"/>
-      <c r="D761" s="6"/>
-    </row>
-    <row r="762" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="762" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A762" s="4">
         <v>761</v>
       </c>
       <c r="B762" s="2"/>
       <c r="C762" s="4"/>
-      <c r="D762" s="6"/>
-    </row>
-    <row r="763" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="763" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A763" s="4">
         <v>762</v>
       </c>
       <c r="B763" s="2"/>
       <c r="C763" s="4"/>
-      <c r="D763" s="6"/>
-    </row>
-    <row r="764" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="764" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A764" s="4">
         <v>763</v>
       </c>
       <c r="B764" s="2"/>
       <c r="C764" s="4"/>
-      <c r="D764" s="6"/>
-    </row>
-    <row r="765" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="765" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A765" s="4">
         <v>764</v>
       </c>
       <c r="B765" s="2"/>
       <c r="C765" s="4"/>
-      <c r="D765" s="6"/>
-    </row>
-    <row r="766" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="766" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A766" s="4">
         <v>765</v>
       </c>
       <c r="B766" s="2"/>
       <c r="C766" s="4"/>
-      <c r="D766" s="6"/>
-    </row>
-    <row r="767" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="767" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A767" s="4">
         <v>766</v>
       </c>
       <c r="B767" s="2"/>
       <c r="C767" s="4"/>
-      <c r="D767" s="6"/>
-    </row>
-    <row r="768" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="768" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A768" s="4">
         <v>767</v>
       </c>
       <c r="B768" s="2"/>
       <c r="C768" s="4"/>
-      <c r="D768" s="6"/>
-    </row>
-    <row r="769" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="769" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A769" s="4">
         <v>768</v>
       </c>
       <c r="B769" s="2"/>
       <c r="C769" s="4"/>
-      <c r="D769" s="6"/>
-    </row>
-    <row r="770" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="770" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A770" s="4">
         <v>769</v>
       </c>
       <c r="B770" s="2"/>
       <c r="C770" s="4"/>
-      <c r="D770" s="6"/>
-    </row>
-    <row r="771" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="771" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A771" s="4">
         <v>770</v>
       </c>
       <c r="B771" s="2"/>
       <c r="C771" s="4"/>
-      <c r="D771" s="6"/>
-    </row>
-    <row r="772" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A772" s="4">
         <v>771</v>
       </c>
       <c r="B772" s="2"/>
       <c r="C772" s="4"/>
-      <c r="D772" s="6"/>
-    </row>
-    <row r="773" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="773" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A773" s="4">
         <v>772</v>
       </c>
       <c r="B773" s="2"/>
       <c r="C773" s="4"/>
-      <c r="D773" s="6"/>
-    </row>
-    <row r="774" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="774" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A774" s="4">
         <v>773</v>
       </c>
       <c r="B774" s="2"/>
       <c r="C774" s="4"/>
-      <c r="D774" s="6"/>
-    </row>
-    <row r="775" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A775" s="4">
         <v>774</v>
       </c>
       <c r="B775" s="2"/>
       <c r="C775" s="4"/>
-      <c r="D775" s="6"/>
-    </row>
-    <row r="776" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="776" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A776" s="4">
         <v>775</v>
       </c>
       <c r="B776" s="2"/>
       <c r="C776" s="4"/>
-      <c r="D776" s="6"/>
-    </row>
-    <row r="777" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="777" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A777" s="4">
         <v>776</v>
       </c>
       <c r="B777" s="2"/>
       <c r="C777" s="4"/>
-      <c r="D777" s="6"/>
-    </row>
-    <row r="778" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A778" s="4">
         <v>777</v>
       </c>
       <c r="B778" s="2"/>
       <c r="C778" s="4"/>
-      <c r="D778" s="6"/>
-    </row>
-    <row r="779" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="779" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A779" s="4">
         <v>778</v>
       </c>
       <c r="B779" s="2"/>
       <c r="C779" s="4"/>
-      <c r="D779" s="6"/>
-    </row>
-    <row r="780" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="780" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A780" s="4">
         <v>779</v>
       </c>
       <c r="B780" s="2"/>
       <c r="C780" s="4"/>
-      <c r="D780" s="6"/>
-    </row>
-    <row r="781" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A781" s="4">
         <v>780</v>
       </c>
       <c r="B781" s="2"/>
       <c r="C781" s="4"/>
-      <c r="D781" s="6"/>
-    </row>
-    <row r="782" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="782" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A782" s="4">
         <v>781</v>
       </c>
       <c r="B782" s="2"/>
       <c r="C782" s="4"/>
-      <c r="D782" s="6"/>
-    </row>
-    <row r="783" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="783" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A783" s="4">
         <v>782</v>
       </c>
       <c r="B783" s="2"/>
       <c r="C783" s="4"/>
-      <c r="D783" s="6"/>
-    </row>
-    <row r="784" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="784" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A784" s="4">
         <v>783</v>
       </c>
       <c r="B784" s="2"/>
       <c r="C784" s="4"/>
-      <c r="D784" s="6"/>
-    </row>
-    <row r="785" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="785" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A785" s="4">
         <v>784</v>
       </c>
       <c r="B785" s="2"/>
       <c r="C785" s="4"/>
-      <c r="D785" s="6"/>
-    </row>
-    <row r="786" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="786" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A786" s="4">
         <v>785</v>
       </c>
       <c r="B786" s="2"/>
       <c r="C786" s="4"/>
-      <c r="D786" s="6"/>
-    </row>
-    <row r="787" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="787" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A787" s="4">
         <v>786</v>
       </c>
       <c r="B787" s="2"/>
       <c r="C787" s="4"/>
-      <c r="D787" s="6"/>
-    </row>
-    <row r="788" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="788" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A788" s="4">
         <v>787</v>
       </c>
       <c r="B788" s="2"/>
       <c r="C788" s="4"/>
-      <c r="D788" s="6"/>
-    </row>
-    <row r="789" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="789" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A789" s="4">
         <v>788</v>
       </c>
       <c r="B789" s="2"/>
       <c r="C789" s="4"/>
-      <c r="D789" s="6"/>
-    </row>
-    <row r="790" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="790" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A790" s="4">
         <v>789</v>
       </c>
       <c r="B790" s="2"/>
       <c r="C790" s="4"/>
-      <c r="D790" s="6"/>
-    </row>
-    <row r="791" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="791" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A791" s="4">
         <v>790</v>
       </c>
       <c r="B791" s="2"/>
       <c r="C791" s="4"/>
-      <c r="D791" s="6"/>
-    </row>
-    <row r="792" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="792" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A792" s="4">
         <v>791</v>
       </c>
       <c r="B792" s="2"/>
       <c r="C792" s="4"/>
-      <c r="D792" s="6"/>
-    </row>
-    <row r="793" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A793" s="4">
         <v>792</v>
       </c>
       <c r="B793" s="2"/>
       <c r="C793" s="4"/>
-      <c r="D793" s="6"/>
-    </row>
-    <row r="794" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A794" s="4">
         <v>793</v>
       </c>
       <c r="B794" s="2"/>
       <c r="C794" s="4"/>
-      <c r="D794" s="6"/>
-    </row>
-    <row r="795" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A795" s="4">
         <v>794</v>
       </c>
       <c r="B795" s="2"/>
       <c r="C795" s="4"/>
-      <c r="D795" s="6"/>
-    </row>
-    <row r="796" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A796" s="4">
         <v>795</v>
       </c>
       <c r="B796" s="2"/>
       <c r="C796" s="4"/>
-      <c r="D796" s="6"/>
-    </row>
-    <row r="797" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A797" s="4">
         <v>796</v>
       </c>
       <c r="B797" s="2"/>
       <c r="C797" s="4"/>
-      <c r="D797" s="6"/>
-    </row>
-    <row r="798" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="798" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A798" s="4">
         <v>797</v>
       </c>
       <c r="B798" s="2"/>
       <c r="C798" s="4"/>
-      <c r="D798" s="6"/>
-    </row>
-    <row r="799" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A799" s="4">
         <v>798</v>
       </c>
       <c r="B799" s="2"/>
       <c r="C799" s="4"/>
-      <c r="D799" s="6"/>
-    </row>
-    <row r="800" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="800" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A800" s="4">
         <v>799</v>
       </c>
       <c r="B800" s="2"/>
       <c r="C800" s="4"/>
-      <c r="D800" s="6"/>
-    </row>
-    <row r="801" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="801" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A801" s="4">
         <v>800</v>
       </c>
       <c r="B801" s="2"/>
       <c r="C801" s="4"/>
-      <c r="D801" s="6"/>
-    </row>
-    <row r="802" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="802" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A802" s="4">
         <v>801</v>
       </c>
       <c r="B802" s="2"/>
       <c r="C802" s="4"/>
-      <c r="D802" s="6"/>
-    </row>
-    <row r="803" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="803" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A803" s="4">
         <v>802</v>
       </c>
       <c r="B803" s="2"/>
       <c r="C803" s="4"/>
-      <c r="D803" s="6"/>
-    </row>
-    <row r="804" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="804" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A804" s="4">
         <v>803</v>
       </c>
       <c r="B804" s="2"/>
       <c r="C804" s="4"/>
-      <c r="D804" s="6"/>
-    </row>
-    <row r="805" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="805" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A805" s="4">
         <v>804</v>
       </c>
       <c r="B805" s="2"/>
       <c r="C805" s="4"/>
-      <c r="D805" s="6"/>
-    </row>
-    <row r="806" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="806" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A806" s="4">
         <v>805</v>
       </c>
       <c r="B806" s="2"/>
       <c r="C806" s="4"/>
-      <c r="D806" s="6"/>
-    </row>
-    <row r="807" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="807" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A807" s="4">
         <v>806</v>
       </c>
       <c r="B807" s="2"/>
       <c r="C807" s="4"/>
-      <c r="D807" s="6"/>
-    </row>
-    <row r="808" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="808" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A808" s="4">
         <v>807</v>
       </c>
       <c r="B808" s="2"/>
       <c r="C808" s="4"/>
-      <c r="D808" s="6"/>
-    </row>
-    <row r="809" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="809" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A809" s="4">
         <v>808</v>
       </c>
       <c r="B809" s="2"/>
       <c r="C809" s="4"/>
-      <c r="D809" s="6"/>
-    </row>
-    <row r="810" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="810" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A810" s="4">
         <v>809</v>
       </c>
       <c r="B810" s="2"/>
       <c r="C810" s="4"/>
-      <c r="D810" s="6"/>
-    </row>
-    <row r="811" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="811" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A811" s="4">
         <v>810</v>
       </c>
       <c r="B811" s="2"/>
       <c r="C811" s="4"/>
-      <c r="D811" s="6"/>
-    </row>
-    <row r="812" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="812" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A812" s="4">
         <v>811</v>
       </c>
       <c r="B812" s="2"/>
       <c r="C812" s="4"/>
-      <c r="D812" s="6"/>
-    </row>
-    <row r="813" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="813" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A813" s="4">
         <v>812</v>
       </c>
       <c r="B813" s="2"/>
       <c r="C813" s="4"/>
-      <c r="D813" s="6"/>
-    </row>
-    <row r="814" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="814" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A814" s="4">
         <v>813</v>
       </c>
       <c r="B814" s="2"/>
       <c r="C814" s="4"/>
-      <c r="D814" s="6"/>
-    </row>
-    <row r="815" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="815" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A815" s="4">
         <v>814</v>
       </c>
       <c r="B815" s="2"/>
       <c r="C815" s="4"/>
-      <c r="D815" s="6"/>
-    </row>
-    <row r="816" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="816" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A816" s="4">
         <v>815</v>
       </c>
       <c r="B816" s="2"/>
       <c r="C816" s="4"/>
-      <c r="D816" s="6"/>
-    </row>
-    <row r="817" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="817" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A817" s="4">
         <v>816</v>
       </c>
       <c r="B817" s="2"/>
       <c r="C817" s="4"/>
-      <c r="D817" s="6"/>
-    </row>
-    <row r="818" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="818" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A818" s="4">
         <v>817</v>
       </c>
       <c r="B818" s="2"/>
       <c r="C818" s="4"/>
-      <c r="D818" s="6"/>
-    </row>
-    <row r="819" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="819" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A819" s="4">
         <v>818</v>
       </c>
       <c r="B819" s="2"/>
       <c r="C819" s="4"/>
-      <c r="D819" s="6"/>
-    </row>
-    <row r="820" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="820" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A820" s="4">
         <v>819</v>
       </c>
       <c r="B820" s="2"/>
       <c r="C820" s="4"/>
-      <c r="D820" s="6"/>
-    </row>
-    <row r="821" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="821" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A821" s="4">
         <v>820</v>
       </c>
       <c r="B821" s="2"/>
       <c r="C821" s="4"/>
-      <c r="D821" s="6"/>
-    </row>
-    <row r="822" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="822" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A822" s="4">
         <v>821</v>
       </c>
       <c r="B822" s="2"/>
       <c r="C822" s="4"/>
-      <c r="D822" s="6"/>
-    </row>
-    <row r="823" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="823" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A823" s="4">
         <v>822</v>
       </c>
       <c r="B823" s="2"/>
       <c r="C823" s="4"/>
-      <c r="D823" s="6"/>
-    </row>
-    <row r="824" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="824" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A824" s="4">
         <v>823</v>
       </c>
       <c r="B824" s="2"/>
       <c r="C824" s="4"/>
-      <c r="D824" s="6"/>
-    </row>
-    <row r="825" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="825" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A825" s="4">
         <v>824</v>
       </c>
       <c r="B825" s="2"/>
       <c r="C825" s="4"/>
-      <c r="D825" s="6"/>
-    </row>
-    <row r="826" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A826" s="4">
         <v>825</v>
       </c>
       <c r="B826" s="2"/>
       <c r="C826" s="4"/>
-      <c r="D826" s="6"/>
-    </row>
-    <row r="827" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="827" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A827" s="4">
         <v>826</v>
       </c>
       <c r="B827" s="2"/>
       <c r="C827" s="4"/>
-      <c r="D827" s="6"/>
-    </row>
-    <row r="828" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="828" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A828" s="4">
         <v>827</v>
       </c>
       <c r="B828" s="2"/>
       <c r="C828" s="4"/>
-      <c r="D828" s="6"/>
-    </row>
-    <row r="829" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="829" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A829" s="4">
         <v>828</v>
       </c>
       <c r="B829" s="2"/>
       <c r="C829" s="4"/>
-      <c r="D829" s="6"/>
-    </row>
-    <row r="830" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="830" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A830" s="4">
         <v>829</v>
       </c>
       <c r="B830" s="2"/>
       <c r="C830" s="4"/>
-      <c r="D830" s="6"/>
-    </row>
-    <row r="831" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="831" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A831" s="4">
         <v>830</v>
       </c>
       <c r="B831" s="2"/>
       <c r="C831" s="4"/>
-      <c r="D831" s="6"/>
-    </row>
-    <row r="832" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="832" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A832" s="4">
         <v>831</v>
       </c>
       <c r="B832" s="2"/>
       <c r="C832" s="4"/>
-      <c r="D832" s="6"/>
-    </row>
-    <row r="833" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="833" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A833" s="4">
         <v>832</v>
       </c>
       <c r="B833" s="2"/>
       <c r="C833" s="4"/>
-      <c r="D833" s="6"/>
-    </row>
-    <row r="834" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="834" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A834" s="4">
         <v>833</v>
       </c>
       <c r="B834" s="2"/>
       <c r="C834" s="4"/>
-      <c r="D834" s="6"/>
-    </row>
-    <row r="835" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="835" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A835" s="4">
         <v>834</v>
       </c>
       <c r="B835" s="2"/>
       <c r="C835" s="4"/>
-      <c r="D835" s="6"/>
-    </row>
-    <row r="836" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="836" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A836" s="4">
         <v>835</v>
       </c>
       <c r="B836" s="2"/>
       <c r="C836" s="4"/>
-      <c r="D836" s="6"/>
-    </row>
-    <row r="837" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="837" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A837" s="4">
         <v>836</v>
       </c>
       <c r="B837" s="2"/>
       <c r="C837" s="4"/>
-      <c r="D837" s="6"/>
-    </row>
-    <row r="838" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="838" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A838" s="4">
         <v>837</v>
       </c>
       <c r="B838" s="2"/>
       <c r="C838" s="4"/>
-      <c r="D838" s="6"/>
-    </row>
-    <row r="839" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="839" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A839" s="4">
         <v>838</v>
       </c>
       <c r="B839" s="2"/>
       <c r="C839" s="4"/>
-      <c r="D839" s="6"/>
-    </row>
-    <row r="840" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="840" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A840" s="4">
         <v>839</v>
       </c>
       <c r="B840" s="2"/>
       <c r="C840" s="4"/>
-      <c r="D840" s="6"/>
-    </row>
-    <row r="841" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="841" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A841" s="4">
         <v>840</v>
       </c>
       <c r="B841" s="2"/>
       <c r="C841" s="4"/>
-      <c r="D841" s="6"/>
-    </row>
-    <row r="842" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="842" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A842" s="4">
         <v>841</v>
       </c>
       <c r="B842" s="2"/>
       <c r="C842" s="4"/>
-      <c r="D842" s="6"/>
-    </row>
-    <row r="843" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="843" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A843" s="4">
         <v>842</v>
       </c>
       <c r="B843" s="2"/>
       <c r="C843" s="4"/>
-      <c r="D843" s="6"/>
-    </row>
-    <row r="844" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="844" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A844" s="4">
         <v>843</v>
       </c>
       <c r="B844" s="2"/>
       <c r="C844" s="4"/>
-      <c r="D844" s="6"/>
-    </row>
-    <row r="845" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="845" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A845" s="4">
         <v>844</v>
       </c>
       <c r="B845" s="2"/>
       <c r="C845" s="4"/>
-      <c r="D845" s="6"/>
-    </row>
-    <row r="846" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="846" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A846" s="4">
         <v>845</v>
       </c>
       <c r="B846" s="2"/>
       <c r="C846" s="4"/>
-      <c r="D846" s="6"/>
-    </row>
-    <row r="847" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="847" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A847" s="4">
         <v>846</v>
       </c>
       <c r="B847" s="2"/>
       <c r="C847" s="4"/>
-      <c r="D847" s="6"/>
-    </row>
-    <row r="848" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="848" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A848" s="4">
         <v>847</v>
       </c>
       <c r="B848" s="2"/>
       <c r="C848" s="4"/>
-      <c r="D848" s="6"/>
-    </row>
-    <row r="849" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="849" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A849" s="4">
         <v>848</v>
       </c>
       <c r="B849" s="2"/>
       <c r="C849" s="4"/>
-      <c r="D849" s="6"/>
-    </row>
-    <row r="850" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="850" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A850" s="4">
         <v>849</v>
       </c>
       <c r="B850" s="2"/>
       <c r="C850" s="4"/>
-      <c r="D850" s="6"/>
-    </row>
-    <row r="851" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="851" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A851" s="4">
         <v>850</v>
       </c>
       <c r="B851" s="2"/>
       <c r="C851" s="4"/>
-      <c r="D851" s="6"/>
-    </row>
-    <row r="852" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="852" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A852" s="4">
         <v>851</v>
       </c>
       <c r="B852" s="2"/>
       <c r="C852" s="4"/>
-      <c r="D852" s="6"/>
-    </row>
-    <row r="853" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="853" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A853" s="4">
         <v>852</v>
       </c>
       <c r="B853" s="2"/>
       <c r="C853" s="4"/>
-      <c r="D853" s="6"/>
-    </row>
-    <row r="854" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="854" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A854" s="4">
         <v>853</v>
       </c>
       <c r="B854" s="2"/>
       <c r="C854" s="4"/>
-      <c r="D854" s="6"/>
-    </row>
-    <row r="855" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="855" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A855" s="4">
         <v>854</v>
       </c>
       <c r="B855" s="2"/>
       <c r="C855" s="4"/>
-      <c r="D855" s="6"/>
-    </row>
-    <row r="856" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="856" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A856" s="4">
         <v>855</v>
       </c>
       <c r="B856" s="2"/>
       <c r="C856" s="4"/>
-      <c r="D856" s="6"/>
-    </row>
-    <row r="857" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="857" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A857" s="4">
         <v>856</v>
       </c>
       <c r="B857" s="2"/>
       <c r="C857" s="4"/>
-      <c r="D857" s="6"/>
-    </row>
-    <row r="858" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="858" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A858" s="4">
         <v>857</v>
       </c>
       <c r="B858" s="2"/>
       <c r="C858" s="4"/>
-      <c r="D858" s="6"/>
-    </row>
-    <row r="859" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="859" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A859" s="4">
         <v>858</v>
       </c>
       <c r="B859" s="2"/>
       <c r="C859" s="4"/>
-      <c r="D859" s="6"/>
-    </row>
-    <row r="860" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="860" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A860" s="4">
         <v>859</v>
       </c>
       <c r="B860" s="2"/>
       <c r="C860" s="4"/>
-      <c r="D860" s="6"/>
-    </row>
-    <row r="861" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="861" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A861" s="4">
         <v>860</v>
       </c>
       <c r="B861" s="2"/>
       <c r="C861" s="4"/>
-      <c r="D861" s="6"/>
-    </row>
-    <row r="862" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A862" s="4">
         <v>861</v>
       </c>
       <c r="B862" s="2"/>
       <c r="C862" s="4"/>
-      <c r="D862" s="6"/>
-    </row>
-    <row r="863" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="863" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A863" s="4">
         <v>862</v>
       </c>
       <c r="B863" s="2"/>
       <c r="C863" s="4"/>
-      <c r="D863" s="6"/>
-    </row>
-    <row r="864" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="864" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A864" s="4">
         <v>863</v>
       </c>
       <c r="B864" s="2"/>
       <c r="C864" s="4"/>
-      <c r="D864" s="6"/>
-    </row>
-    <row r="865" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="865" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A865" s="4">
         <v>864</v>
       </c>
       <c r="B865" s="2"/>
       <c r="C865" s="4"/>
-      <c r="D865" s="6"/>
-    </row>
-    <row r="866" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="866" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A866" s="4">
         <v>865</v>
       </c>
       <c r="B866" s="2"/>
       <c r="C866" s="4"/>
-      <c r="D866" s="6"/>
-    </row>
-    <row r="867" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="867" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A867" s="4">
         <v>866</v>
       </c>
       <c r="B867" s="2"/>
       <c r="C867" s="4"/>
-      <c r="D867" s="6"/>
-    </row>
-    <row r="868" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A868" s="4">
         <v>867</v>
       </c>
       <c r="B868" s="2"/>
       <c r="C868" s="4"/>
-      <c r="D868" s="6"/>
-    </row>
-    <row r="869" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="869" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A869" s="4">
         <v>868</v>
       </c>
       <c r="B869" s="2"/>
       <c r="C869" s="4"/>
-      <c r="D869" s="6"/>
-    </row>
-    <row r="870" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="870" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A870" s="4">
         <v>869</v>
       </c>
       <c r="B870" s="2"/>
       <c r="C870" s="4"/>
-      <c r="D870" s="6"/>
-    </row>
-    <row r="871" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A871" s="4">
         <v>870</v>
       </c>
       <c r="B871" s="2"/>
       <c r="C871" s="4"/>
-      <c r="D871" s="6"/>
-    </row>
-    <row r="872" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="872" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A872" s="4">
         <v>871</v>
       </c>
       <c r="B872" s="2"/>
       <c r="C872" s="4"/>
-      <c r="D872" s="6"/>
-    </row>
-    <row r="873" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="873" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A873" s="4">
         <v>872</v>
       </c>
       <c r="B873" s="2"/>
       <c r="C873" s="4"/>
-      <c r="D873" s="6"/>
-    </row>
-    <row r="874" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A874" s="4">
         <v>873</v>
       </c>
       <c r="B874" s="2"/>
       <c r="C874" s="4"/>
-      <c r="D874" s="6"/>
-    </row>
-    <row r="875" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="875" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A875" s="4">
         <v>874</v>
       </c>
       <c r="B875" s="2"/>
       <c r="C875" s="4"/>
-      <c r="D875" s="6"/>
-    </row>
-    <row r="876" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="876" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A876" s="4">
         <v>875</v>
       </c>
       <c r="B876" s="2"/>
       <c r="C876" s="4"/>
-      <c r="D876" s="6"/>
-    </row>
-    <row r="877" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A877" s="4">
         <v>876</v>
       </c>
       <c r="B877" s="2"/>
       <c r="C877" s="4"/>
-      <c r="D877" s="6"/>
-    </row>
-    <row r="878" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="878" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A878" s="4">
         <v>877</v>
       </c>
       <c r="B878" s="2"/>
       <c r="C878" s="4"/>
-      <c r="D878" s="6"/>
-    </row>
-    <row r="879" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="879" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A879" s="4">
         <v>878</v>
       </c>
       <c r="B879" s="2"/>
       <c r="C879" s="4"/>
-      <c r="D879" s="6"/>
-    </row>
-    <row r="880" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A880" s="4">
         <v>879</v>
       </c>
       <c r="B880" s="2"/>
       <c r="C880" s="4"/>
-      <c r="D880" s="6"/>
-    </row>
-    <row r="881" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="881" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A881" s="4">
         <v>880</v>
       </c>
       <c r="B881" s="2"/>
       <c r="C881" s="4"/>
-      <c r="D881" s="6"/>
-    </row>
-    <row r="882" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="882" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A882" s="4">
         <v>881</v>
       </c>
       <c r="B882" s="2"/>
       <c r="C882" s="4"/>
-      <c r="D882" s="6"/>
-    </row>
-    <row r="883" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A883" s="4">
         <v>882</v>
       </c>
       <c r="B883" s="2"/>
       <c r="C883" s="4"/>
-      <c r="D883" s="6"/>
-    </row>
-    <row r="884" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="884" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A884" s="4">
         <v>883</v>
       </c>
       <c r="B884" s="2"/>
       <c r="C884" s="4"/>
-      <c r="D884" s="6"/>
-    </row>
-    <row r="885" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="885" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A885" s="4">
         <v>884</v>
       </c>
       <c r="B885" s="2"/>
       <c r="C885" s="4"/>
-      <c r="D885" s="6"/>
-    </row>
-    <row r="886" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A886" s="4">
         <v>885</v>
       </c>
       <c r="B886" s="2"/>
       <c r="C886" s="4"/>
-      <c r="D886" s="6"/>
-    </row>
-    <row r="887" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="887" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A887" s="4">
         <v>886</v>
       </c>
       <c r="B887" s="2"/>
       <c r="C887" s="4"/>
-      <c r="D887" s="6"/>
-    </row>
-    <row r="888" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="888" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A888" s="4">
         <v>887</v>
       </c>
       <c r="B888" s="2"/>
       <c r="C888" s="4"/>
-      <c r="D888" s="6"/>
-    </row>
-    <row r="889" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="889" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A889" s="4">
         <v>888</v>
       </c>
       <c r="B889" s="2"/>
       <c r="C889" s="4"/>
-      <c r="D889" s="6"/>
-    </row>
-    <row r="890" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="890" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A890" s="4">
         <v>889</v>
       </c>
       <c r="B890" s="2"/>
       <c r="C890" s="4"/>
-      <c r="D890" s="6"/>
-    </row>
-    <row r="891" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="891" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A891" s="4">
         <v>890</v>
       </c>
       <c r="B891" s="2"/>
       <c r="C891" s="4"/>
-      <c r="D891" s="6"/>
-    </row>
-    <row r="892" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="892" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A892" s="4">
         <v>891</v>
       </c>
       <c r="B892" s="2"/>
       <c r="C892" s="4"/>
-      <c r="D892" s="6"/>
-    </row>
-    <row r="893" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="893" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A893" s="4">
         <v>892</v>
       </c>
       <c r="B893" s="2"/>
       <c r="C893" s="4"/>
-      <c r="D893" s="6"/>
-    </row>
-    <row r="894" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="894" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A894" s="4">
         <v>893</v>
       </c>
       <c r="B894" s="2"/>
       <c r="C894" s="4"/>
-      <c r="D894" s="6"/>
-    </row>
-    <row r="895" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="895" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A895" s="4">
         <v>894</v>
       </c>
       <c r="B895" s="2"/>
       <c r="C895" s="4"/>
-      <c r="D895" s="6"/>
-    </row>
-    <row r="896" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="896" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A896" s="4">
         <v>895</v>
       </c>
       <c r="B896" s="2"/>
       <c r="C896" s="4"/>
-      <c r="D896" s="6"/>
-    </row>
-    <row r="897" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="897" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A897" s="4">
         <v>896</v>
       </c>
       <c r="B897" s="2"/>
       <c r="C897" s="4"/>
-      <c r="D897" s="6"/>
-    </row>
-    <row r="898" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="898" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A898" s="4">
         <v>897</v>
       </c>
       <c r="B898" s="2"/>
       <c r="C898" s="4"/>
-      <c r="D898" s="6"/>
-    </row>
-    <row r="899" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="899" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A899" s="4">
         <v>898</v>
       </c>
       <c r="B899" s="2"/>
       <c r="C899" s="4"/>
-      <c r="D899" s="6"/>
-    </row>
-    <row r="900" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="900" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A900" s="4">
         <v>899</v>
       </c>
       <c r="B900" s="2"/>
       <c r="C900" s="4"/>
-      <c r="D900" s="6"/>
-    </row>
-    <row r="901" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="901" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A901" s="4">
         <v>900</v>
       </c>
       <c r="B901" s="2"/>
       <c r="C901" s="4"/>
-      <c r="D901" s="6"/>
-    </row>
-    <row r="902" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="902" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A902" s="4">
         <v>901</v>
       </c>
       <c r="B902" s="2"/>
       <c r="C902" s="4"/>
-      <c r="D902" s="6"/>
-    </row>
-    <row r="903" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="903" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A903" s="4">
         <v>902</v>
       </c>
       <c r="B903" s="2"/>
       <c r="C903" s="4"/>
-      <c r="D903" s="6"/>
-    </row>
-    <row r="904" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="904" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A904" s="4">
         <v>903</v>
       </c>
       <c r="B904" s="2"/>
       <c r="C904" s="4"/>
-      <c r="D904" s="6"/>
-    </row>
-    <row r="905" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="905" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A905" s="4">
         <v>904</v>
       </c>
       <c r="B905" s="2"/>
       <c r="C905" s="4"/>
-      <c r="D905" s="6"/>
-    </row>
-    <row r="906" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="906" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A906" s="4">
         <v>905</v>
       </c>
       <c r="B906" s="2"/>
       <c r="C906" s="4"/>
-      <c r="D906" s="6"/>
-    </row>
-    <row r="907" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="907" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A907" s="4">
         <v>906</v>
       </c>
       <c r="B907" s="2"/>
       <c r="C907" s="4"/>
-      <c r="D907" s="6"/>
-    </row>
-    <row r="908" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="908" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A908" s="4">
         <v>907</v>
       </c>
       <c r="B908" s="2"/>
       <c r="C908" s="4"/>
-      <c r="D908" s="6"/>
-    </row>
-    <row r="909" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="909" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A909" s="4">
         <v>908</v>
       </c>
       <c r="B909" s="2"/>
       <c r="C909" s="4"/>
-      <c r="D909" s="6"/>
-    </row>
-    <row r="910" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="910" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A910" s="4">
         <v>909</v>
       </c>
       <c r="B910" s="2"/>
       <c r="C910" s="4"/>
-      <c r="D910" s="6"/>
-    </row>
-    <row r="911" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="911" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A911" s="4">
         <v>910</v>
       </c>
       <c r="B911" s="2"/>
       <c r="C911" s="4"/>
-      <c r="D911" s="6"/>
-    </row>
-    <row r="912" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="912" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A912" s="4">
         <v>911</v>
       </c>
       <c r="B912" s="2"/>
       <c r="C912" s="4"/>
-      <c r="D912" s="6"/>
-    </row>
-    <row r="913" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="913" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A913" s="4">
         <v>912</v>
       </c>
       <c r="B913" s="2"/>
       <c r="C913" s="4"/>
-      <c r="D913" s="6"/>
-    </row>
-    <row r="914" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="914" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A914" s="4">
         <v>913</v>
       </c>
       <c r="B914" s="2"/>
       <c r="C914" s="4"/>
-      <c r="D914" s="6"/>
-    </row>
-    <row r="915" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="915" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A915" s="4">
         <v>914</v>
       </c>
       <c r="B915" s="2"/>
       <c r="C915" s="4"/>
-      <c r="D915" s="6"/>
-    </row>
-    <row r="916" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="916" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A916" s="4">
         <v>915</v>
       </c>
       <c r="B916" s="2"/>
       <c r="C916" s="4"/>
-      <c r="D916" s="6"/>
-    </row>
-    <row r="917" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="917" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A917" s="4">
         <v>916</v>
       </c>
       <c r="B917" s="2"/>
       <c r="C917" s="4"/>
-      <c r="D917" s="6"/>
-    </row>
-    <row r="918" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="918" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A918" s="4">
         <v>917</v>
       </c>
       <c r="B918" s="2"/>
       <c r="C918" s="4"/>
-      <c r="D918" s="6"/>
-    </row>
-    <row r="919" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="919" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A919" s="4">
         <v>918</v>
       </c>
       <c r="B919" s="2"/>
       <c r="C919" s="4"/>
-      <c r="D919" s="6"/>
-    </row>
-    <row r="920" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="920" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A920" s="4">
         <v>919</v>
       </c>
       <c r="B920" s="2"/>
       <c r="C920" s="4"/>
-      <c r="D920" s="6"/>
-    </row>
-    <row r="921" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="921" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A921" s="4">
         <v>920</v>
       </c>
       <c r="B921" s="2"/>
       <c r="C921" s="4"/>
-      <c r="D921" s="6"/>
-    </row>
-    <row r="922" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="922" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A922" s="4">
         <v>921</v>
       </c>
       <c r="B922" s="2"/>
       <c r="C922" s="4"/>
-      <c r="D922" s="6"/>
-    </row>
-    <row r="923" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="923" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A923" s="4">
         <v>922</v>
       </c>
       <c r="B923" s="2"/>
       <c r="C923" s="4"/>
-      <c r="D923" s="6"/>
-    </row>
-    <row r="924" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="924" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A924" s="4">
         <v>923</v>
       </c>
       <c r="B924" s="2"/>
       <c r="C924" s="4"/>
-      <c r="D924" s="6"/>
-    </row>
-    <row r="925" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="925" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A925" s="4">
         <v>924</v>
       </c>
       <c r="B925" s="2"/>
       <c r="C925" s="4"/>
-      <c r="D925" s="6"/>
-    </row>
-    <row r="926" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="926" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A926" s="4">
         <v>925</v>
       </c>
       <c r="B926" s="2"/>
       <c r="C926" s="4"/>
-      <c r="D926" s="6"/>
-    </row>
-    <row r="927" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="927" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A927" s="4">
         <v>926</v>
       </c>
       <c r="B927" s="2"/>
       <c r="C927" s="4"/>
-      <c r="D927" s="6"/>
-    </row>
-    <row r="928" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="928" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A928" s="4">
         <v>927</v>
       </c>
       <c r="B928" s="2"/>
       <c r="C928" s="4"/>
-      <c r="D928" s="6"/>
-    </row>
-    <row r="929" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="929" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A929" s="4">
         <v>928</v>
       </c>
       <c r="B929" s="2"/>
       <c r="C929" s="4"/>
-      <c r="D929" s="6"/>
-    </row>
-    <row r="930" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="930" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A930" s="4">
         <v>929</v>
       </c>
       <c r="B930" s="2"/>
       <c r="C930" s="4"/>
-      <c r="D930" s="6"/>
-    </row>
-    <row r="931" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="931" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A931" s="4">
         <v>930</v>
       </c>
       <c r="B931" s="2"/>
       <c r="C931" s="4"/>
-      <c r="D931" s="6"/>
-    </row>
-    <row r="932" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="932" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A932" s="4">
         <v>931</v>
       </c>
       <c r="B932" s="2"/>
       <c r="C932" s="4"/>
-      <c r="D932" s="6"/>
-    </row>
-    <row r="933" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="933" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A933" s="4">
         <v>932</v>
       </c>
       <c r="B933" s="2"/>
       <c r="C933" s="4"/>
-      <c r="D933" s="6"/>
-    </row>
-    <row r="934" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="934" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A934" s="4">
         <v>933</v>
       </c>
       <c r="B934" s="2"/>
       <c r="C934" s="4"/>
-      <c r="D934" s="6"/>
-    </row>
-    <row r="935" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="935" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A935" s="4">
         <v>934</v>
       </c>
       <c r="B935" s="2"/>
       <c r="C935" s="4"/>
-      <c r="D935" s="6"/>
-    </row>
-    <row r="936" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="936" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A936" s="4">
         <v>935</v>
       </c>
       <c r="B936" s="2"/>
       <c r="C936" s="4"/>
-      <c r="D936" s="6"/>
-    </row>
-    <row r="937" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="937" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A937" s="4">
         <v>936</v>
       </c>
       <c r="B937" s="2"/>
       <c r="C937" s="4"/>
-      <c r="D937" s="6"/>
-    </row>
-    <row r="938" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="938" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A938" s="4">
         <v>937</v>
       </c>
       <c r="B938" s="2"/>
       <c r="C938" s="4"/>
-      <c r="D938" s="6"/>
-    </row>
-    <row r="939" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="939" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A939" s="4">
         <v>938</v>
       </c>
       <c r="B939" s="2"/>
       <c r="C939" s="4"/>
-      <c r="D939" s="6"/>
-    </row>
-    <row r="940" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="940" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A940" s="4">
         <v>939</v>
       </c>
       <c r="B940" s="2"/>
       <c r="C940" s="4"/>
-      <c r="D940" s="6"/>
-    </row>
-    <row r="941" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="941" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A941" s="4">
         <v>940</v>
       </c>
       <c r="B941" s="2"/>
       <c r="C941" s="4"/>
-      <c r="D941" s="6"/>
-    </row>
-    <row r="942" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="942" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A942" s="4">
         <v>941</v>
       </c>
       <c r="B942" s="2"/>
       <c r="C942" s="4"/>
-      <c r="D942" s="6"/>
-    </row>
-    <row r="943" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="943" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A943" s="4">
         <v>942</v>
       </c>
       <c r="B943" s="2"/>
       <c r="C943" s="4"/>
-      <c r="D943" s="6"/>
-    </row>
-    <row r="944" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="944" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A944" s="4">
         <v>943</v>
       </c>
       <c r="B944" s="2"/>
       <c r="C944" s="4"/>
-      <c r="D944" s="6"/>
-    </row>
-    <row r="945" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="945" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A945" s="4">
         <v>944</v>
       </c>
       <c r="B945" s="2"/>
       <c r="C945" s="4"/>
-      <c r="D945" s="6"/>
-    </row>
-    <row r="946" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="946" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A946" s="4">
         <v>945</v>
       </c>
       <c r="B946" s="2"/>
       <c r="C946" s="4"/>
-      <c r="D946" s="6"/>
-    </row>
-    <row r="947" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="947" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A947" s="4">
         <v>946</v>
       </c>
       <c r="B947" s="2"/>
       <c r="C947" s="4"/>
-      <c r="D947" s="6"/>
-    </row>
-    <row r="948" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="948" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A948" s="4">
         <v>947</v>
       </c>
       <c r="B948" s="2"/>
       <c r="C948" s="4"/>
-      <c r="D948" s="6"/>
-    </row>
-    <row r="949" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="949" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A949" s="4">
         <v>948</v>
       </c>
       <c r="B949" s="2"/>
       <c r="C949" s="4"/>
-      <c r="D949" s="6"/>
-    </row>
-    <row r="950" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="950" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A950" s="4">
         <v>949</v>
       </c>
       <c r="B950" s="2"/>
       <c r="C950" s="4"/>
-      <c r="D950" s="6"/>
-    </row>
-    <row r="951" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="951" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A951" s="4">
         <v>950</v>
       </c>
       <c r="B951" s="2"/>
       <c r="C951" s="4"/>
-      <c r="D951" s="6"/>
-    </row>
-    <row r="952" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="952" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A952" s="4">
         <v>951</v>
       </c>
       <c r="B952" s="2"/>
       <c r="C952" s="4"/>
-      <c r="D952" s="6"/>
-    </row>
-    <row r="953" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="953" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A953" s="4">
         <v>952</v>
       </c>
       <c r="B953" s="2"/>
       <c r="C953" s="4"/>
-      <c r="D953" s="6"/>
-    </row>
-    <row r="954" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="954" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A954" s="4">
         <v>953</v>
       </c>
       <c r="B954" s="2"/>
       <c r="C954" s="4"/>
-      <c r="D954" s="6"/>
-    </row>
-    <row r="955" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="955" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A955" s="4">
         <v>954</v>
       </c>
       <c r="B955" s="2"/>
       <c r="C955" s="4"/>
-      <c r="D955" s="6"/>
-    </row>
-    <row r="956" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="956" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A956" s="4">
         <v>955</v>
       </c>
       <c r="B956" s="2"/>
       <c r="C956" s="4"/>
-      <c r="D956" s="6"/>
-    </row>
-    <row r="957" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="957" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A957" s="4">
         <v>956</v>
       </c>
       <c r="B957" s="2"/>
       <c r="C957" s="4"/>
-      <c r="D957" s="6"/>
-    </row>
-    <row r="958" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="958" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A958" s="4">
         <v>957</v>
       </c>
       <c r="B958" s="2"/>
       <c r="C958" s="4"/>
-      <c r="D958" s="6"/>
-    </row>
-    <row r="959" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="959" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A959" s="4">
         <v>958</v>
       </c>
       <c r="B959" s="2"/>
       <c r="C959" s="4"/>
-      <c r="D959" s="6"/>
-    </row>
-    <row r="960" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="960" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A960" s="4">
         <v>959</v>
       </c>
       <c r="B960" s="2"/>
       <c r="C960" s="4"/>
-      <c r="D960" s="6"/>
-    </row>
-    <row r="961" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="961" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A961" s="4">
         <v>960</v>
       </c>
       <c r="B961" s="2"/>
       <c r="C961" s="4"/>
-      <c r="D961" s="6"/>
-    </row>
-    <row r="962" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="962" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A962" s="4">
         <v>961</v>
       </c>
       <c r="B962" s="2"/>
       <c r="C962" s="4"/>
-      <c r="D962" s="6"/>
-    </row>
-    <row r="963" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="963" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A963" s="4">
         <v>962</v>
       </c>
       <c r="B963" s="2"/>
       <c r="C963" s="4"/>
-      <c r="D963" s="6"/>
-    </row>
-    <row r="964" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="964" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A964" s="4">
         <v>963</v>
       </c>
       <c r="B964" s="2"/>
       <c r="C964" s="4"/>
-      <c r="D964" s="6"/>
-    </row>
-    <row r="965" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="965" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A965" s="4">
         <v>964</v>
       </c>
       <c r="B965" s="2"/>
       <c r="C965" s="4"/>
-      <c r="D965" s="6"/>
-    </row>
-    <row r="966" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="966" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A966" s="4">
         <v>965</v>
       </c>
       <c r="B966" s="2"/>
       <c r="C966" s="4"/>
-      <c r="D966" s="6"/>
-    </row>
-    <row r="967" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="967" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A967" s="4">
         <v>966</v>
       </c>
       <c r="B967" s="2"/>
       <c r="C967" s="4"/>
-      <c r="D967" s="6"/>
-    </row>
-    <row r="968" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="968" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A968" s="4">
         <v>967</v>
       </c>
       <c r="B968" s="2"/>
       <c r="C968" s="4"/>
-      <c r="D968" s="6"/>
-    </row>
-    <row r="969" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="969" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A969" s="4">
         <v>968</v>
       </c>
       <c r="B969" s="2"/>
       <c r="C969" s="4"/>
-      <c r="D969" s="6"/>
-    </row>
-    <row r="970" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="970" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A970" s="4">
         <v>969</v>
       </c>
       <c r="B970" s="2"/>
       <c r="C970" s="4"/>
-      <c r="D970" s="6"/>
-    </row>
-    <row r="971" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="971" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A971" s="4">
         <v>970</v>
       </c>
       <c r="B971" s="2"/>
       <c r="C971" s="4"/>
-      <c r="D971" s="6"/>
-    </row>
-    <row r="972" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="972" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A972" s="4">
         <v>971</v>
       </c>
       <c r="B972" s="2"/>
       <c r="C972" s="4"/>
-      <c r="D972" s="6"/>
-    </row>
-    <row r="973" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="973" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A973" s="4">
         <v>972</v>
       </c>
       <c r="B973" s="2"/>
       <c r="C973" s="4"/>
-      <c r="D973" s="6"/>
-    </row>
-    <row r="974" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="974" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A974" s="4">
         <v>973</v>
       </c>
       <c r="B974" s="2"/>
       <c r="C974" s="4"/>
-      <c r="D974" s="6"/>
-    </row>
-    <row r="975" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="975" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A975" s="4">
         <v>974</v>
       </c>
       <c r="B975" s="2"/>
       <c r="C975" s="4"/>
-      <c r="D975" s="6"/>
-    </row>
-    <row r="976" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="976" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A976" s="4">
         <v>975</v>
       </c>
       <c r="B976" s="2"/>
       <c r="C976" s="4"/>
-      <c r="D976" s="6"/>
-    </row>
-    <row r="977" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="977" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A977" s="4">
         <v>976</v>
       </c>
       <c r="B977" s="2"/>
       <c r="C977" s="4"/>
-      <c r="D977" s="6"/>
-    </row>
-    <row r="978" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="978" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A978" s="4">
         <v>977</v>
       </c>
       <c r="B978" s="2"/>
       <c r="C978" s="4"/>
-      <c r="D978" s="6"/>
-    </row>
-    <row r="979" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="979" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A979" s="4">
         <v>978</v>
       </c>
       <c r="B979" s="2"/>
       <c r="C979" s="4"/>
-      <c r="D979" s="6"/>
-    </row>
-    <row r="980" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="980" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A980" s="4">
         <v>979</v>
       </c>
       <c r="B980" s="2"/>
       <c r="C980" s="4"/>
-      <c r="D980" s="6"/>
-    </row>
-    <row r="981" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="981" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A981" s="4">
         <v>980</v>
       </c>
       <c r="B981" s="2"/>
       <c r="C981" s="4"/>
-      <c r="D981" s="6"/>
-    </row>
-    <row r="982" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="982" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A982" s="4">
         <v>981</v>
       </c>
       <c r="B982" s="2"/>
       <c r="C982" s="4"/>
-      <c r="D982" s="6"/>
-    </row>
-    <row r="983" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="983" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A983" s="4">
         <v>982</v>
       </c>
       <c r="B983" s="2"/>
       <c r="C983" s="4"/>
-      <c r="D983" s="6"/>
-    </row>
-    <row r="984" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="984" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A984" s="4">
         <v>983</v>
       </c>
       <c r="B984" s="2"/>
       <c r="C984" s="4"/>
-      <c r="D984" s="6"/>
-    </row>
-    <row r="985" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="985" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A985" s="4">
         <v>984</v>
       </c>
       <c r="B985" s="2"/>
       <c r="C985" s="4"/>
-      <c r="D985" s="6"/>
-    </row>
-    <row r="986" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="986" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A986" s="4">
         <v>985</v>
       </c>
       <c r="B986" s="2"/>
       <c r="C986" s="4"/>
-      <c r="D986" s="6"/>
-    </row>
-    <row r="987" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="987" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A987" s="4">
         <v>986</v>
       </c>
       <c r="B987" s="2"/>
       <c r="C987" s="4"/>
-      <c r="D987" s="6"/>
-    </row>
-    <row r="988" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="988" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A988" s="4">
         <v>987</v>
       </c>
       <c r="B988" s="2"/>
       <c r="C988" s="4"/>
-      <c r="D988" s="6"/>
-    </row>
-    <row r="989" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="989" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A989" s="4">
         <v>988</v>
       </c>
       <c r="B989" s="2"/>
       <c r="C989" s="4"/>
-      <c r="D989" s="6"/>
-    </row>
-    <row r="990" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="990" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A990" s="4">
         <v>989</v>
       </c>
       <c r="B990" s="2"/>
       <c r="C990" s="4"/>
-      <c r="D990" s="6"/>
-    </row>
-    <row r="991" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="991" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A991" s="4">
         <v>990</v>
       </c>
       <c r="B991" s="2"/>
       <c r="C991" s="4"/>
-      <c r="D991" s="6"/>
-    </row>
-    <row r="992" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="992" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A992" s="4">
         <v>991</v>
       </c>
       <c r="B992" s="2"/>
       <c r="C992" s="4"/>
-      <c r="D992" s="6"/>
-    </row>
-    <row r="993" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="993" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A993" s="4">
         <v>992</v>
       </c>
       <c r="B993" s="2"/>
       <c r="C993" s="4"/>
-      <c r="D993" s="6"/>
-    </row>
-    <row r="994" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="994" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A994" s="4">
         <v>993</v>
       </c>
       <c r="B994" s="2"/>
       <c r="C994" s="4"/>
-      <c r="D994" s="6"/>
-    </row>
-    <row r="995" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="995" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A995" s="4">
         <v>994</v>
       </c>
       <c r="B995" s="2"/>
       <c r="C995" s="4"/>
-      <c r="D995" s="6"/>
-    </row>
-    <row r="996" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="996" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A996" s="4">
         <v>995</v>
       </c>
       <c r="B996" s="2"/>
       <c r="C996" s="4"/>
-      <c r="D996" s="6"/>
-    </row>
-    <row r="997" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="997" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A997" s="4">
         <v>996</v>
       </c>
       <c r="B997" s="2"/>
       <c r="C997" s="4"/>
-      <c r="D997" s="6"/>
-    </row>
-    <row r="998" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="998" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A998" s="4">
         <v>997</v>
       </c>
       <c r="B998" s="2"/>
       <c r="C998" s="4"/>
-      <c r="D998" s="6"/>
-    </row>
-    <row r="999" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="999" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A999" s="4">
         <v>998</v>
       </c>
       <c r="B999" s="2"/>
       <c r="C999" s="4"/>
-      <c r="D999" s="6"/>
-    </row>
-    <row r="1000" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1000" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1000" s="4">
         <v>999</v>
       </c>
       <c r="B1000" s="2"/>
       <c r="C1000" s="4"/>
-      <c r="D1000" s="6"/>
-    </row>
-    <row r="1001" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1001" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1001" s="4">
         <v>1000</v>
       </c>
       <c r="B1001" s="2"/>
       <c r="C1001" s="4"/>
-      <c r="D1001" s="6"/>
-    </row>
-    <row r="1002" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1002" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1002" s="4">
         <v>1001</v>
       </c>
       <c r="B1002" s="2"/>
       <c r="C1002" s="4"/>
-      <c r="D1002" s="6"/>
-    </row>
-    <row r="1003" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1003" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1003" s="4">
         <v>1002</v>
       </c>
       <c r="B1003" s="2"/>
       <c r="C1003" s="4"/>
-      <c r="D1003" s="6"/>
-    </row>
-    <row r="1004" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1004" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1004" s="4">
         <v>1003</v>
       </c>
       <c r="B1004" s="2"/>
       <c r="C1004" s="4"/>
-      <c r="D1004" s="6"/>
-    </row>
-    <row r="1005" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1005" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1005" s="4">
         <v>1004</v>
       </c>
       <c r="B1005" s="2"/>
       <c r="C1005" s="4"/>
-      <c r="D1005" s="6"/>
-    </row>
-    <row r="1006" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1006" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1006" s="4">
         <v>1005</v>
       </c>
       <c r="B1006" s="2"/>
       <c r="C1006" s="4"/>
-      <c r="D1006" s="6"/>
-    </row>
-    <row r="1007" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1007" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1007" s="4">
         <v>1006</v>
       </c>
       <c r="B1007" s="2"/>
       <c r="C1007" s="4"/>
-      <c r="D1007" s="6"/>
-    </row>
-    <row r="1008" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1008" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1008" s="4">
         <v>1007</v>
       </c>
       <c r="B1008" s="2"/>
       <c r="C1008" s="4"/>
-      <c r="D1008" s="6"/>
-    </row>
-    <row r="1009" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1009" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1009" s="4">
         <v>1008</v>
       </c>
       <c r="B1009" s="2"/>
       <c r="C1009" s="4"/>
-      <c r="D1009" s="6"/>
-    </row>
-    <row r="1010" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1010" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1010" s="4">
         <v>1009</v>
       </c>
       <c r="B1010" s="2"/>
       <c r="C1010" s="4"/>
-      <c r="D1010" s="6"/>
-    </row>
-    <row r="1011" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1011" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1011" s="4">
         <v>1010</v>
       </c>
       <c r="B1011" s="2"/>
       <c r="C1011" s="4"/>
-      <c r="D1011" s="6"/>
-    </row>
-    <row r="1012" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1012" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1012" s="4">
         <v>1011</v>
       </c>
       <c r="B1012" s="2"/>
       <c r="C1012" s="4"/>
-      <c r="D1012" s="6"/>
-    </row>
-    <row r="1013" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1013" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1013" s="4">
         <v>1012</v>
       </c>
       <c r="B1013" s="2"/>
       <c r="C1013" s="4"/>
-      <c r="D1013" s="6"/>
-    </row>
-    <row r="1014" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1014" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1014" s="4">
         <v>1013</v>
       </c>
       <c r="B1014" s="2"/>
       <c r="C1014" s="4"/>
-      <c r="D1014" s="6"/>
-    </row>
-    <row r="1015" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1015" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1015" s="4">
         <v>1014</v>
       </c>
       <c r="B1015" s="2"/>
       <c r="C1015" s="4"/>
-      <c r="D1015" s="6"/>
-    </row>
-    <row r="1016" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1016" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1016" s="4">
         <v>1015</v>
       </c>
       <c r="B1016" s="2"/>
       <c r="C1016" s="4"/>
-      <c r="D1016" s="6"/>
-    </row>
-    <row r="1017" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1017" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1017" s="4">
         <v>1016</v>
       </c>
       <c r="B1017" s="2"/>
       <c r="C1017" s="4"/>
-      <c r="D1017" s="6"/>
-    </row>
-    <row r="1018" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1018" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1018" s="4">
         <v>1017</v>
       </c>
       <c r="B1018" s="2"/>
       <c r="C1018" s="4"/>
-      <c r="D1018" s="6"/>
-    </row>
-    <row r="1019" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1019" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1019" s="4">
         <v>1018</v>
       </c>
       <c r="B1019" s="2"/>
       <c r="C1019" s="4"/>
-      <c r="D1019" s="6"/>
-    </row>
-    <row r="1020" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1020" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1020" s="4">
         <v>1019</v>
       </c>
       <c r="B1020" s="2"/>
       <c r="C1020" s="4"/>
-      <c r="D1020" s="6"/>
-    </row>
-    <row r="1021" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1021" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1021" s="4">
         <v>1020</v>
       </c>
       <c r="B1021" s="2"/>
       <c r="C1021" s="4"/>
-      <c r="D1021" s="6"/>
-    </row>
-    <row r="1022" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1022" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1022" s="4">
         <v>1021</v>
       </c>
       <c r="B1022" s="2"/>
       <c r="C1022" s="4"/>
-      <c r="D1022" s="6"/>
-    </row>
-    <row r="1023" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1023" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1023" s="4">
         <v>1022</v>
       </c>
       <c r="B1023" s="2"/>
       <c r="C1023" s="4"/>
-      <c r="D1023" s="6"/>
-    </row>
-    <row r="1024" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1024" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1024" s="4">
         <v>1023</v>
       </c>
       <c r="B1024" s="2"/>
       <c r="C1024" s="4"/>
-      <c r="D1024" s="6"/>
-    </row>
-    <row r="1025" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1025" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1025" s="4">
         <v>1024</v>
       </c>
       <c r="B1025" s="2"/>
       <c r="C1025" s="4"/>
-      <c r="D1025" s="6"/>
-    </row>
-    <row r="1026" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1026" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1026" s="4">
         <v>1025</v>
       </c>
       <c r="B1026" s="2"/>
       <c r="C1026" s="4"/>
-      <c r="D1026" s="6"/>
-    </row>
-    <row r="1027" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1027" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1027" s="4">
         <v>1026</v>
       </c>
       <c r="B1027" s="2"/>
       <c r="C1027" s="4"/>
-      <c r="D1027" s="6"/>
-    </row>
-    <row r="1028" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1028" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1028" s="4">
         <v>1027</v>
       </c>
       <c r="B1028" s="2"/>
       <c r="C1028" s="4"/>
-      <c r="D1028" s="6"/>
-    </row>
-    <row r="1029" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1029" s="4">
         <v>1028</v>
       </c>
       <c r="B1029" s="2"/>
       <c r="C1029" s="4"/>
-      <c r="D1029" s="6"/>
-    </row>
-    <row r="1030" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1030" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1030" s="4">
         <v>1029</v>
       </c>
       <c r="B1030" s="2"/>
       <c r="C1030" s="4"/>
-      <c r="D1030" s="6"/>
-    </row>
-    <row r="1031" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1031" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1031" s="4">
         <v>1030</v>
       </c>
       <c r="B1031" s="2"/>
       <c r="C1031" s="4"/>
-      <c r="D1031" s="6"/>
-    </row>
-    <row r="1032" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1032" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1032" s="4">
         <v>1031</v>
       </c>
       <c r="B1032" s="2"/>
       <c r="C1032" s="4"/>
-      <c r="D1032" s="6"/>
-    </row>
-    <row r="1033" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1033" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1033" s="4">
         <v>1032</v>
       </c>
       <c r="B1033" s="2"/>
       <c r="C1033" s="4"/>
-      <c r="D1033" s="6"/>
-    </row>
-    <row r="1034" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1034" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1034" s="4">
         <v>1033</v>
       </c>
       <c r="B1034" s="2"/>
       <c r="C1034" s="4"/>
-      <c r="D1034" s="6"/>
-    </row>
-    <row r="1035" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1035" s="4">
         <v>1034</v>
       </c>
       <c r="B1035" s="2"/>
       <c r="C1035" s="4"/>
-      <c r="D1035" s="6"/>
-    </row>
-    <row r="1036" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1036" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1036" s="4">
         <v>1035</v>
       </c>
       <c r="B1036" s="2"/>
       <c r="C1036" s="4"/>
-      <c r="D1036" s="6"/>
-    </row>
-    <row r="1037" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1037" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1037" s="4">
         <v>1036</v>
       </c>
       <c r="B1037" s="2"/>
       <c r="C1037" s="4"/>
-      <c r="D1037" s="6"/>
-    </row>
-    <row r="1038" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1038" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1038" s="4">
         <v>1037</v>
       </c>
       <c r="B1038" s="2"/>
       <c r="C1038" s="4"/>
-      <c r="D1038" s="6"/>
-    </row>
-    <row r="1039" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1039" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1039" s="4">
         <v>1038</v>
       </c>
       <c r="B1039" s="2"/>
       <c r="C1039" s="4"/>
-      <c r="D1039" s="6"/>
-    </row>
-    <row r="1040" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1040" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1040" s="4">
         <v>1039</v>
       </c>
       <c r="B1040" s="2"/>
       <c r="C1040" s="4"/>
-      <c r="D1040" s="6"/>
-    </row>
-    <row r="1041" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1041" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1041" s="4">
         <v>1040</v>
       </c>
       <c r="B1041" s="2"/>
       <c r="C1041" s="4"/>
-      <c r="D1041" s="6"/>
-    </row>
-    <row r="1042" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1042" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1042" s="4">
         <v>1041</v>
       </c>
       <c r="B1042" s="2"/>
       <c r="C1042" s="4"/>
-      <c r="D1042" s="6"/>
-    </row>
-    <row r="1043" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1043" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1043" s="4">
         <v>1042</v>
       </c>
       <c r="B1043" s="2"/>
       <c r="C1043" s="4"/>
-      <c r="D1043" s="6"/>
-    </row>
-    <row r="1044" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1044" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1044" s="4">
         <v>1043</v>
       </c>
       <c r="B1044" s="2"/>
       <c r="C1044" s="4"/>
-      <c r="D1044" s="6"/>
-    </row>
-    <row r="1045" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1045" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1045" s="4">
         <v>1044</v>
       </c>
       <c r="B1045" s="2"/>
       <c r="C1045" s="4"/>
-      <c r="D1045" s="6"/>
-    </row>
-    <row r="1046" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1046" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1046" s="4">
         <v>1045</v>
       </c>
       <c r="B1046" s="2"/>
       <c r="C1046" s="4"/>
-      <c r="D1046" s="6"/>
-    </row>
-    <row r="1047" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1047" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1047" s="4">
         <v>1046</v>
       </c>
       <c r="B1047" s="2"/>
       <c r="C1047" s="4"/>
-      <c r="D1047" s="6"/>
-    </row>
-    <row r="1048" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1048" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1048" s="4">
         <v>1047</v>
       </c>
       <c r="B1048" s="2"/>
       <c r="C1048" s="4"/>
-      <c r="D1048" s="6"/>
-    </row>
-    <row r="1049" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1049" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1049" s="4">
         <v>1048</v>
       </c>
       <c r="B1049" s="2"/>
       <c r="C1049" s="4"/>
-      <c r="D1049" s="6"/>
-    </row>
-    <row r="1050" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1050" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1050" s="4">
         <v>1049</v>
       </c>
       <c r="B1050" s="2"/>
       <c r="C1050" s="4"/>
-      <c r="D1050" s="6"/>
-    </row>
-    <row r="1051" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1051" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1051" s="4">
         <v>1050</v>
       </c>
       <c r="B1051" s="2"/>
       <c r="C1051" s="4"/>
-      <c r="D1051" s="6"/>
-    </row>
-    <row r="1052" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1052" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1052" s="4">
         <v>1051</v>
       </c>
       <c r="B1052" s="2"/>
       <c r="C1052" s="4"/>
-      <c r="D1052" s="6"/>
-    </row>
-    <row r="1053" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1053" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1053" s="4">
         <v>1052</v>
       </c>
       <c r="B1053" s="2"/>
       <c r="C1053" s="4"/>
-      <c r="D1053" s="6"/>
-    </row>
-    <row r="1054" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1054" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1054" s="4">
         <v>1053</v>
       </c>
       <c r="B1054" s="2"/>
       <c r="C1054" s="4"/>
-      <c r="D1054" s="6"/>
-    </row>
-    <row r="1055" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1055" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1055" s="4">
         <v>1054</v>
       </c>
       <c r="B1055" s="2"/>
       <c r="C1055" s="4"/>
-      <c r="D1055" s="6"/>
-    </row>
-    <row r="1056" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1056" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1056" s="4">
         <v>1055</v>
       </c>
       <c r="B1056" s="2"/>
       <c r="C1056" s="4"/>
-      <c r="D1056" s="6"/>
-    </row>
-    <row r="1057" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1057" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1057" s="4">
         <v>1056</v>
       </c>
       <c r="B1057" s="2"/>
       <c r="C1057" s="4"/>
-      <c r="D1057" s="6"/>
-    </row>
-    <row r="1058" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1058" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1058" s="4">
         <v>1057</v>
       </c>
       <c r="B1058" s="2"/>
       <c r="C1058" s="4"/>
-      <c r="D1058" s="6"/>
-    </row>
-    <row r="1059" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1059" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1059" s="4">
         <v>1058</v>
       </c>
       <c r="B1059" s="2"/>
       <c r="C1059" s="4"/>
-      <c r="D1059" s="6"/>
-    </row>
-    <row r="1060" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1060" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1060" s="4">
         <v>1059</v>
       </c>
       <c r="B1060" s="2"/>
       <c r="C1060" s="4"/>
-      <c r="D1060" s="6"/>
-    </row>
-    <row r="1061" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1061" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1061" s="4">
         <v>1060</v>
       </c>
       <c r="B1061" s="2"/>
       <c r="C1061" s="4"/>
-      <c r="D1061" s="6"/>
-    </row>
-    <row r="1062" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1062" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1062" s="4">
         <v>1061</v>
       </c>
       <c r="B1062" s="2"/>
       <c r="C1062" s="4"/>
-      <c r="D1062" s="6"/>
-    </row>
-    <row r="1063" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1063" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1063" s="4">
         <v>1062</v>
       </c>
       <c r="B1063" s="2"/>
       <c r="C1063" s="4"/>
-      <c r="D1063" s="6"/>
-    </row>
-    <row r="1064" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1064" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1064" s="4">
         <v>1063</v>
       </c>
       <c r="B1064" s="2"/>
       <c r="C1064" s="4"/>
-      <c r="D1064" s="6"/>
-    </row>
-    <row r="1065" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1065" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1065" s="4">
         <v>1064</v>
       </c>
       <c r="B1065" s="2"/>
       <c r="C1065" s="4"/>
-      <c r="D1065" s="6"/>
-    </row>
-    <row r="1066" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1066" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1066" s="4">
         <v>1065</v>
       </c>
       <c r="B1066" s="2"/>
       <c r="C1066" s="4"/>
-      <c r="D1066" s="6"/>
-    </row>
-    <row r="1067" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1067" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1067" s="4">
         <v>1066</v>
       </c>
       <c r="B1067" s="2"/>
       <c r="C1067" s="4"/>
-      <c r="D1067" s="6"/>
-    </row>
-    <row r="1068" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1068" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1068" s="4">
         <v>1067</v>
       </c>
       <c r="B1068" s="2"/>
       <c r="C1068" s="4"/>
-      <c r="D1068" s="6"/>
-    </row>
-    <row r="1069" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1069" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1069" s="4">
         <v>1068</v>
       </c>
       <c r="B1069" s="2"/>
       <c r="C1069" s="4"/>
-      <c r="D1069" s="6"/>
-    </row>
-    <row r="1070" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1070" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1070" s="4">
         <v>1069</v>
       </c>
       <c r="B1070" s="2"/>
       <c r="C1070" s="4"/>
-      <c r="D1070" s="6"/>
-    </row>
-    <row r="1071" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1071" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1071" s="4">
         <v>1070</v>
       </c>
       <c r="B1071" s="2"/>
       <c r="C1071" s="4"/>
-      <c r="D1071" s="6"/>
-    </row>
-    <row r="1072" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1072" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1072" s="4">
         <v>1071</v>
       </c>
       <c r="B1072" s="2"/>
       <c r="C1072" s="4"/>
-      <c r="D1072" s="6"/>
-    </row>
-    <row r="1073" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1073" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1073" s="4">
         <v>1072</v>
       </c>
       <c r="B1073" s="2"/>
       <c r="C1073" s="4"/>
-      <c r="D1073" s="6"/>
-    </row>
-    <row r="1074" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1074" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1074" s="4">
         <v>1073</v>
       </c>
       <c r="B1074" s="2"/>
       <c r="C1074" s="4"/>
-      <c r="D1074" s="6"/>
-    </row>
-    <row r="1075" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1075" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1075" s="4">
         <v>1074</v>
       </c>
       <c r="B1075" s="2"/>
       <c r="C1075" s="4"/>
-      <c r="D1075" s="6"/>
-    </row>
-    <row r="1076" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1076" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1076" s="4">
         <v>1075</v>
       </c>
       <c r="B1076" s="2"/>
       <c r="C1076" s="4"/>
-      <c r="D1076" s="6"/>
-    </row>
-    <row r="1077" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1077" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1077" s="4">
         <v>1076</v>
       </c>
       <c r="B1077" s="2"/>
       <c r="C1077" s="4"/>
-      <c r="D1077" s="6"/>
-    </row>
-    <row r="1078" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1078" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1078" s="4">
         <v>1077</v>
       </c>
       <c r="B1078" s="2"/>
       <c r="C1078" s="4"/>
-      <c r="D1078" s="6"/>
-    </row>
-    <row r="1079" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1079" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1079" s="4">
         <v>1078</v>
       </c>
       <c r="B1079" s="2"/>
       <c r="C1079" s="4"/>
-      <c r="D1079" s="6"/>
-    </row>
-    <row r="1080" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1080" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1080" s="4">
         <v>1079</v>
       </c>
       <c r="B1080" s="2"/>
       <c r="C1080" s="4"/>
-      <c r="D1080" s="6"/>
-    </row>
-    <row r="1081" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1081" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1081" s="4">
         <v>1080</v>
       </c>
       <c r="B1081" s="2"/>
       <c r="C1081" s="4"/>
-      <c r="D1081" s="6"/>
-    </row>
-    <row r="1082" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1082" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1082" s="4">
         <v>1081</v>
       </c>
       <c r="B1082" s="2"/>
       <c r="C1082" s="4"/>
-      <c r="D1082" s="6"/>
-    </row>
-    <row r="1083" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1083" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1083" s="4">
         <v>1082</v>
       </c>
       <c r="B1083" s="2"/>
       <c r="C1083" s="4"/>
-      <c r="D1083" s="6"/>
-    </row>
-    <row r="1084" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1084" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1084" s="4">
         <v>1083</v>
       </c>
       <c r="B1084" s="2"/>
       <c r="C1084" s="4"/>
-      <c r="D1084" s="6"/>
-    </row>
-    <row r="1085" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1085" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1085" s="4">
         <v>1084</v>
       </c>
       <c r="B1085" s="2"/>
       <c r="C1085" s="4"/>
-      <c r="D1085" s="6"/>
-    </row>
-    <row r="1086" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1086" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1086" s="4">
         <v>1085</v>
       </c>
       <c r="B1086" s="2"/>
       <c r="C1086" s="4"/>
-      <c r="D1086" s="6"/>
-    </row>
-    <row r="1087" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1087" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1087" s="4">
         <v>1086</v>
       </c>
       <c r="B1087" s="2"/>
       <c r="C1087" s="4"/>
-      <c r="D1087" s="6"/>
-    </row>
-    <row r="1088" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1088" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1088" s="4">
         <v>1087</v>
       </c>
       <c r="B1088" s="2"/>
       <c r="C1088" s="4"/>
-      <c r="D1088" s="6"/>
-    </row>
-    <row r="1089" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1089" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1089" s="4">
         <v>1088</v>
       </c>
       <c r="B1089" s="2"/>
       <c r="C1089" s="4"/>
-      <c r="D1089" s="6"/>
-    </row>
-    <row r="1090" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1090" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1090" s="4">
         <v>1089</v>
       </c>
       <c r="B1090" s="2"/>
       <c r="C1090" s="4"/>
-      <c r="D1090" s="6"/>
-    </row>
-    <row r="1091" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1091" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1091" s="4">
         <v>1090</v>
       </c>
       <c r="B1091" s="2"/>
       <c r="C1091" s="4"/>
-      <c r="D1091" s="6"/>
-    </row>
-    <row r="1092" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1092" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1092" s="4">
         <v>1091</v>
       </c>
       <c r="B1092" s="2"/>
       <c r="C1092" s="4"/>
-      <c r="D1092" s="6"/>
-    </row>
-    <row r="1093" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1093" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1093" s="4">
         <v>1092</v>
       </c>
       <c r="B1093" s="2"/>
       <c r="C1093" s="4"/>
-      <c r="D1093" s="6"/>
-    </row>
-    <row r="1094" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1094" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1094" s="4">
         <v>1093</v>
       </c>
       <c r="B1094" s="2"/>
       <c r="C1094" s="4"/>
-      <c r="D1094" s="6"/>
-    </row>
-    <row r="1095" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1095" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1095" s="4">
         <v>1094</v>
       </c>
       <c r="B1095" s="2"/>
       <c r="C1095" s="4"/>
-      <c r="D1095" s="6"/>
-    </row>
-    <row r="1096" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1096" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1096" s="4">
         <v>1095</v>
       </c>
       <c r="B1096" s="2"/>
       <c r="C1096" s="4"/>
-      <c r="D1096" s="6"/>
-    </row>
-    <row r="1097" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1097" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1097" s="4">
         <v>1096</v>
       </c>
       <c r="B1097" s="2"/>
       <c r="C1097" s="4"/>
-      <c r="D1097" s="6"/>
-    </row>
-    <row r="1098" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1098" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1098" s="4">
         <v>1097</v>
       </c>
       <c r="B1098" s="2"/>
       <c r="C1098" s="4"/>
-      <c r="D1098" s="6"/>
-    </row>
-    <row r="1099" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1099" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1099" s="4">
         <v>1098</v>
       </c>
       <c r="B1099" s="2"/>
       <c r="C1099" s="4"/>
-      <c r="D1099" s="6"/>
-    </row>
-    <row r="1100" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1100" s="4">
         <v>1099</v>
       </c>
       <c r="B1100" s="2"/>
       <c r="C1100" s="4"/>
-      <c r="D1100" s="6"/>
-    </row>
-    <row r="1101" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1101" s="4">
         <v>1100</v>
       </c>
       <c r="B1101" s="2"/>
       <c r="C1101" s="4"/>
-      <c r="D1101" s="6"/>
-    </row>
-    <row r="1102" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1102" s="4">
         <v>1101</v>
       </c>
       <c r="B1102" s="2"/>
       <c r="C1102" s="4"/>
-      <c r="D1102" s="6"/>
-    </row>
-    <row r="1103" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1103" s="4">
         <v>1102</v>
       </c>
       <c r="B1103" s="2"/>
       <c r="C1103" s="4"/>
-      <c r="D1103" s="6"/>
-    </row>
-    <row r="1104" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1104" s="4">
         <v>1103</v>
       </c>
       <c r="B1104" s="2"/>
       <c r="C1104" s="4"/>
-      <c r="D1104" s="6"/>
-    </row>
-    <row r="1105" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1105" s="4">
         <v>1104</v>
       </c>
       <c r="B1105" s="2"/>
       <c r="C1105" s="4"/>
-      <c r="D1105" s="6"/>
-    </row>
-    <row r="1106" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1106" s="4">
         <v>1105</v>
       </c>
       <c r="B1106" s="2"/>
       <c r="C1106" s="4"/>
-      <c r="D1106" s="6"/>
-    </row>
-    <row r="1107" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1107" s="4">
         <v>1106</v>
       </c>
       <c r="B1107" s="2"/>
       <c r="C1107" s="4"/>
-      <c r="D1107" s="6"/>
-    </row>
-    <row r="1108" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1108" s="4">
         <v>1107</v>
       </c>
       <c r="B1108" s="2"/>
       <c r="C1108" s="4"/>
-      <c r="D1108" s="6"/>
-    </row>
-    <row r="1109" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1109" s="4">
         <v>1108</v>
       </c>
       <c r="B1109" s="2"/>
       <c r="C1109" s="4"/>
-      <c r="D1109" s="6"/>
-    </row>
-    <row r="1110" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1110" s="4">
         <v>1109</v>
       </c>
       <c r="B1110" s="2"/>
       <c r="C1110" s="4"/>
-      <c r="D1110" s="6"/>
-    </row>
-    <row r="1111" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1111" s="4">
         <v>1110</v>
       </c>
       <c r="B1111" s="2"/>
       <c r="C1111" s="4"/>
-      <c r="D1111" s="6"/>
-    </row>
-    <row r="1112" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1112" s="4">
         <v>1111</v>
       </c>
       <c r="B1112" s="2"/>
       <c r="C1112" s="4"/>
-      <c r="D1112" s="6"/>
-    </row>
-    <row r="1113" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1113" s="4">
         <v>1112</v>
       </c>
       <c r="B1113" s="2"/>
       <c r="C1113" s="4"/>
-      <c r="D1113" s="6"/>
-    </row>
-    <row r="1114" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1114" s="4">
         <v>1113</v>
       </c>
       <c r="B1114" s="2"/>
       <c r="C1114" s="4"/>
-      <c r="D1114" s="6"/>
-    </row>
-    <row r="1115" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1115" s="4">
         <v>1114</v>
       </c>
       <c r="B1115" s="2"/>
       <c r="C1115" s="4"/>
-      <c r="D1115" s="6"/>
-    </row>
-    <row r="1116" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1116" s="4">
         <v>1115</v>
       </c>
       <c r="B1116" s="2"/>
       <c r="C1116" s="4"/>
-      <c r="D1116" s="6"/>
-    </row>
-    <row r="1117" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1117" s="4">
         <v>1116</v>
       </c>
       <c r="B1117" s="2"/>
       <c r="C1117" s="4"/>
-      <c r="D1117" s="6"/>
-    </row>
-    <row r="1118" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1118" s="4">
         <v>1117</v>
       </c>
       <c r="B1118" s="2"/>
       <c r="C1118" s="4"/>
-      <c r="D1118" s="6"/>
-    </row>
-    <row r="1119" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1119" s="4">
         <v>1118</v>
       </c>
       <c r="B1119" s="2"/>
       <c r="C1119" s="4"/>
-      <c r="D1119" s="6"/>
-    </row>
-    <row r="1120" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1120" s="4">
         <v>1119</v>
       </c>
       <c r="B1120" s="2"/>
       <c r="C1120" s="4"/>
-      <c r="D1120" s="6"/>
-    </row>
-    <row r="1121" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1121" s="4">
         <v>1120</v>
       </c>
       <c r="B1121" s="2"/>
       <c r="C1121" s="4"/>
-      <c r="D1121" s="6"/>
-    </row>
-    <row r="1122" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1122" s="4">
         <v>1121</v>
       </c>
       <c r="B1122" s="2"/>
       <c r="C1122" s="4"/>
-      <c r="D1122" s="6"/>
-    </row>
-    <row r="1123" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1123" s="4">
         <v>1122</v>
       </c>
       <c r="B1123" s="2"/>
       <c r="C1123" s="4"/>
-      <c r="D1123" s="6"/>
-    </row>
-    <row r="1124" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1124" s="4">
         <v>1123</v>
       </c>
       <c r="B1124" s="2"/>
       <c r="C1124" s="4"/>
-      <c r="D1124" s="6"/>
-    </row>
-    <row r="1125" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1125" s="4">
         <v>1124</v>
       </c>
       <c r="B1125" s="2"/>
       <c r="C1125" s="4"/>
-      <c r="D1125" s="6"/>
-    </row>
-    <row r="1126" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1126" s="4">
         <v>1125</v>
       </c>
       <c r="B1126" s="2"/>
       <c r="C1126" s="4"/>
-      <c r="D1126" s="6"/>
-    </row>
-    <row r="1127" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1127" s="4">
         <v>1126</v>
       </c>
       <c r="B1127" s="2"/>
       <c r="C1127" s="4"/>
-      <c r="D1127" s="6"/>
-    </row>
-    <row r="1128" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1128" s="4">
         <v>1127</v>
       </c>
       <c r="B1128" s="2"/>
       <c r="C1128" s="4"/>
-      <c r="D1128" s="6"/>
-    </row>
-    <row r="1129" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1129" s="4">
         <v>1128</v>
       </c>
       <c r="B1129" s="2"/>
       <c r="C1129" s="4"/>
-      <c r="D1129" s="6"/>
-    </row>
-    <row r="1130" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1130" s="4">
         <v>1129</v>
       </c>
       <c r="B1130" s="2"/>
       <c r="C1130" s="4"/>
-      <c r="D1130" s="6"/>
-    </row>
-    <row r="1131" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1131" s="4">
         <v>1130</v>
       </c>
       <c r="B1131" s="2"/>
       <c r="C1131" s="4"/>
-      <c r="D1131" s="6"/>
-    </row>
-    <row r="1132" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1132" s="4">
         <v>1131</v>
       </c>
       <c r="B1132" s="2"/>
       <c r="C1132" s="4"/>
-      <c r="D1132" s="6"/>
-    </row>
-    <row r="1133" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1133" s="4">
         <v>1132</v>
       </c>
       <c r="B1133" s="2"/>
       <c r="C1133" s="4"/>
-      <c r="D1133" s="6"/>
-    </row>
-    <row r="1134" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1134" s="4">
         <v>1133</v>
       </c>
       <c r="B1134" s="2"/>
       <c r="C1134" s="4"/>
-      <c r="D1134" s="6"/>
-    </row>
-    <row r="1135" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1135" s="4">
         <v>1134</v>
       </c>
       <c r="B1135" s="2"/>
       <c r="C1135" s="4"/>
-      <c r="D1135" s="6"/>
-    </row>
-    <row r="1136" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1136" s="4">
         <v>1135</v>
       </c>
       <c r="B1136" s="2"/>
       <c r="C1136" s="4"/>
-      <c r="D1136" s="6"/>
-    </row>
-    <row r="1137" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1137" s="4">
         <v>1136</v>
       </c>
       <c r="B1137" s="2"/>
       <c r="C1137" s="4"/>
-      <c r="D1137" s="6"/>
-    </row>
-    <row r="1138" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1138" s="4">
         <v>1137</v>
       </c>
       <c r="B1138" s="2"/>
       <c r="C1138" s="4"/>
-      <c r="D1138" s="6"/>
-    </row>
-    <row r="1139" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1139" s="4">
         <v>1138</v>
       </c>
       <c r="B1139" s="2"/>
       <c r="C1139" s="4"/>
-      <c r="D1139" s="6"/>
-    </row>
-    <row r="1140" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1140" s="4">
         <v>1139</v>
       </c>
       <c r="B1140" s="2"/>
       <c r="C1140" s="4"/>
-      <c r="D1140" s="6"/>
-    </row>
-    <row r="1141" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1141" s="4">
         <v>1140</v>
       </c>
       <c r="B1141" s="2"/>
       <c r="C1141" s="4"/>
-      <c r="D1141" s="6"/>
-    </row>
-    <row r="1142" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1142" s="4">
         <v>1141</v>
       </c>
       <c r="B1142" s="2"/>
       <c r="C1142" s="4"/>
-      <c r="D1142" s="6"/>
-    </row>
-    <row r="1143" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1143" s="4">
         <v>1142</v>
       </c>
       <c r="B1143" s="2"/>
       <c r="C1143" s="4"/>
-      <c r="D1143" s="6"/>
-    </row>
-    <row r="1144" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1144" s="4">
         <v>1143</v>
       </c>
       <c r="B1144" s="2"/>
       <c r="C1144" s="4"/>
-      <c r="D1144" s="6"/>
-    </row>
-    <row r="1145" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1145" s="4">
         <v>1144</v>
       </c>
       <c r="B1145" s="2"/>
       <c r="C1145" s="4"/>
-      <c r="D1145" s="6"/>
-    </row>
-    <row r="1146" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1146" s="4">
         <v>1145</v>
       </c>
       <c r="B1146" s="2"/>
       <c r="C1146" s="4"/>
-      <c r="D1146" s="6"/>
-    </row>
-    <row r="1147" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1147" s="4">
         <v>1146</v>
       </c>
       <c r="B1147" s="2"/>
       <c r="C1147" s="4"/>
-      <c r="D1147" s="6"/>
-    </row>
-    <row r="1148" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1148" s="4">
         <v>1147</v>
       </c>
       <c r="B1148" s="2"/>
       <c r="C1148" s="4"/>
-      <c r="D1148" s="6"/>
-    </row>
-    <row r="1149" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1149" s="4">
         <v>1148</v>
       </c>
       <c r="B1149" s="2"/>
       <c r="C1149" s="4"/>
-      <c r="D1149" s="6"/>
-    </row>
-    <row r="1150" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1150" s="4">
         <v>1149</v>
       </c>
       <c r="B1150" s="2"/>
       <c r="C1150" s="4"/>
-      <c r="D1150" s="6"/>
-    </row>
-    <row r="1151" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1151" s="4">
         <v>1150</v>
       </c>
       <c r="B1151" s="2"/>
       <c r="C1151" s="4"/>
-      <c r="D1151" s="6"/>
-    </row>
-    <row r="1152" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1152" s="4">
         <v>1151</v>
       </c>
       <c r="B1152" s="2"/>
       <c r="C1152" s="4"/>
-      <c r="D1152" s="6"/>
-    </row>
-    <row r="1153" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1153" s="4">
         <v>1152</v>
       </c>
       <c r="B1153" s="2"/>
       <c r="C1153" s="4"/>
-      <c r="D1153" s="6"/>
-    </row>
-    <row r="1154" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1154" s="4">
         <v>1153</v>
       </c>
       <c r="B1154" s="2"/>
       <c r="C1154" s="4"/>
-      <c r="D1154" s="6"/>
-    </row>
-    <row r="1155" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1155" s="4">
         <v>1154</v>
       </c>
       <c r="B1155" s="2"/>
       <c r="C1155" s="4"/>
-      <c r="D1155" s="6"/>
-    </row>
-    <row r="1156" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1156" s="4">
         <v>1155</v>
       </c>
       <c r="B1156" s="2"/>
       <c r="C1156" s="4"/>
-      <c r="D1156" s="6"/>
-    </row>
-    <row r="1157" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1157" s="4">
         <v>1156</v>
       </c>
       <c r="B1157" s="2"/>
       <c r="C1157" s="4"/>
-      <c r="D1157" s="6"/>
-    </row>
-    <row r="1158" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1158" s="4">
         <v>1157</v>
       </c>
       <c r="B1158" s="2"/>
       <c r="C1158" s="4"/>
-      <c r="D1158" s="6"/>
-    </row>
-    <row r="1159" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1159" s="4">
         <v>1158</v>
       </c>
       <c r="B1159" s="2"/>
       <c r="C1159" s="4"/>
-      <c r="D1159" s="6"/>
-    </row>
-    <row r="1160" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1160" s="4">
         <v>1159</v>
       </c>
       <c r="B1160" s="2"/>
       <c r="C1160" s="4"/>
-      <c r="D1160" s="6"/>
-    </row>
-    <row r="1161" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1161" s="4">
         <v>1160</v>
       </c>
       <c r="B1161" s="2"/>
       <c r="C1161" s="4"/>
-      <c r="D1161" s="6"/>
-    </row>
-    <row r="1162" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1162" s="4">
         <v>1161</v>
       </c>
       <c r="B1162" s="2"/>
       <c r="C1162" s="4"/>
-      <c r="D1162" s="6"/>
-    </row>
-    <row r="1163" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1163" s="4">
         <v>1162</v>
       </c>
       <c r="B1163" s="2"/>
       <c r="C1163" s="4"/>
-      <c r="D1163" s="6"/>
-    </row>
-    <row r="1164" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1164" s="4">
         <v>1163</v>
       </c>
       <c r="B1164" s="2"/>
       <c r="C1164" s="4"/>
-      <c r="D1164" s="6"/>
-    </row>
-    <row r="1165" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1165" s="4">
         <v>1164</v>
       </c>
       <c r="B1165" s="2"/>
       <c r="C1165" s="4"/>
-      <c r="D1165" s="6"/>
-    </row>
-    <row r="1166" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1166" s="4">
         <v>1165</v>
       </c>
       <c r="B1166" s="2"/>
       <c r="C1166" s="4"/>
-      <c r="D1166" s="6"/>
-    </row>
-    <row r="1167" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1167" s="4">
         <v>1166</v>
       </c>
       <c r="B1167" s="2"/>
       <c r="C1167" s="4"/>
-      <c r="D1167" s="6"/>
-    </row>
-    <row r="1168" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1168" s="4">
         <v>1167</v>
       </c>
       <c r="B1168" s="2"/>
       <c r="C1168" s="4"/>
-      <c r="D1168" s="6"/>
-    </row>
-    <row r="1169" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1169" s="4">
         <v>1168</v>
       </c>
       <c r="B1169" s="2"/>
       <c r="C1169" s="4"/>
-      <c r="D1169" s="6"/>
-    </row>
-    <row r="1170" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1170" s="4">
         <v>1169</v>
       </c>
       <c r="B1170" s="2"/>
       <c r="C1170" s="4"/>
-      <c r="D1170" s="6"/>
-    </row>
-    <row r="1171" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1171" s="4">
         <v>1170</v>
       </c>
       <c r="B1171" s="2"/>
       <c r="C1171" s="4"/>
-      <c r="D1171" s="6"/>
-    </row>
-    <row r="1172" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1172" s="4">
         <v>1171</v>
       </c>
       <c r="B1172" s="2"/>
       <c r="C1172" s="4"/>
-      <c r="D1172" s="6"/>
-    </row>
-    <row r="1173" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1173" s="4">
         <v>1172</v>
       </c>
       <c r="B1173" s="2"/>
       <c r="C1173" s="4"/>
-      <c r="D1173" s="6"/>
-    </row>
-    <row r="1174" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1174" s="4">
         <v>1173</v>
       </c>
       <c r="B1174" s="2"/>
       <c r="C1174" s="4"/>
-      <c r="D1174" s="6"/>
-    </row>
-    <row r="1175" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1175" s="4">
         <v>1174</v>
       </c>
       <c r="B1175" s="2"/>
       <c r="C1175" s="4"/>
-      <c r="D1175" s="6"/>
-    </row>
-    <row r="1176" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1176" s="4">
         <v>1175</v>
       </c>
       <c r="B1176" s="2"/>
       <c r="C1176" s="4"/>
-      <c r="D1176" s="6"/>
-    </row>
-    <row r="1177" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1177" s="4">
         <v>1176</v>
       </c>
       <c r="B1177" s="2"/>
       <c r="C1177" s="4"/>
-      <c r="D1177" s="6"/>
-    </row>
-    <row r="1178" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1178" s="4">
         <v>1177</v>
       </c>
       <c r="B1178" s="2"/>
       <c r="C1178" s="4"/>
-      <c r="D1178" s="6"/>
-    </row>
-    <row r="1179" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1179" s="4">
         <v>1178</v>
       </c>
       <c r="B1179" s="2"/>
       <c r="C1179" s="4"/>
-      <c r="D1179" s="6"/>
-    </row>
-    <row r="1180" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1180" s="4">
         <v>1179</v>
       </c>
       <c r="B1180" s="2"/>
       <c r="C1180" s="4"/>
-      <c r="D1180" s="6"/>
-    </row>
-    <row r="1181" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1181" s="4">
         <v>1180</v>
       </c>
       <c r="B1181" s="2"/>
       <c r="C1181" s="4"/>
-      <c r="D1181" s="6"/>
-    </row>
-    <row r="1182" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1182" s="4">
         <v>1181</v>
       </c>
       <c r="B1182" s="2"/>
       <c r="C1182" s="4"/>
-      <c r="D1182" s="6"/>
-    </row>
-    <row r="1183" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1183" s="4">
         <v>1182</v>
       </c>
       <c r="B1183" s="2"/>
       <c r="C1183" s="4"/>
-      <c r="D1183" s="6"/>
-    </row>
-    <row r="1184" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1184" s="4">
         <v>1183</v>
       </c>
       <c r="B1184" s="2"/>
       <c r="C1184" s="4"/>
-      <c r="D1184" s="6"/>
-    </row>
-    <row r="1185" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1185" s="4">
         <v>1184</v>
       </c>
       <c r="B1185" s="2"/>
       <c r="C1185" s="4"/>
-      <c r="D1185" s="6"/>
-    </row>
-    <row r="1186" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1186" s="4">
         <v>1185</v>
       </c>
       <c r="B1186" s="2"/>
       <c r="C1186" s="4"/>
-      <c r="D1186" s="6"/>
-    </row>
-    <row r="1187" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1187" s="4">
         <v>1186</v>
       </c>
       <c r="B1187" s="2"/>
       <c r="C1187" s="4"/>
-      <c r="D1187" s="6"/>
-    </row>
-    <row r="1188" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1188" s="4">
         <v>1187</v>
       </c>
       <c r="B1188" s="2"/>
       <c r="C1188" s="4"/>
-      <c r="D1188" s="6"/>
-    </row>
-    <row r="1189" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1189" s="4">
         <v>1188</v>
       </c>
       <c r="B1189" s="2"/>
       <c r="C1189" s="4"/>
-      <c r="D1189" s="6"/>
-    </row>
-    <row r="1190" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1190" s="4">
         <v>1189</v>
       </c>
       <c r="B1190" s="2"/>
       <c r="C1190" s="4"/>
-      <c r="D1190" s="6"/>
-    </row>
-    <row r="1191" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1191" s="4">
         <v>1190</v>
       </c>
       <c r="B1191" s="2"/>
       <c r="C1191" s="4"/>
-      <c r="D1191" s="6"/>
-    </row>
-    <row r="1192" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1192" s="4">
         <v>1191</v>
       </c>
       <c r="B1192" s="2"/>
       <c r="C1192" s="4"/>
-      <c r="D1192" s="6"/>
-    </row>
-    <row r="1193" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1193" s="4">
         <v>1192</v>
       </c>
       <c r="B1193" s="2"/>
       <c r="C1193" s="4"/>
-      <c r="D1193" s="6"/>
-    </row>
-    <row r="1194" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1194" s="4">
         <v>1193</v>
       </c>
       <c r="B1194" s="2"/>
       <c r="C1194" s="4"/>
-      <c r="D1194" s="6"/>
-    </row>
-    <row r="1195" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1195" s="4">
         <v>1194</v>
       </c>
       <c r="B1195" s="2"/>
       <c r="C1195" s="4"/>
-      <c r="D1195" s="6"/>
-    </row>
-    <row r="1196" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1196" s="4">
         <v>1195</v>
       </c>
       <c r="B1196" s="2"/>
       <c r="C1196" s="4"/>
-      <c r="D1196" s="6"/>
-    </row>
-    <row r="1197" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1197" s="4">
         <v>1196</v>
       </c>
       <c r="B1197" s="2"/>
       <c r="C1197" s="4"/>
-      <c r="D1197" s="6"/>
-    </row>
-    <row r="1198" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1198" s="4">
         <v>1197</v>
       </c>
       <c r="B1198" s="2"/>
       <c r="C1198" s="4"/>
-      <c r="D1198" s="6"/>
-    </row>
-    <row r="1199" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1199" s="4">
         <v>1198</v>
       </c>
       <c r="B1199" s="2"/>
       <c r="C1199" s="4"/>
-      <c r="D1199" s="6"/>
-    </row>
-    <row r="1200" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1200" s="4">
         <v>1199</v>
       </c>
       <c r="B1200" s="2"/>
       <c r="C1200" s="4"/>
-      <c r="D1200" s="6"/>
-    </row>
-    <row r="1201" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="1201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1201" s="4">
         <v>1200</v>
       </c>
       <c r="B1201" s="2"/>
       <c r="C1201" s="4"/>
-      <c r="D1201" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/OpenBudget.xlsx
+++ b/docs/OpenBudget.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nodir\open-budget-checker\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF0D9DC-8D36-43A3-B9E1-222EAAE62E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F0BDD8-373A-472D-B823-2453679BB64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{83070EB0-F3E9-4F09-9EA5-B85425558D79}"/>
   </bookViews>
@@ -9450,13 +9450,13 @@
       <c r="A602" s="4">
         <v>601</v>
       </c>
-      <c r="B602" s="7">
+      <c r="B602" s="2">
         <v>997984958</v>
       </c>
-      <c r="C602" s="8">
+      <c r="C602" s="4">
         <v>1623</v>
       </c>
-      <c r="D602" s="6" t="str">
+      <c r="D602" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "997984958", "voteDate": "2026-03-20 16:23"},</v>
       </c>
@@ -9465,13 +9465,13 @@
       <c r="A603" s="4">
         <v>602</v>
       </c>
-      <c r="B603" s="7">
+      <c r="B603" s="2">
         <v>942698844</v>
       </c>
-      <c r="C603" s="8">
+      <c r="C603" s="4">
         <v>1649</v>
       </c>
-      <c r="D603" s="6" t="str">
+      <c r="D603" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "942698844", "voteDate": "2026-03-20 16:49"},</v>
       </c>
@@ -9480,13 +9480,13 @@
       <c r="A604" s="4">
         <v>603</v>
       </c>
-      <c r="B604" s="7">
+      <c r="B604" s="2">
         <v>951055257</v>
       </c>
-      <c r="C604" s="8">
+      <c r="C604" s="4">
         <v>1652</v>
       </c>
-      <c r="D604" s="6" t="str">
+      <c r="D604" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "951055257", "voteDate": "2026-03-20 16:52"},</v>
       </c>
@@ -9495,13 +9495,13 @@
       <c r="A605" s="4">
         <v>604</v>
       </c>
-      <c r="B605" s="7">
+      <c r="B605" s="2">
         <v>770935459</v>
       </c>
-      <c r="C605" s="8">
+      <c r="C605" s="4">
         <v>1651</v>
       </c>
-      <c r="D605" s="6" t="str">
+      <c r="D605" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "770935459", "voteDate": "2026-03-20 16:51"},</v>
       </c>
@@ -9510,13 +9510,13 @@
       <c r="A606" s="4">
         <v>605</v>
       </c>
-      <c r="B606" s="7">
+      <c r="B606" s="2">
         <v>938008694</v>
       </c>
-      <c r="C606" s="8">
+      <c r="C606" s="4">
         <v>1645</v>
       </c>
-      <c r="D606" s="6" t="str">
+      <c r="D606" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "938008694", "voteDate": "2026-03-20 16:45"},</v>
       </c>
@@ -9525,13 +9525,13 @@
       <c r="A607" s="4">
         <v>606</v>
       </c>
-      <c r="B607" s="7">
+      <c r="B607" s="2">
         <v>775503072</v>
       </c>
-      <c r="C607" s="8">
+      <c r="C607" s="4">
         <v>1651</v>
       </c>
-      <c r="D607" s="6" t="str">
+      <c r="D607" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "775503072", "voteDate": "2026-03-20 16:51"},</v>
       </c>
@@ -9540,13 +9540,13 @@
       <c r="A608" s="4">
         <v>607</v>
       </c>
-      <c r="B608" s="7">
+      <c r="B608" s="2">
         <v>905557846</v>
       </c>
-      <c r="C608" s="8">
+      <c r="C608" s="4">
         <v>1653</v>
       </c>
-      <c r="D608" s="6" t="str">
+      <c r="D608" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "905557846", "voteDate": "2026-03-20 16:53"},</v>
       </c>
@@ -9555,13 +9555,13 @@
       <c r="A609" s="4">
         <v>608</v>
       </c>
-      <c r="B609" s="7">
+      <c r="B609" s="2">
         <v>939041058</v>
       </c>
-      <c r="C609" s="8">
+      <c r="C609" s="4">
         <v>1653</v>
       </c>
-      <c r="D609" s="6" t="str">
+      <c r="D609" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "939041058", "voteDate": "2026-03-20 16:53"},</v>
       </c>
@@ -9570,13 +9570,13 @@
       <c r="A610" s="4">
         <v>609</v>
       </c>
-      <c r="B610" s="7">
+      <c r="B610" s="2">
         <v>777134373</v>
       </c>
-      <c r="C610" s="8">
+      <c r="C610" s="4">
         <v>1654</v>
       </c>
-      <c r="D610" s="6" t="str">
+      <c r="D610" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "777134373", "voteDate": "2026-03-20 16:54"},</v>
       </c>
@@ -9585,13 +9585,13 @@
       <c r="A611" s="4">
         <v>610</v>
       </c>
-      <c r="B611" s="7">
+      <c r="B611" s="2">
         <v>773576727</v>
       </c>
-      <c r="C611" s="8">
+      <c r="C611" s="4">
         <v>1651</v>
       </c>
-      <c r="D611" s="6" t="str">
+      <c r="D611" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "773576727", "voteDate": "2026-03-20 16:51"},</v>
       </c>
@@ -9600,13 +9600,13 @@
       <c r="A612" s="4">
         <v>611</v>
       </c>
-      <c r="B612" s="7">
+      <c r="B612" s="2">
         <v>939041058</v>
       </c>
-      <c r="C612" s="8">
+      <c r="C612" s="4">
         <v>1653</v>
       </c>
-      <c r="D612" s="6" t="str">
+      <c r="D612" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "939041058", "voteDate": "2026-03-20 16:53"},</v>
       </c>
@@ -9615,13 +9615,13 @@
       <c r="A613" s="4">
         <v>612</v>
       </c>
-      <c r="B613" s="7">
+      <c r="B613" s="2">
         <v>930709299</v>
       </c>
-      <c r="C613" s="8">
+      <c r="C613" s="4">
         <v>1654</v>
       </c>
-      <c r="D613" s="6" t="str">
+      <c r="D613" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "930709299", "voteDate": "2026-03-20 16:54"},</v>
       </c>
@@ -9630,13 +9630,13 @@
       <c r="A614" s="4">
         <v>613</v>
       </c>
-      <c r="B614" s="7">
+      <c r="B614" s="2">
         <v>911222031</v>
       </c>
-      <c r="C614" s="8">
+      <c r="C614" s="4">
         <v>1657</v>
       </c>
-      <c r="D614" s="6" t="str">
+      <c r="D614" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "911222031", "voteDate": "2026-03-20 16:57"},</v>
       </c>
@@ -9645,13 +9645,13 @@
       <c r="A615" s="4">
         <v>614</v>
       </c>
-      <c r="B615" s="7">
+      <c r="B615" s="2">
         <v>935310147</v>
       </c>
-      <c r="C615" s="8">
+      <c r="C615" s="4">
         <v>1650</v>
       </c>
-      <c r="D615" s="6" t="str">
+      <c r="D615" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "935310147", "voteDate": "2026-03-20 16:50"},</v>
       </c>
@@ -9660,13 +9660,13 @@
       <c r="A616" s="4">
         <v>615</v>
       </c>
-      <c r="B616" s="7">
+      <c r="B616" s="2">
         <v>942570343</v>
       </c>
-      <c r="C616" s="8">
+      <c r="C616" s="4">
         <v>1656</v>
       </c>
-      <c r="D616" s="6" t="str">
+      <c r="D616" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "942570343", "voteDate": "2026-03-20 16:56"},</v>
       </c>
@@ -9675,13 +9675,13 @@
       <c r="A617" s="4">
         <v>616</v>
       </c>
-      <c r="B617" s="7">
+      <c r="B617" s="2">
         <v>884081018</v>
       </c>
-      <c r="C617" s="8">
+      <c r="C617" s="4">
         <v>1657</v>
       </c>
-      <c r="D617" s="6" t="str">
+      <c r="D617" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "884081018", "voteDate": "2026-03-20 16:57"},</v>
       </c>
@@ -9690,13 +9690,13 @@
       <c r="A618" s="4">
         <v>617</v>
       </c>
-      <c r="B618" s="7">
+      <c r="B618" s="2">
         <v>996279684</v>
       </c>
-      <c r="C618" s="8">
+      <c r="C618" s="4">
         <v>1658</v>
       </c>
-      <c r="D618" s="6" t="str">
+      <c r="D618" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "996279684", "voteDate": "2026-03-20 16:58"},</v>
       </c>
@@ -9705,13 +9705,13 @@
       <c r="A619" s="4">
         <v>618</v>
       </c>
-      <c r="B619" s="7">
+      <c r="B619" s="2">
         <v>885027371</v>
       </c>
-      <c r="C619" s="8">
+      <c r="C619" s="4">
         <v>1658</v>
       </c>
-      <c r="D619" s="6" t="str">
+      <c r="D619" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "885027371", "voteDate": "2026-03-20 16:58"},</v>
       </c>
@@ -9720,13 +9720,13 @@
       <c r="A620" s="4">
         <v>619</v>
       </c>
-      <c r="B620" s="7">
+      <c r="B620" s="2">
         <v>918207800</v>
       </c>
-      <c r="C620" s="8">
+      <c r="C620" s="4">
         <v>1654</v>
       </c>
-      <c r="D620" s="6" t="str">
+      <c r="D620" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "918207800", "voteDate": "2026-03-20 16:54"},</v>
       </c>
@@ -9735,13 +9735,13 @@
       <c r="A621" s="4">
         <v>620</v>
       </c>
-      <c r="B621" s="7">
+      <c r="B621" s="2">
         <v>995432911</v>
       </c>
-      <c r="C621" s="8">
+      <c r="C621" s="4">
         <v>1655</v>
       </c>
-      <c r="D621" s="6" t="str">
+      <c r="D621" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "995432911", "voteDate": "2026-03-20 16:55"},</v>
       </c>
@@ -9750,13 +9750,13 @@
       <c r="A622" s="4">
         <v>621</v>
       </c>
-      <c r="B622" s="7">
+      <c r="B622" s="2">
         <v>931169992</v>
       </c>
-      <c r="C622" s="8">
+      <c r="C622" s="4">
         <v>1700</v>
       </c>
-      <c r="D622" s="6" t="str">
+      <c r="D622" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "931169992", "voteDate": "2026-03-20 17:00"},</v>
       </c>
@@ -9765,13 +9765,13 @@
       <c r="A623" s="4">
         <v>622</v>
       </c>
-      <c r="B623" s="7">
+      <c r="B623" s="2">
         <v>951826332</v>
       </c>
-      <c r="C623" s="8">
+      <c r="C623" s="4">
         <v>1701</v>
       </c>
-      <c r="D623" s="6" t="str">
+      <c r="D623" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "951826332", "voteDate": "2026-03-20 17:01"},</v>
       </c>
@@ -9780,13 +9780,13 @@
       <c r="A624" s="4">
         <v>623</v>
       </c>
-      <c r="B624" s="7">
+      <c r="B624" s="2">
         <v>991288391</v>
       </c>
-      <c r="C624" s="8">
+      <c r="C624" s="4">
         <v>1703</v>
       </c>
-      <c r="D624" s="6" t="str">
+      <c r="D624" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "991288391", "voteDate": "2026-03-20 17:03"},</v>
       </c>
@@ -9795,13 +9795,13 @@
       <c r="A625" s="4">
         <v>624</v>
       </c>
-      <c r="B625" s="7">
+      <c r="B625" s="2">
         <v>931373111</v>
       </c>
-      <c r="C625" s="8">
+      <c r="C625" s="4">
         <v>1701</v>
       </c>
-      <c r="D625" s="6" t="str">
+      <c r="D625" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "931373111", "voteDate": "2026-03-20 17:01"},</v>
       </c>
@@ -9810,13 +9810,13 @@
       <c r="A626" s="4">
         <v>625</v>
       </c>
-      <c r="B626" s="7">
+      <c r="B626" s="2">
         <v>930858823</v>
       </c>
-      <c r="C626" s="8">
+      <c r="C626" s="4">
         <v>1702</v>
       </c>
-      <c r="D626" s="6" t="str">
+      <c r="D626" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "930858823", "voteDate": "2026-03-20 17:02"},</v>
       </c>
@@ -9825,13 +9825,13 @@
       <c r="A627" s="4">
         <v>626</v>
       </c>
-      <c r="B627" s="7">
+      <c r="B627" s="2">
         <v>948184868</v>
       </c>
-      <c r="C627" s="8">
+      <c r="C627" s="4">
         <v>1704</v>
       </c>
-      <c r="D627" s="6" t="str">
+      <c r="D627" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "948184868", "voteDate": "2026-03-20 17:04"},</v>
       </c>
@@ -9840,13 +9840,13 @@
       <c r="A628" s="4">
         <v>627</v>
       </c>
-      <c r="B628" s="7">
+      <c r="B628" s="2">
         <v>941983030</v>
       </c>
-      <c r="C628" s="8">
+      <c r="C628" s="4">
         <v>1702</v>
       </c>
-      <c r="D628" s="6" t="str">
+      <c r="D628" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "941983030", "voteDate": "2026-03-20 17:02"},</v>
       </c>
@@ -9855,13 +9855,13 @@
       <c r="A629" s="4">
         <v>628</v>
       </c>
-      <c r="B629" s="7">
+      <c r="B629" s="2">
         <v>912864686</v>
       </c>
-      <c r="C629" s="8">
+      <c r="C629" s="4">
         <v>1702</v>
       </c>
-      <c r="D629" s="6" t="str">
+      <c r="D629" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "912864686", "voteDate": "2026-03-20 17:02"},</v>
       </c>
@@ -9870,13 +9870,13 @@
       <c r="A630" s="4">
         <v>629</v>
       </c>
-      <c r="B630" s="7">
+      <c r="B630" s="2">
         <v>910690855</v>
       </c>
-      <c r="C630" s="8">
+      <c r="C630" s="4">
         <v>1702</v>
       </c>
-      <c r="D630" s="6" t="str">
+      <c r="D630" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "910690855", "voteDate": "2026-03-20 17:02"},</v>
       </c>
@@ -9885,13 +9885,13 @@
       <c r="A631" s="4">
         <v>630</v>
       </c>
-      <c r="B631" s="7">
+      <c r="B631" s="2">
         <v>955200125</v>
       </c>
-      <c r="C631" s="8">
+      <c r="C631" s="4">
         <v>1708</v>
       </c>
-      <c r="D631" s="6" t="str">
+      <c r="D631" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "955200125", "voteDate": "2026-03-20 17:08"},</v>
       </c>
@@ -9900,13 +9900,13 @@
       <c r="A632" s="4">
         <v>631</v>
       </c>
-      <c r="B632" s="7">
+      <c r="B632" s="2">
         <v>991288391</v>
       </c>
-      <c r="C632" s="8">
+      <c r="C632" s="4">
         <v>1703</v>
       </c>
-      <c r="D632" s="6" t="str">
+      <c r="D632" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "991288391", "voteDate": "2026-03-20 17:03"},</v>
       </c>
@@ -9915,13 +9915,13 @@
       <c r="A633" s="4">
         <v>632</v>
       </c>
-      <c r="B633" s="7">
+      <c r="B633" s="2">
         <v>703600891</v>
       </c>
-      <c r="C633" s="8">
+      <c r="C633" s="4">
         <v>1708</v>
       </c>
-      <c r="D633" s="6" t="str">
+      <c r="D633" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "703600891", "voteDate": "2026-03-20 17:08"},</v>
       </c>
@@ -9930,13 +9930,13 @@
       <c r="A634" s="4">
         <v>633</v>
       </c>
-      <c r="B634" s="7">
+      <c r="B634" s="2">
         <v>955322803</v>
       </c>
-      <c r="C634" s="8">
+      <c r="C634" s="4">
         <v>1709</v>
       </c>
-      <c r="D634" s="6" t="str">
+      <c r="D634" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "955322803", "voteDate": "2026-03-20 17:09"},</v>
       </c>
@@ -9945,13 +9945,13 @@
       <c r="A635" s="4">
         <v>634</v>
       </c>
-      <c r="B635" s="7">
+      <c r="B635" s="2">
         <v>994638594</v>
       </c>
-      <c r="C635" s="8">
+      <c r="C635" s="4">
         <v>1708</v>
       </c>
-      <c r="D635" s="6" t="str">
+      <c r="D635" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "994638594", "voteDate": "2026-03-20 17:08"},</v>
       </c>
@@ -9960,13 +9960,13 @@
       <c r="A636" s="4">
         <v>635</v>
       </c>
-      <c r="B636" s="7">
+      <c r="B636" s="2">
         <v>509002213</v>
       </c>
-      <c r="C636" s="8">
+      <c r="C636" s="4">
         <v>1710</v>
       </c>
-      <c r="D636" s="6" t="str">
+      <c r="D636" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "509002213", "voteDate": "2026-03-20 17:10"},</v>
       </c>
@@ -9975,13 +9975,13 @@
       <c r="A637" s="4">
         <v>636</v>
       </c>
-      <c r="B637" s="7">
+      <c r="B637" s="2">
         <v>931565582</v>
       </c>
-      <c r="C637" s="8">
+      <c r="C637" s="4">
         <v>1708</v>
       </c>
-      <c r="D637" s="6" t="str">
+      <c r="D637" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "931565582", "voteDate": "2026-03-20 17:08"},</v>
       </c>
@@ -9990,13 +9990,13 @@
       <c r="A638" s="4">
         <v>637</v>
       </c>
-      <c r="B638" s="7">
+      <c r="B638" s="2">
         <v>905140998</v>
       </c>
-      <c r="C638" s="8">
+      <c r="C638" s="4">
         <v>1710</v>
       </c>
-      <c r="D638" s="6" t="str">
+      <c r="D638" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "905140998", "voteDate": "2026-03-20 17:10"},</v>
       </c>
@@ -10005,13 +10005,13 @@
       <c r="A639" s="4">
         <v>638</v>
       </c>
-      <c r="B639" s="7">
+      <c r="B639" s="2">
         <v>889335023</v>
       </c>
-      <c r="C639" s="8">
+      <c r="C639" s="4">
         <v>1709</v>
       </c>
-      <c r="D639" s="6" t="str">
+      <c r="D639" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "889335023", "voteDate": "2026-03-20 17:09"},</v>
       </c>
@@ -10020,13 +10020,13 @@
       <c r="A640" s="4">
         <v>639</v>
       </c>
-      <c r="B640" s="7">
+      <c r="B640" s="2">
         <v>938267782</v>
       </c>
-      <c r="C640" s="8">
+      <c r="C640" s="4">
         <v>1714</v>
       </c>
-      <c r="D640" s="6" t="str">
+      <c r="D640" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "938267782", "voteDate": "2026-03-20 17:14"},</v>
       </c>
@@ -10035,13 +10035,13 @@
       <c r="A641" s="4">
         <v>640</v>
       </c>
-      <c r="B641" s="7">
+      <c r="B641" s="2">
         <v>336063072</v>
       </c>
-      <c r="C641" s="8">
+      <c r="C641" s="4">
         <v>1656</v>
       </c>
-      <c r="D641" s="6" t="str">
+      <c r="D641" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "336063072", "voteDate": "2026-03-20 16:56"},</v>
       </c>
@@ -10050,13 +10050,13 @@
       <c r="A642" s="4">
         <v>641</v>
       </c>
-      <c r="B642" s="7">
+      <c r="B642" s="2">
         <v>990150303</v>
       </c>
-      <c r="C642" s="8">
+      <c r="C642" s="4">
         <v>1702</v>
       </c>
-      <c r="D642" s="6" t="str">
+      <c r="D642" t="str">
         <f t="shared" si="9"/>
         <v>{"phoneNumber": "990150303", "voteDate": "2026-03-20 17:02"},</v>
       </c>
@@ -10065,14 +10065,14 @@
       <c r="A643" s="4">
         <v>642</v>
       </c>
-      <c r="B643" s="7">
+      <c r="B643" s="2">
         <v>502771477</v>
       </c>
-      <c r="C643" s="8">
+      <c r="C643" s="4">
         <v>1701</v>
       </c>
-      <c r="D643" s="6" t="str">
-        <f t="shared" ref="D643:D701" si="10">"{""phoneNumber"": """&amp;B643&amp;""", ""voteDate"": """&amp;TEXT(DATE(2026,3,20),"yyyy-mm-dd")&amp;" "&amp;TEXT(C643,"00\:00")&amp;"""},"</f>
+      <c r="D643" t="str">
+        <f t="shared" ref="D643:D706" si="10">"{""phoneNumber"": """&amp;B643&amp;""", ""voteDate"": """&amp;TEXT(DATE(2026,3,20),"yyyy-mm-dd")&amp;" "&amp;TEXT(C643,"00\:00")&amp;"""},"</f>
         <v>{"phoneNumber": "502771477", "voteDate": "2026-03-20 17:01"},</v>
       </c>
     </row>
@@ -10080,13 +10080,13 @@
       <c r="A644" s="4">
         <v>643</v>
       </c>
-      <c r="B644" s="7">
+      <c r="B644" s="2">
         <v>950674323</v>
       </c>
-      <c r="C644" s="8">
+      <c r="C644" s="4">
         <v>1708</v>
       </c>
-      <c r="D644" s="6" t="str">
+      <c r="D644" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "950674323", "voteDate": "2026-03-20 17:08"},</v>
       </c>
@@ -10095,13 +10095,13 @@
       <c r="A645" s="4">
         <v>644</v>
       </c>
-      <c r="B645" s="7">
+      <c r="B645" s="2">
         <v>507171593</v>
       </c>
-      <c r="C645" s="8">
+      <c r="C645" s="4">
         <v>1713</v>
       </c>
-      <c r="D645" s="6" t="str">
+      <c r="D645" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "507171593", "voteDate": "2026-03-20 17:13"},</v>
       </c>
@@ -10110,13 +10110,13 @@
       <c r="A646" s="4">
         <v>645</v>
       </c>
-      <c r="B646" s="7">
+      <c r="B646" s="2">
         <v>505810925</v>
       </c>
-      <c r="C646" s="8">
+      <c r="C646" s="4">
         <v>1636</v>
       </c>
-      <c r="D646" s="6" t="str">
+      <c r="D646" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "505810925", "voteDate": "2026-03-20 16:36"},</v>
       </c>
@@ -10125,13 +10125,13 @@
       <c r="A647" s="4">
         <v>646</v>
       </c>
-      <c r="B647" s="7">
+      <c r="B647" s="2">
         <v>915392525</v>
       </c>
-      <c r="C647" s="8">
+      <c r="C647" s="4">
         <v>1703</v>
       </c>
-      <c r="D647" s="6" t="str">
+      <c r="D647" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "915392525", "voteDate": "2026-03-20 17:03"},</v>
       </c>
@@ -10140,13 +10140,13 @@
       <c r="A648" s="4">
         <v>647</v>
       </c>
-      <c r="B648" s="7">
+      <c r="B648" s="2">
         <v>994934097</v>
       </c>
-      <c r="C648" s="8">
+      <c r="C648" s="4">
         <v>1705</v>
       </c>
-      <c r="D648" s="6" t="str">
+      <c r="D648" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "994934097", "voteDate": "2026-03-20 17:05"},</v>
       </c>
@@ -10155,13 +10155,13 @@
       <c r="A649" s="4">
         <v>648</v>
       </c>
-      <c r="B649" s="7">
+      <c r="B649" s="2">
         <v>902275989</v>
       </c>
-      <c r="C649" s="8">
+      <c r="C649" s="4">
         <v>1719</v>
       </c>
-      <c r="D649" s="6" t="str">
+      <c r="D649" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "902275989", "voteDate": "2026-03-20 17:19"},</v>
       </c>
@@ -10170,13 +10170,13 @@
       <c r="A650" s="4">
         <v>649</v>
       </c>
-      <c r="B650" s="7">
+      <c r="B650" s="2">
         <v>955200125</v>
       </c>
-      <c r="C650" s="8">
+      <c r="C650" s="4">
         <v>1708</v>
       </c>
-      <c r="D650" s="6" t="str">
+      <c r="D650" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "955200125", "voteDate": "2026-03-20 17:08"},</v>
       </c>
@@ -10185,13 +10185,13 @@
       <c r="A651" s="4">
         <v>650</v>
       </c>
-      <c r="B651" s="7">
+      <c r="B651" s="2">
         <v>777561133</v>
       </c>
-      <c r="C651" s="8">
+      <c r="C651" s="4">
         <v>1710</v>
       </c>
-      <c r="D651" s="6" t="str">
+      <c r="D651" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "777561133", "voteDate": "2026-03-20 17:10"},</v>
       </c>
@@ -10200,13 +10200,13 @@
       <c r="A652" s="4">
         <v>651</v>
       </c>
-      <c r="B652" s="7">
+      <c r="B652" s="2">
         <v>931939314</v>
       </c>
-      <c r="C652" s="8">
+      <c r="C652" s="4">
         <v>1715</v>
       </c>
-      <c r="D652" s="6" t="str">
+      <c r="D652" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "931939314", "voteDate": "2026-03-20 17:15"},</v>
       </c>
@@ -10215,13 +10215,13 @@
       <c r="A653" s="4">
         <v>652</v>
       </c>
-      <c r="B653" s="7">
+      <c r="B653" s="2">
         <v>911941394</v>
       </c>
-      <c r="C653" s="8">
+      <c r="C653" s="4">
         <v>1712</v>
       </c>
-      <c r="D653" s="6" t="str">
+      <c r="D653" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "911941394", "voteDate": "2026-03-20 17:12"},</v>
       </c>
@@ -10230,13 +10230,13 @@
       <c r="A654" s="4">
         <v>653</v>
       </c>
-      <c r="B654" s="7">
+      <c r="B654" s="2">
         <v>975450906</v>
       </c>
-      <c r="C654" s="8">
+      <c r="C654" s="4">
         <v>1721</v>
       </c>
-      <c r="D654" s="6" t="str">
+      <c r="D654" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "975450906", "voteDate": "2026-03-20 17:21"},</v>
       </c>
@@ -10245,13 +10245,13 @@
       <c r="A655" s="4">
         <v>654</v>
       </c>
-      <c r="B655" s="7">
+      <c r="B655" s="2">
         <v>901255989</v>
       </c>
-      <c r="C655" s="8">
+      <c r="C655" s="4">
         <v>1724</v>
       </c>
-      <c r="D655" s="6" t="str">
+      <c r="D655" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "901255989", "voteDate": "2026-03-20 17:24"},</v>
       </c>
@@ -10260,13 +10260,13 @@
       <c r="A656" s="4">
         <v>655</v>
       </c>
-      <c r="B656" s="7">
+      <c r="B656" s="2">
         <v>905976525</v>
       </c>
-      <c r="C656" s="8">
+      <c r="C656" s="4">
         <v>1724</v>
       </c>
-      <c r="D656" s="6" t="str">
+      <c r="D656" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "905976525", "voteDate": "2026-03-20 17:24"},</v>
       </c>
@@ -10275,13 +10275,13 @@
       <c r="A657" s="4">
         <v>656</v>
       </c>
-      <c r="B657" s="7">
+      <c r="B657" s="2">
         <v>877945355</v>
       </c>
-      <c r="C657" s="8">
+      <c r="C657" s="4">
         <v>1713</v>
       </c>
-      <c r="D657" s="6" t="str">
+      <c r="D657" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "877945355", "voteDate": "2026-03-20 17:13"},</v>
       </c>
@@ -10290,13 +10290,13 @@
       <c r="A658" s="4">
         <v>657</v>
       </c>
-      <c r="B658" s="7">
+      <c r="B658" s="2">
         <v>953748121</v>
       </c>
-      <c r="C658" s="8">
+      <c r="C658" s="4">
         <v>1713</v>
       </c>
-      <c r="D658" s="6" t="str">
+      <c r="D658" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "953748121", "voteDate": "2026-03-20 17:13"},</v>
       </c>
@@ -10305,13 +10305,13 @@
       <c r="A659" s="4">
         <v>658</v>
       </c>
-      <c r="B659" s="7">
+      <c r="B659" s="2">
         <v>932780008</v>
       </c>
-      <c r="C659" s="8">
+      <c r="C659" s="4">
         <v>1718</v>
       </c>
-      <c r="D659" s="6" t="str">
+      <c r="D659" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "932780008", "voteDate": "2026-03-20 17:18"},</v>
       </c>
@@ -10320,13 +10320,13 @@
       <c r="A660" s="4">
         <v>659</v>
       </c>
-      <c r="B660" s="7">
+      <c r="B660" s="2">
         <v>933180528</v>
       </c>
-      <c r="C660" s="8">
+      <c r="C660" s="4">
         <v>1719</v>
       </c>
-      <c r="D660" s="6" t="str">
+      <c r="D660" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "933180528", "voteDate": "2026-03-20 17:19"},</v>
       </c>
@@ -10335,13 +10335,13 @@
       <c r="A661" s="4">
         <v>660</v>
       </c>
-      <c r="B661" s="7">
+      <c r="B661" s="2">
         <v>882844393</v>
       </c>
-      <c r="C661" s="8">
+      <c r="C661" s="4">
         <v>1720</v>
       </c>
-      <c r="D661" s="6" t="str">
+      <c r="D661" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "882844393", "voteDate": "2026-03-20 17:20"},</v>
       </c>
@@ -10350,13 +10350,13 @@
       <c r="A662" s="4">
         <v>661</v>
       </c>
-      <c r="B662" s="7">
+      <c r="B662" s="2">
         <v>507707580</v>
       </c>
-      <c r="C662" s="8">
+      <c r="C662" s="4">
         <v>1723</v>
       </c>
-      <c r="D662" s="6" t="str">
+      <c r="D662" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "507707580", "voteDate": "2026-03-20 17:23"},</v>
       </c>
@@ -10365,13 +10365,13 @@
       <c r="A663" s="4">
         <v>662</v>
       </c>
-      <c r="B663" s="7">
+      <c r="B663" s="2">
         <v>905206747</v>
       </c>
-      <c r="C663" s="8">
+      <c r="C663" s="4">
         <v>1728</v>
       </c>
-      <c r="D663" s="6" t="str">
+      <c r="D663" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "905206747", "voteDate": "2026-03-20 17:28"},</v>
       </c>
@@ -10380,13 +10380,13 @@
       <c r="A664" s="4">
         <v>663</v>
       </c>
-      <c r="B664" s="7">
+      <c r="B664" s="2">
         <v>947449678</v>
       </c>
-      <c r="C664" s="8">
+      <c r="C664" s="4">
         <v>1733</v>
       </c>
-      <c r="D664" s="6" t="str">
+      <c r="D664" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "947449678", "voteDate": "2026-03-20 17:33"},</v>
       </c>
@@ -10395,13 +10395,13 @@
       <c r="A665" s="4">
         <v>664</v>
       </c>
-      <c r="B665" s="7">
+      <c r="B665" s="2">
         <v>508891631</v>
       </c>
-      <c r="C665" s="8">
+      <c r="C665" s="4">
         <v>1639</v>
       </c>
-      <c r="D665" s="6" t="str">
+      <c r="D665" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "508891631", "voteDate": "2026-03-20 16:39"},</v>
       </c>
@@ -10410,13 +10410,13 @@
       <c r="A666" s="4">
         <v>665</v>
       </c>
-      <c r="B666" s="7">
+      <c r="B666" s="2">
         <v>945080599</v>
       </c>
-      <c r="C666" s="8">
+      <c r="C666" s="4">
         <v>1637</v>
       </c>
-      <c r="D666" s="6" t="str">
+      <c r="D666" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "945080599", "voteDate": "2026-03-20 16:37"},</v>
       </c>
@@ -10425,13 +10425,13 @@
       <c r="A667" s="4">
         <v>666</v>
       </c>
-      <c r="B667" s="7">
+      <c r="B667" s="2">
         <v>934361718</v>
       </c>
-      <c r="C667" s="8">
+      <c r="C667" s="4">
         <v>1731</v>
       </c>
-      <c r="D667" s="6" t="str">
+      <c r="D667" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "934361718", "voteDate": "2026-03-20 17:31"},</v>
       </c>
@@ -10440,13 +10440,13 @@
       <c r="A668" s="4">
         <v>667</v>
       </c>
-      <c r="B668" s="7">
+      <c r="B668" s="2">
         <v>949780816</v>
       </c>
-      <c r="C668" s="8">
+      <c r="C668" s="4">
         <v>1732</v>
       </c>
-      <c r="D668" s="6" t="str">
+      <c r="D668" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "949780816", "voteDate": "2026-03-20 17:32"},</v>
       </c>
@@ -10455,13 +10455,13 @@
       <c r="A669" s="4">
         <v>668</v>
       </c>
-      <c r="B669" s="7">
+      <c r="B669" s="2">
         <v>911202272</v>
       </c>
-      <c r="C669" s="8">
+      <c r="C669" s="4">
         <v>1727</v>
       </c>
-      <c r="D669" s="6" t="str">
+      <c r="D669" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "911202272", "voteDate": "2026-03-20 17:27"},</v>
       </c>
@@ -10470,13 +10470,13 @@
       <c r="A670" s="4">
         <v>669</v>
       </c>
-      <c r="B670" s="7">
+      <c r="B670" s="2">
         <v>975900274</v>
       </c>
-      <c r="C670" s="8">
+      <c r="C670" s="4">
         <v>1731</v>
       </c>
-      <c r="D670" s="6" t="str">
+      <c r="D670" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "975900274", "voteDate": "2026-03-20 17:31"},</v>
       </c>
@@ -10485,13 +10485,13 @@
       <c r="A671" s="4">
         <v>670</v>
       </c>
-      <c r="B671" s="7">
+      <c r="B671" s="2">
         <v>931144597</v>
       </c>
-      <c r="C671" s="8">
+      <c r="C671" s="4">
         <v>1736</v>
       </c>
-      <c r="D671" s="6" t="str">
+      <c r="D671" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "931144597", "voteDate": "2026-03-20 17:36"},</v>
       </c>
@@ -10500,13 +10500,13 @@
       <c r="A672" s="4">
         <v>671</v>
       </c>
-      <c r="B672" s="7">
+      <c r="B672" s="2">
         <v>944237080</v>
       </c>
-      <c r="C672" s="8">
+      <c r="C672" s="4">
         <v>1736</v>
       </c>
-      <c r="D672" s="6" t="str">
+      <c r="D672" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "944237080", "voteDate": "2026-03-20 17:36"},</v>
       </c>
@@ -10515,13 +10515,13 @@
       <c r="A673" s="4">
         <v>672</v>
       </c>
-      <c r="B673" s="7">
+      <c r="B673" s="2">
         <v>902927121</v>
       </c>
-      <c r="C673" s="8">
+      <c r="C673" s="4">
         <v>1736</v>
       </c>
-      <c r="D673" s="6" t="str">
+      <c r="D673" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "902927121", "voteDate": "2026-03-20 17:36"},</v>
       </c>
@@ -10530,13 +10530,13 @@
       <c r="A674" s="4">
         <v>673</v>
       </c>
-      <c r="B674" s="7">
+      <c r="B674" s="2">
         <v>917471992</v>
       </c>
-      <c r="C674" s="8">
+      <c r="C674" s="4">
         <v>1744</v>
       </c>
-      <c r="D674" s="6" t="str">
+      <c r="D674" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "917471992", "voteDate": "2026-03-20 17:44"},</v>
       </c>
@@ -10545,13 +10545,13 @@
       <c r="A675" s="4">
         <v>674</v>
       </c>
-      <c r="B675" s="7">
+      <c r="B675" s="2">
         <v>700391929</v>
       </c>
-      <c r="C675" s="8">
+      <c r="C675" s="4">
         <v>1743</v>
       </c>
-      <c r="D675" s="6" t="str">
+      <c r="D675" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "700391929", "voteDate": "2026-03-20 17:43"},</v>
       </c>
@@ -10560,13 +10560,13 @@
       <c r="A676" s="4">
         <v>675</v>
       </c>
-      <c r="B676" s="7">
+      <c r="B676" s="2">
         <v>904959850</v>
       </c>
-      <c r="C676" s="8">
+      <c r="C676" s="4">
         <v>1726</v>
       </c>
-      <c r="D676" s="6" t="str">
+      <c r="D676" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "904959850", "voteDate": "2026-03-20 17:26"},</v>
       </c>
@@ -10575,13 +10575,13 @@
       <c r="A677" s="4">
         <v>676</v>
       </c>
-      <c r="B677" s="7">
+      <c r="B677" s="2">
         <v>919472212</v>
       </c>
-      <c r="C677" s="8">
+      <c r="C677" s="4">
         <v>1737</v>
       </c>
-      <c r="D677" s="6" t="str">
+      <c r="D677" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "919472212", "voteDate": "2026-03-20 17:37"},</v>
       </c>
@@ -10590,13 +10590,13 @@
       <c r="A678" s="4">
         <v>677</v>
       </c>
-      <c r="B678" s="7">
+      <c r="B678" s="2">
         <v>958390102</v>
       </c>
-      <c r="C678" s="8">
+      <c r="C678" s="4">
         <v>1748</v>
       </c>
-      <c r="D678" s="6" t="str">
+      <c r="D678" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "958390102", "voteDate": "2026-03-20 17:48"},</v>
       </c>
@@ -10605,13 +10605,13 @@
       <c r="A679" s="4">
         <v>678</v>
       </c>
-      <c r="B679" s="7">
+      <c r="B679" s="2">
         <v>912851252</v>
       </c>
-      <c r="C679" s="8">
+      <c r="C679" s="4">
         <v>1749</v>
       </c>
-      <c r="D679" s="6" t="str">
+      <c r="D679" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "912851252", "voteDate": "2026-03-20 17:49"},</v>
       </c>
@@ -10620,13 +10620,13 @@
       <c r="A680" s="4">
         <v>679</v>
       </c>
-      <c r="B680" s="7">
+      <c r="B680" s="2">
         <v>913207880</v>
       </c>
-      <c r="C680" s="8">
+      <c r="C680" s="4">
         <v>1718</v>
       </c>
-      <c r="D680" s="6" t="str">
+      <c r="D680" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "913207880", "voteDate": "2026-03-20 17:18"},</v>
       </c>
@@ -10635,13 +10635,13 @@
       <c r="A681" s="4">
         <v>680</v>
       </c>
-      <c r="B681" s="7">
+      <c r="B681" s="2">
         <v>973802526</v>
       </c>
-      <c r="C681" s="8">
+      <c r="C681" s="4">
         <v>1748</v>
       </c>
-      <c r="D681" s="6" t="str">
+      <c r="D681" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "973802526", "voteDate": "2026-03-20 17:48"},</v>
       </c>
@@ -10650,13 +10650,13 @@
       <c r="A682" s="4">
         <v>681</v>
       </c>
-      <c r="B682" s="7">
+      <c r="B682" s="2">
         <v>889529858</v>
       </c>
-      <c r="C682" s="8">
+      <c r="C682" s="4">
         <v>1750</v>
       </c>
-      <c r="D682" s="6" t="str">
+      <c r="D682" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "889529858", "voteDate": "2026-03-20 17:50"},</v>
       </c>
@@ -10665,13 +10665,13 @@
       <c r="A683" s="4">
         <v>682</v>
       </c>
-      <c r="B683" s="7">
+      <c r="B683" s="2">
         <v>903448579</v>
       </c>
-      <c r="C683" s="8">
+      <c r="C683" s="4">
         <v>1749</v>
       </c>
-      <c r="D683" s="6" t="str">
+      <c r="D683" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "903448579", "voteDate": "2026-03-20 17:49"},</v>
       </c>
@@ -10680,13 +10680,13 @@
       <c r="A684" s="4">
         <v>683</v>
       </c>
-      <c r="B684" s="7">
+      <c r="B684" s="2">
         <v>905632007</v>
       </c>
-      <c r="C684" s="8">
+      <c r="C684" s="4">
         <v>1748</v>
       </c>
-      <c r="D684" s="6" t="str">
+      <c r="D684" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "905632007", "voteDate": "2026-03-20 17:48"},</v>
       </c>
@@ -10695,13 +10695,13 @@
       <c r="A685" s="4">
         <v>684</v>
       </c>
-      <c r="B685" s="7">
+      <c r="B685" s="2">
         <v>917407515</v>
       </c>
-      <c r="C685" s="8">
+      <c r="C685" s="4">
         <v>1746</v>
       </c>
-      <c r="D685" s="6" t="str">
+      <c r="D685" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "917407515", "voteDate": "2026-03-20 17:46"},</v>
       </c>
@@ -10710,13 +10710,13 @@
       <c r="A686" s="4">
         <v>685</v>
       </c>
-      <c r="B686" s="7">
+      <c r="B686" s="2">
         <v>941210921</v>
       </c>
-      <c r="C686" s="8">
+      <c r="C686" s="4">
         <v>1751</v>
       </c>
-      <c r="D686" s="6" t="str">
+      <c r="D686" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "941210921", "voteDate": "2026-03-20 17:51"},</v>
       </c>
@@ -10725,13 +10725,13 @@
       <c r="A687" s="4">
         <v>686</v>
       </c>
-      <c r="B687" s="7">
+      <c r="B687" s="2">
         <v>948286655</v>
       </c>
-      <c r="C687" s="8">
+      <c r="C687" s="4">
         <v>1751</v>
       </c>
-      <c r="D687" s="6" t="str">
+      <c r="D687" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "948286655", "voteDate": "2026-03-20 17:51"},</v>
       </c>
@@ -10740,13 +10740,13 @@
       <c r="A688" s="4">
         <v>687</v>
       </c>
-      <c r="B688" s="7">
+      <c r="B688" s="2">
         <v>900595755</v>
       </c>
-      <c r="C688" s="8">
+      <c r="C688" s="4">
         <v>1740</v>
       </c>
-      <c r="D688" s="6" t="str">
+      <c r="D688" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "900595755", "voteDate": "2026-03-20 17:40"},</v>
       </c>
@@ -10755,13 +10755,13 @@
       <c r="A689" s="4">
         <v>688</v>
       </c>
-      <c r="B689" s="7">
+      <c r="B689" s="2">
         <v>903072942</v>
       </c>
-      <c r="C689" s="8">
+      <c r="C689" s="4">
         <v>1748</v>
       </c>
-      <c r="D689" s="6" t="str">
+      <c r="D689" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "903072942", "voteDate": "2026-03-20 17:48"},</v>
       </c>
@@ -10770,13 +10770,13 @@
       <c r="A690" s="4">
         <v>689</v>
       </c>
-      <c r="B690" s="7">
+      <c r="B690" s="2">
         <v>940592062</v>
       </c>
-      <c r="C690" s="8">
+      <c r="C690" s="4">
         <v>1744</v>
       </c>
-      <c r="D690" s="6" t="str">
+      <c r="D690" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "940592062", "voteDate": "2026-03-20 17:44"},</v>
       </c>
@@ -10785,13 +10785,13 @@
       <c r="A691" s="4">
         <v>690</v>
       </c>
-      <c r="B691" s="7">
+      <c r="B691" s="2">
         <v>941506595</v>
       </c>
-      <c r="C691" s="8">
+      <c r="C691" s="4">
         <v>1722</v>
       </c>
-      <c r="D691" s="6" t="str">
+      <c r="D691" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "941506595", "voteDate": "2026-03-20 17:22"},</v>
       </c>
@@ -10800,13 +10800,13 @@
       <c r="A692" s="4">
         <v>691</v>
       </c>
-      <c r="B692" s="7">
+      <c r="B692" s="2">
         <v>508852919</v>
       </c>
-      <c r="C692" s="8">
+      <c r="C692" s="4">
         <v>1739</v>
       </c>
-      <c r="D692" s="6" t="str">
+      <c r="D692" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "508852919", "voteDate": "2026-03-20 17:39"},</v>
       </c>
@@ -10815,13 +10815,13 @@
       <c r="A693" s="4">
         <v>692</v>
       </c>
-      <c r="B693" s="7">
+      <c r="B693" s="2">
         <v>919646331</v>
       </c>
-      <c r="C693" s="8">
+      <c r="C693" s="4">
         <v>1757</v>
       </c>
-      <c r="D693" s="6" t="str">
+      <c r="D693" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "919646331", "voteDate": "2026-03-20 17:57"},</v>
       </c>
@@ -10830,13 +10830,13 @@
       <c r="A694" s="4">
         <v>693</v>
       </c>
-      <c r="B694" s="7">
+      <c r="B694" s="2">
         <v>911066451</v>
       </c>
-      <c r="C694" s="8">
+      <c r="C694" s="4">
         <v>1749</v>
       </c>
-      <c r="D694" s="6" t="str">
+      <c r="D694" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "911066451", "voteDate": "2026-03-20 17:49"},</v>
       </c>
@@ -10845,13 +10845,13 @@
       <c r="A695" s="4">
         <v>694</v>
       </c>
-      <c r="B695" s="7">
+      <c r="B695" s="2">
         <v>916634439</v>
       </c>
-      <c r="C695" s="8">
+      <c r="C695" s="4">
         <v>1753</v>
       </c>
-      <c r="D695" s="6" t="str">
+      <c r="D695" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "916634439", "voteDate": "2026-03-20 17:53"},</v>
       </c>
@@ -10860,13 +10860,13 @@
       <c r="A696" s="4">
         <v>695</v>
       </c>
-      <c r="B696" s="7">
+      <c r="B696" s="2">
         <v>934562809</v>
       </c>
-      <c r="C696" s="8">
+      <c r="C696" s="4">
         <v>1753</v>
       </c>
-      <c r="D696" s="6" t="str">
+      <c r="D696" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "934562809", "voteDate": "2026-03-20 17:53"},</v>
       </c>
@@ -10875,13 +10875,13 @@
       <c r="A697" s="4">
         <v>696</v>
       </c>
-      <c r="B697" s="7">
+      <c r="B697" s="2">
         <v>999570502</v>
       </c>
-      <c r="C697" s="8">
+      <c r="C697" s="4">
         <v>1756</v>
       </c>
-      <c r="D697" s="6" t="str">
+      <c r="D697" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "999570502", "voteDate": "2026-03-20 17:56"},</v>
       </c>
@@ -10890,13 +10890,13 @@
       <c r="A698" s="4">
         <v>697</v>
       </c>
-      <c r="B698" s="7">
+      <c r="B698" s="2">
         <v>931257528</v>
       </c>
-      <c r="C698" s="8">
+      <c r="C698" s="4">
         <v>1803</v>
       </c>
-      <c r="D698" s="6" t="str">
+      <c r="D698" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "931257528", "voteDate": "2026-03-20 18:03"},</v>
       </c>
@@ -10905,13 +10905,13 @@
       <c r="A699" s="4">
         <v>698</v>
       </c>
-      <c r="B699" s="7">
+      <c r="B699" s="2">
         <v>991664122</v>
       </c>
-      <c r="C699" s="8">
+      <c r="C699" s="4">
         <v>1804</v>
       </c>
-      <c r="D699" s="6" t="str">
+      <c r="D699" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "991664122", "voteDate": "2026-03-20 18:04"},</v>
       </c>
@@ -10920,13 +10920,13 @@
       <c r="A700" s="4">
         <v>699</v>
       </c>
-      <c r="B700" s="7">
+      <c r="B700" s="2">
         <v>946669850</v>
       </c>
-      <c r="C700" s="8">
+      <c r="C700" s="4">
         <v>1732</v>
       </c>
-      <c r="D700" s="6" t="str">
+      <c r="D700" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "946669850", "voteDate": "2026-03-20 17:32"},</v>
       </c>
@@ -10935,13 +10935,13 @@
       <c r="A701" s="4">
         <v>700</v>
       </c>
-      <c r="B701" s="7">
+      <c r="B701" s="2">
         <v>998852730</v>
       </c>
-      <c r="C701" s="8">
+      <c r="C701" s="4">
         <v>1737</v>
       </c>
-      <c r="D701" s="6" t="str">
+      <c r="D701" t="str">
         <f t="shared" si="10"/>
         <v>{"phoneNumber": "998852730", "voteDate": "2026-03-20 17:37"},</v>
       </c>
@@ -10950,801 +10950,1617 @@
       <c r="A702" s="4">
         <v>701</v>
       </c>
-      <c r="B702" s="2"/>
-      <c r="C702" s="4"/>
+      <c r="B702" s="7">
+        <v>998852730</v>
+      </c>
+      <c r="C702" s="8">
+        <v>1737</v>
+      </c>
+      <c r="D702" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "998852730", "voteDate": "2026-03-20 17:37"},</v>
+      </c>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A703" s="4">
         <v>702</v>
       </c>
-      <c r="B703" s="2"/>
-      <c r="C703" s="4"/>
+      <c r="B703" s="7">
+        <v>904489494</v>
+      </c>
+      <c r="C703" s="8">
+        <v>1746</v>
+      </c>
+      <c r="D703" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "904489494", "voteDate": "2026-03-20 17:46"},</v>
+      </c>
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A704" s="4">
         <v>703</v>
       </c>
-      <c r="B704" s="2"/>
-      <c r="C704" s="4"/>
-    </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B704" s="7">
+        <v>997191302</v>
+      </c>
+      <c r="C704" s="8">
+        <v>1740</v>
+      </c>
+      <c r="D704" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "997191302", "voteDate": "2026-03-20 17:40"},</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A705" s="4">
         <v>704</v>
       </c>
-      <c r="B705" s="2"/>
-      <c r="C705" s="4"/>
-    </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B705" s="7">
+        <v>918928148</v>
+      </c>
+      <c r="C705" s="8">
+        <v>1743</v>
+      </c>
+      <c r="D705" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "918928148", "voteDate": "2026-03-20 17:43"},</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A706" s="4">
         <v>705</v>
       </c>
-      <c r="B706" s="2"/>
-      <c r="C706" s="4"/>
-    </row>
-    <row r="707" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B706" s="7">
+        <v>991054716</v>
+      </c>
+      <c r="C706" s="8">
+        <v>1802</v>
+      </c>
+      <c r="D706" s="6" t="str">
+        <f t="shared" si="10"/>
+        <v>{"phoneNumber": "991054716", "voteDate": "2026-03-20 18:02"},</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A707" s="4">
         <v>706</v>
       </c>
-      <c r="B707" s="2"/>
-      <c r="C707" s="4"/>
-    </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B707" s="7">
+        <v>507135646</v>
+      </c>
+      <c r="C707" s="8">
+        <v>1746</v>
+      </c>
+      <c r="D707" s="6" t="str">
+        <f t="shared" ref="D707:D770" si="11">"{""phoneNumber"": """&amp;B707&amp;""", ""voteDate"": """&amp;TEXT(DATE(2026,3,20),"yyyy-mm-dd")&amp;" "&amp;TEXT(C707,"00\:00")&amp;"""},"</f>
+        <v>{"phoneNumber": "507135646", "voteDate": "2026-03-20 17:46"},</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A708" s="4">
         <v>707</v>
       </c>
-      <c r="B708" s="2"/>
-      <c r="C708" s="4"/>
-    </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B708" s="7">
+        <v>507135646</v>
+      </c>
+      <c r="C708" s="8">
+        <v>1746</v>
+      </c>
+      <c r="D708" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "507135646", "voteDate": "2026-03-20 17:46"},</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A709" s="4">
         <v>708</v>
       </c>
-      <c r="B709" s="2"/>
-      <c r="C709" s="4"/>
-    </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B709" s="7">
+        <v>945624692</v>
+      </c>
+      <c r="C709" s="8">
+        <v>1745</v>
+      </c>
+      <c r="D709" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "945624692", "voteDate": "2026-03-20 17:45"},</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A710" s="4">
         <v>709</v>
       </c>
-      <c r="B710" s="2"/>
-      <c r="C710" s="4"/>
-    </row>
-    <row r="711" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B710" s="7">
+        <v>773003126</v>
+      </c>
+      <c r="C710" s="8">
+        <v>1756</v>
+      </c>
+      <c r="D710" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "773003126", "voteDate": "2026-03-20 17:56"},</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A711" s="4">
         <v>710</v>
       </c>
-      <c r="B711" s="2"/>
-      <c r="C711" s="4"/>
-    </row>
-    <row r="712" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B711" s="7">
+        <v>912062458</v>
+      </c>
+      <c r="C711" s="8">
+        <v>1800</v>
+      </c>
+      <c r="D711" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "912062458", "voteDate": "2026-03-20 18:00"},</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A712" s="4">
         <v>711</v>
       </c>
-      <c r="B712" s="2"/>
-      <c r="C712" s="4"/>
-    </row>
-    <row r="713" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B712" s="7">
+        <v>930038377</v>
+      </c>
+      <c r="C712" s="8">
+        <v>1756</v>
+      </c>
+      <c r="D712" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "930038377", "voteDate": "2026-03-20 17:56"},</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A713" s="4">
         <v>712</v>
       </c>
-      <c r="B713" s="2"/>
-      <c r="C713" s="4"/>
-    </row>
-    <row r="714" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B713" s="7">
+        <v>882969998</v>
+      </c>
+      <c r="C713" s="8">
+        <v>1758</v>
+      </c>
+      <c r="D713" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "882969998", "voteDate": "2026-03-20 17:58"},</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A714" s="4">
         <v>713</v>
       </c>
-      <c r="B714" s="2"/>
-      <c r="C714" s="4"/>
-    </row>
-    <row r="715" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B714" s="7">
+        <v>944420168</v>
+      </c>
+      <c r="C714" s="8">
+        <v>1815</v>
+      </c>
+      <c r="D714" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "944420168", "voteDate": "2026-03-20 18:15"},</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A715" s="4">
         <v>714</v>
       </c>
-      <c r="B715" s="2"/>
-      <c r="C715" s="4"/>
-    </row>
-    <row r="716" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B715" s="7">
+        <v>995707664</v>
+      </c>
+      <c r="C715" s="8">
+        <v>1806</v>
+      </c>
+      <c r="D715" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "995707664", "voteDate": "2026-03-20 18:06"},</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A716" s="4">
         <v>715</v>
       </c>
-      <c r="B716" s="2"/>
-      <c r="C716" s="4"/>
-    </row>
-    <row r="717" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B716" s="7">
+        <v>507138795</v>
+      </c>
+      <c r="C716" s="8">
+        <v>1807</v>
+      </c>
+      <c r="D716" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "507138795", "voteDate": "2026-03-20 18:07"},</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A717" s="4">
         <v>716</v>
       </c>
-      <c r="B717" s="2"/>
-      <c r="C717" s="4"/>
-    </row>
-    <row r="718" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B717" s="7">
+        <v>900178684</v>
+      </c>
+      <c r="C717" s="8">
+        <v>1801</v>
+      </c>
+      <c r="D717" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "900178684", "voteDate": "2026-03-20 18:01"},</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A718" s="4">
         <v>717</v>
       </c>
-      <c r="B718" s="2"/>
-      <c r="C718" s="4"/>
-    </row>
-    <row r="719" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B718" s="7">
+        <v>900160390</v>
+      </c>
+      <c r="C718" s="8">
+        <v>1803</v>
+      </c>
+      <c r="D718" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "900160390", "voteDate": "2026-03-20 18:03"},</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A719" s="4">
         <v>718</v>
       </c>
-      <c r="B719" s="2"/>
-      <c r="C719" s="4"/>
-    </row>
-    <row r="720" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B719" s="7">
+        <v>902302705</v>
+      </c>
+      <c r="C719" s="8">
+        <v>1812</v>
+      </c>
+      <c r="D719" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "902302705", "voteDate": "2026-03-20 18:12"},</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A720" s="4">
         <v>719</v>
       </c>
-      <c r="B720" s="2"/>
-      <c r="C720" s="4"/>
-    </row>
-    <row r="721" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B720" s="7">
+        <v>900160390</v>
+      </c>
+      <c r="C720" s="8">
+        <v>1803</v>
+      </c>
+      <c r="D720" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "900160390", "voteDate": "2026-03-20 18:03"},</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A721" s="4">
         <v>720</v>
       </c>
-      <c r="B721" s="2"/>
-      <c r="C721" s="4"/>
-    </row>
-    <row r="722" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B721" s="7">
+        <v>939749748</v>
+      </c>
+      <c r="C721" s="8">
+        <v>1802</v>
+      </c>
+      <c r="D721" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "939749748", "voteDate": "2026-03-20 18:02"},</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A722" s="4">
         <v>721</v>
       </c>
-      <c r="B722" s="2"/>
-      <c r="C722" s="4"/>
-    </row>
-    <row r="723" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B722" s="7">
+        <v>954837787</v>
+      </c>
+      <c r="C722" s="8">
+        <v>1818</v>
+      </c>
+      <c r="D722" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "954837787", "voteDate": "2026-03-20 18:18"},</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A723" s="4">
         <v>722</v>
       </c>
-      <c r="B723" s="2"/>
-      <c r="C723" s="4"/>
-    </row>
-    <row r="724" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B723" s="7">
+        <v>994947493</v>
+      </c>
+      <c r="C723" s="8">
+        <v>1758</v>
+      </c>
+      <c r="D723" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "994947493", "voteDate": "2026-03-20 17:58"},</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A724" s="4">
         <v>723</v>
       </c>
-      <c r="B724" s="2"/>
-      <c r="C724" s="4"/>
-    </row>
-    <row r="725" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B724" s="7">
+        <v>935659865</v>
+      </c>
+      <c r="C724" s="8">
+        <v>1757</v>
+      </c>
+      <c r="D724" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "935659865", "voteDate": "2026-03-20 17:57"},</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A725" s="4">
         <v>724</v>
       </c>
-      <c r="B725" s="2"/>
-      <c r="C725" s="4"/>
-    </row>
-    <row r="726" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B725" s="7">
+        <v>935089897</v>
+      </c>
+      <c r="C725" s="8">
+        <v>1811</v>
+      </c>
+      <c r="D725" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "935089897", "voteDate": "2026-03-20 18:11"},</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A726" s="4">
         <v>725</v>
       </c>
-      <c r="B726" s="2"/>
-      <c r="C726" s="4"/>
-    </row>
-    <row r="727" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B726" s="7">
+        <v>990982423</v>
+      </c>
+      <c r="C726" s="8">
+        <v>1820</v>
+      </c>
+      <c r="D726" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "990982423", "voteDate": "2026-03-20 18:20"},</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A727" s="4">
         <v>726</v>
       </c>
-      <c r="B727" s="2"/>
-      <c r="C727" s="4"/>
-    </row>
-    <row r="728" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B727" s="7">
+        <v>949716888</v>
+      </c>
+      <c r="C727" s="8">
+        <v>1821</v>
+      </c>
+      <c r="D727" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "949716888", "voteDate": "2026-03-20 18:21"},</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A728" s="4">
         <v>727</v>
       </c>
-      <c r="B728" s="2"/>
-      <c r="C728" s="4"/>
-    </row>
-    <row r="729" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B728" s="7">
+        <v>997285790</v>
+      </c>
+      <c r="C728" s="8">
+        <v>1809</v>
+      </c>
+      <c r="D728" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "997285790", "voteDate": "2026-03-20 18:09"},</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A729" s="4">
         <v>728</v>
       </c>
-      <c r="B729" s="2"/>
-      <c r="C729" s="4"/>
-    </row>
-    <row r="730" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B729" s="7">
+        <v>939098686</v>
+      </c>
+      <c r="C729" s="8">
+        <v>1448</v>
+      </c>
+      <c r="D729" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "939098686", "voteDate": "2026-03-20 14:48"},</v>
+      </c>
+    </row>
+    <row r="730" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A730" s="4">
         <v>729</v>
       </c>
-      <c r="B730" s="2"/>
-      <c r="C730" s="4"/>
-    </row>
-    <row r="731" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B730" s="7">
+        <v>940358305</v>
+      </c>
+      <c r="C730" s="8">
+        <v>1822</v>
+      </c>
+      <c r="D730" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "940358305", "voteDate": "2026-03-20 18:22"},</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A731" s="4">
         <v>730</v>
       </c>
-      <c r="B731" s="2"/>
-      <c r="C731" s="4"/>
-    </row>
-    <row r="732" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B731" s="7">
+        <v>944263738</v>
+      </c>
+      <c r="C731" s="8">
+        <v>1824</v>
+      </c>
+      <c r="D731" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "944263738", "voteDate": "2026-03-20 18:24"},</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A732" s="4">
         <v>731</v>
       </c>
-      <c r="B732" s="2"/>
-      <c r="C732" s="4"/>
-    </row>
-    <row r="733" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B732" s="7">
+        <v>335303202</v>
+      </c>
+      <c r="C732" s="8">
+        <v>1822</v>
+      </c>
+      <c r="D732" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "335303202", "voteDate": "2026-03-20 18:22"},</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A733" s="4">
         <v>732</v>
       </c>
-      <c r="B733" s="2"/>
-      <c r="C733" s="4"/>
-    </row>
-    <row r="734" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B733" s="7">
+        <v>911089218</v>
+      </c>
+      <c r="C733" s="8">
+        <v>1827</v>
+      </c>
+      <c r="D733" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "911089218", "voteDate": "2026-03-20 18:27"},</v>
+      </c>
+    </row>
+    <row r="734" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A734" s="4">
         <v>733</v>
       </c>
-      <c r="B734" s="2"/>
-      <c r="C734" s="4"/>
-    </row>
-    <row r="735" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B734" s="7">
+        <v>956060092</v>
+      </c>
+      <c r="C734" s="8">
+        <v>1826</v>
+      </c>
+      <c r="D734" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "956060092", "voteDate": "2026-03-20 18:26"},</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A735" s="4">
         <v>734</v>
       </c>
-      <c r="B735" s="2"/>
-      <c r="C735" s="4"/>
-    </row>
-    <row r="736" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B735" s="7">
+        <v>992087792</v>
+      </c>
+      <c r="C735" s="8">
+        <v>1827</v>
+      </c>
+      <c r="D735" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "992087792", "voteDate": "2026-03-20 18:27"},</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A736" s="4">
         <v>735</v>
       </c>
-      <c r="B736" s="2"/>
-      <c r="C736" s="4"/>
-    </row>
-    <row r="737" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B736" s="7">
+        <v>945145121</v>
+      </c>
+      <c r="C736" s="8">
+        <v>1825</v>
+      </c>
+      <c r="D736" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "945145121", "voteDate": "2026-03-20 18:25"},</v>
+      </c>
+    </row>
+    <row r="737" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A737" s="4">
         <v>736</v>
       </c>
-      <c r="B737" s="2"/>
-      <c r="C737" s="4"/>
-    </row>
-    <row r="738" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B737" s="7">
+        <v>938600333</v>
+      </c>
+      <c r="C737" s="8">
+        <v>1826</v>
+      </c>
+      <c r="D737" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "938600333", "voteDate": "2026-03-20 18:26"},</v>
+      </c>
+    </row>
+    <row r="738" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A738" s="4">
         <v>737</v>
       </c>
-      <c r="B738" s="2"/>
-      <c r="C738" s="4"/>
-    </row>
-    <row r="739" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B738" s="7">
+        <v>937921802</v>
+      </c>
+      <c r="C738" s="8">
+        <v>1828</v>
+      </c>
+      <c r="D738" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "937921802", "voteDate": "2026-03-20 18:28"},</v>
+      </c>
+    </row>
+    <row r="739" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A739" s="4">
         <v>738</v>
       </c>
-      <c r="B739" s="2"/>
-      <c r="C739" s="4"/>
-    </row>
-    <row r="740" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B739" s="7">
+        <v>200014241</v>
+      </c>
+      <c r="C739" s="8">
+        <v>1826</v>
+      </c>
+      <c r="D739" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "200014241", "voteDate": "2026-03-20 18:26"},</v>
+      </c>
+    </row>
+    <row r="740" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A740" s="4">
         <v>739</v>
       </c>
-      <c r="B740" s="2"/>
-      <c r="C740" s="4"/>
-    </row>
-    <row r="741" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B740" s="7">
+        <v>972140050</v>
+      </c>
+      <c r="C740" s="8">
+        <v>1827</v>
+      </c>
+      <c r="D740" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "972140050", "voteDate": "2026-03-20 18:27"},</v>
+      </c>
+    </row>
+    <row r="741" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A741" s="4">
         <v>740</v>
       </c>
-      <c r="B741" s="2"/>
-      <c r="C741" s="4"/>
-    </row>
-    <row r="742" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B741" s="7">
+        <v>901631665</v>
+      </c>
+      <c r="C741" s="8">
+        <v>1823</v>
+      </c>
+      <c r="D741" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "901631665", "voteDate": "2026-03-20 18:23"},</v>
+      </c>
+    </row>
+    <row r="742" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A742" s="4">
         <v>741</v>
       </c>
-      <c r="B742" s="2"/>
-      <c r="C742" s="4"/>
-    </row>
-    <row r="743" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B742" s="7">
+        <v>501089218</v>
+      </c>
+      <c r="C742" s="8">
+        <v>1830</v>
+      </c>
+      <c r="D742" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "501089218", "voteDate": "2026-03-20 18:30"},</v>
+      </c>
+    </row>
+    <row r="743" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A743" s="4">
         <v>742</v>
       </c>
-      <c r="B743" s="2"/>
-      <c r="C743" s="4"/>
-    </row>
-    <row r="744" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B743" s="7">
+        <v>906332551</v>
+      </c>
+      <c r="C743" s="8">
+        <v>1821</v>
+      </c>
+      <c r="D743" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "906332551", "voteDate": "2026-03-20 18:21"},</v>
+      </c>
+    </row>
+    <row r="744" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A744" s="4">
         <v>743</v>
       </c>
-      <c r="B744" s="2"/>
-      <c r="C744" s="4"/>
-    </row>
-    <row r="745" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B744" s="7">
+        <v>954837787</v>
+      </c>
+      <c r="C744" s="8">
+        <v>1818</v>
+      </c>
+      <c r="D744" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "954837787", "voteDate": "2026-03-20 18:18"},</v>
+      </c>
+    </row>
+    <row r="745" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A745" s="4">
         <v>744</v>
       </c>
-      <c r="B745" s="2"/>
-      <c r="C745" s="4"/>
-    </row>
-    <row r="746" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B745" s="7">
+        <v>940016755</v>
+      </c>
+      <c r="C745" s="8">
+        <v>1833</v>
+      </c>
+      <c r="D745" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "940016755", "voteDate": "2026-03-20 18:33"},</v>
+      </c>
+    </row>
+    <row r="746" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A746" s="4">
         <v>745</v>
       </c>
-      <c r="B746" s="2"/>
-      <c r="C746" s="4"/>
-    </row>
-    <row r="747" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B746" s="7">
+        <v>992237099</v>
+      </c>
+      <c r="C746" s="8">
+        <v>1831</v>
+      </c>
+      <c r="D746" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "992237099", "voteDate": "2026-03-20 18:31"},</v>
+      </c>
+    </row>
+    <row r="747" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A747" s="4">
         <v>746</v>
       </c>
-      <c r="B747" s="2"/>
-      <c r="C747" s="4"/>
-    </row>
-    <row r="748" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B747" s="7">
+        <v>771337099</v>
+      </c>
+      <c r="C747" s="8">
+        <v>1833</v>
+      </c>
+      <c r="D747" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "771337099", "voteDate": "2026-03-20 18:33"},</v>
+      </c>
+    </row>
+    <row r="748" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A748" s="4">
         <v>747</v>
       </c>
-      <c r="B748" s="2"/>
-      <c r="C748" s="4"/>
-    </row>
-    <row r="749" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B748" s="7">
+        <v>934079020</v>
+      </c>
+      <c r="C748" s="8">
+        <v>1833</v>
+      </c>
+      <c r="D748" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "934079020", "voteDate": "2026-03-20 18:33"},</v>
+      </c>
+    </row>
+    <row r="749" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A749" s="4">
         <v>748</v>
       </c>
-      <c r="B749" s="2"/>
-      <c r="C749" s="4"/>
-    </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B749" s="7">
+        <v>931791222</v>
+      </c>
+      <c r="C749" s="8">
+        <v>1830</v>
+      </c>
+      <c r="D749" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "931791222", "voteDate": "2026-03-20 18:30"},</v>
+      </c>
+    </row>
+    <row r="750" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A750" s="4">
         <v>749</v>
       </c>
-      <c r="B750" s="2"/>
-      <c r="C750" s="4"/>
-    </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B750" s="7">
+        <v>931363800</v>
+      </c>
+      <c r="C750" s="8">
+        <v>1837</v>
+      </c>
+      <c r="D750" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "931363800", "voteDate": "2026-03-20 18:37"},</v>
+      </c>
+    </row>
+    <row r="751" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A751" s="4">
         <v>750</v>
       </c>
-      <c r="B751" s="2"/>
-      <c r="C751" s="4"/>
-    </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B751" s="7">
+        <v>912056701</v>
+      </c>
+      <c r="C751" s="8">
+        <v>1830</v>
+      </c>
+      <c r="D751" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "912056701", "voteDate": "2026-03-20 18:30"},</v>
+      </c>
+    </row>
+    <row r="752" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A752" s="4">
         <v>751</v>
       </c>
-      <c r="B752" s="2"/>
-      <c r="C752" s="4"/>
-    </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B752" s="7">
+        <v>915864902</v>
+      </c>
+      <c r="C752" s="8">
+        <v>1840</v>
+      </c>
+      <c r="D752" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "915864902", "voteDate": "2026-03-20 18:40"},</v>
+      </c>
+    </row>
+    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A753" s="4">
         <v>752</v>
       </c>
-      <c r="B753" s="2"/>
-      <c r="C753" s="4"/>
-    </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B753" s="7">
+        <v>944947854</v>
+      </c>
+      <c r="C753" s="8">
+        <v>1805</v>
+      </c>
+      <c r="D753" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "944947854", "voteDate": "2026-03-20 18:05"},</v>
+      </c>
+    </row>
+    <row r="754" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A754" s="4">
         <v>753</v>
       </c>
-      <c r="B754" s="2"/>
-      <c r="C754" s="4"/>
-    </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B754" s="7">
+        <v>933064601</v>
+      </c>
+      <c r="C754" s="8">
+        <v>1846</v>
+      </c>
+      <c r="D754" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "933064601", "voteDate": "2026-03-20 18:46"},</v>
+      </c>
+    </row>
+    <row r="755" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A755" s="4">
         <v>754</v>
       </c>
-      <c r="B755" s="2"/>
-      <c r="C755" s="4"/>
-    </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B755" s="7">
+        <v>911399037</v>
+      </c>
+      <c r="C755" s="8">
+        <v>1818</v>
+      </c>
+      <c r="D755" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "911399037", "voteDate": "2026-03-20 18:18"},</v>
+      </c>
+    </row>
+    <row r="756" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A756" s="4">
         <v>755</v>
       </c>
-      <c r="B756" s="2"/>
-      <c r="C756" s="4"/>
-    </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B756" s="7">
+        <v>993984773</v>
+      </c>
+      <c r="C756" s="8">
+        <v>1823</v>
+      </c>
+      <c r="D756" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "993984773", "voteDate": "2026-03-20 18:23"},</v>
+      </c>
+    </row>
+    <row r="757" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A757" s="4">
         <v>756</v>
       </c>
-      <c r="B757" s="2"/>
-      <c r="C757" s="4"/>
-    </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B757" s="7">
+        <v>957922003</v>
+      </c>
+      <c r="C757" s="8">
+        <v>1820</v>
+      </c>
+      <c r="D757" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "957922003", "voteDate": "2026-03-20 18:20"},</v>
+      </c>
+    </row>
+    <row r="758" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A758" s="4">
         <v>757</v>
       </c>
-      <c r="B758" s="2"/>
-      <c r="C758" s="4"/>
-    </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B758" s="7">
+        <v>909921675</v>
+      </c>
+      <c r="C758" s="8">
+        <v>1830</v>
+      </c>
+      <c r="D758" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "909921675", "voteDate": "2026-03-20 18:30"},</v>
+      </c>
+    </row>
+    <row r="759" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A759" s="4">
         <v>758</v>
       </c>
-      <c r="B759" s="2"/>
-      <c r="C759" s="4"/>
-    </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B759" s="7">
+        <v>950703797</v>
+      </c>
+      <c r="C759" s="8">
+        <v>1825</v>
+      </c>
+      <c r="D759" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "950703797", "voteDate": "2026-03-20 18:25"},</v>
+      </c>
+    </row>
+    <row r="760" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A760" s="4">
         <v>759</v>
       </c>
-      <c r="B760" s="2"/>
-      <c r="C760" s="4"/>
-    </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B760" s="7">
+        <v>777829898</v>
+      </c>
+      <c r="C760" s="8">
+        <v>1834</v>
+      </c>
+      <c r="D760" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "777829898", "voteDate": "2026-03-20 18:34"},</v>
+      </c>
+    </row>
+    <row r="761" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A761" s="4">
         <v>760</v>
       </c>
-      <c r="B761" s="2"/>
-      <c r="C761" s="4"/>
-    </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B761" s="7">
+        <v>991387171</v>
+      </c>
+      <c r="C761" s="8">
+        <v>1832</v>
+      </c>
+      <c r="D761" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "991387171", "voteDate": "2026-03-20 18:32"},</v>
+      </c>
+    </row>
+    <row r="762" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A762" s="4">
         <v>761</v>
       </c>
-      <c r="B762" s="2"/>
-      <c r="C762" s="4"/>
-    </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B762" s="7">
+        <v>940211272</v>
+      </c>
+      <c r="C762" s="8">
+        <v>1840</v>
+      </c>
+      <c r="D762" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "940211272", "voteDate": "2026-03-20 18:40"},</v>
+      </c>
+    </row>
+    <row r="763" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A763" s="4">
         <v>762</v>
       </c>
-      <c r="B763" s="2"/>
-      <c r="C763" s="4"/>
-    </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B763" s="7">
+        <v>940902800</v>
+      </c>
+      <c r="C763" s="8">
+        <v>1844</v>
+      </c>
+      <c r="D763" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "940902800", "voteDate": "2026-03-20 18:44"},</v>
+      </c>
+    </row>
+    <row r="764" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A764" s="4">
         <v>763</v>
       </c>
-      <c r="B764" s="2"/>
-      <c r="C764" s="4"/>
-    </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B764" s="7">
+        <v>906279086</v>
+      </c>
+      <c r="C764" s="8">
+        <v>1843</v>
+      </c>
+      <c r="D764" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "906279086", "voteDate": "2026-03-20 18:43"},</v>
+      </c>
+    </row>
+    <row r="765" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A765" s="4">
         <v>764</v>
       </c>
-      <c r="B765" s="2"/>
-      <c r="C765" s="4"/>
-    </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B765" s="7">
+        <v>937107656</v>
+      </c>
+      <c r="C765" s="8">
+        <v>1838</v>
+      </c>
+      <c r="D765" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "937107656", "voteDate": "2026-03-20 18:38"},</v>
+      </c>
+    </row>
+    <row r="766" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A766" s="4">
         <v>765</v>
       </c>
-      <c r="B766" s="2"/>
-      <c r="C766" s="4"/>
-    </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B766" s="7">
+        <v>943053012</v>
+      </c>
+      <c r="C766" s="8">
+        <v>1839</v>
+      </c>
+      <c r="D766" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "943053012", "voteDate": "2026-03-20 18:39"},</v>
+      </c>
+    </row>
+    <row r="767" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A767" s="4">
         <v>766</v>
       </c>
-      <c r="B767" s="2"/>
-      <c r="C767" s="4"/>
-    </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B767" s="7">
+        <v>951162407</v>
+      </c>
+      <c r="C767" s="8">
+        <v>1848</v>
+      </c>
+      <c r="D767" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "951162407", "voteDate": "2026-03-20 18:48"},</v>
+      </c>
+    </row>
+    <row r="768" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A768" s="4">
         <v>767</v>
       </c>
-      <c r="B768" s="2"/>
-      <c r="C768" s="4"/>
-    </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B768" s="7">
+        <v>886980222</v>
+      </c>
+      <c r="C768" s="8">
+        <v>1810</v>
+      </c>
+      <c r="D768" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "886980222", "voteDate": "2026-03-20 18:10"},</v>
+      </c>
+    </row>
+    <row r="769" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A769" s="4">
         <v>768</v>
       </c>
-      <c r="B769" s="2"/>
-      <c r="C769" s="4"/>
-    </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B769" s="7">
+        <v>940468624</v>
+      </c>
+      <c r="C769" s="8">
+        <v>1827</v>
+      </c>
+      <c r="D769" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "940468624", "voteDate": "2026-03-20 18:27"},</v>
+      </c>
+    </row>
+    <row r="770" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A770" s="4">
         <v>769</v>
       </c>
-      <c r="B770" s="2"/>
-      <c r="C770" s="4"/>
-    </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B770" s="7">
+        <v>912069655</v>
+      </c>
+      <c r="C770" s="8">
+        <v>1819</v>
+      </c>
+      <c r="D770" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v>{"phoneNumber": "912069655", "voteDate": "2026-03-20 18:19"},</v>
+      </c>
+    </row>
+    <row r="771" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A771" s="4">
         <v>770</v>
       </c>
-      <c r="B771" s="2"/>
-      <c r="C771" s="4"/>
-    </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B771" s="7">
+        <v>905347655</v>
+      </c>
+      <c r="C771" s="8">
+        <v>1820</v>
+      </c>
+      <c r="D771" s="6" t="str">
+        <f t="shared" ref="D771:D803" si="12">"{""phoneNumber"": """&amp;B771&amp;""", ""voteDate"": """&amp;TEXT(DATE(2026,3,20),"yyyy-mm-dd")&amp;" "&amp;TEXT(C771,"00\:00")&amp;"""},"</f>
+        <v>{"phoneNumber": "905347655", "voteDate": "2026-03-20 18:20"},</v>
+      </c>
+    </row>
+    <row r="772" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A772" s="4">
         <v>771</v>
       </c>
-      <c r="B772" s="2"/>
-      <c r="C772" s="4"/>
-    </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B772" s="7">
+        <v>505027225</v>
+      </c>
+      <c r="C772" s="8">
+        <v>1815</v>
+      </c>
+      <c r="D772" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "505027225", "voteDate": "2026-03-20 18:15"},</v>
+      </c>
+    </row>
+    <row r="773" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A773" s="4">
         <v>772</v>
       </c>
-      <c r="B773" s="2"/>
-      <c r="C773" s="4"/>
-    </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B773" s="7">
+        <v>978960988</v>
+      </c>
+      <c r="C773" s="8">
+        <v>1849</v>
+      </c>
+      <c r="D773" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "978960988", "voteDate": "2026-03-20 18:49"},</v>
+      </c>
+    </row>
+    <row r="774" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A774" s="4">
         <v>773</v>
       </c>
-      <c r="B774" s="2"/>
-      <c r="C774" s="4"/>
-    </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B774" s="7">
+        <v>887972259</v>
+      </c>
+      <c r="C774" s="8">
+        <v>1842</v>
+      </c>
+      <c r="D774" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "887972259", "voteDate": "2026-03-20 18:42"},</v>
+      </c>
+    </row>
+    <row r="775" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A775" s="4">
         <v>774</v>
       </c>
-      <c r="B775" s="2"/>
-      <c r="C775" s="4"/>
-    </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B775" s="7">
+        <v>884288844</v>
+      </c>
+      <c r="C775" s="8">
+        <v>1844</v>
+      </c>
+      <c r="D775" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "884288844", "voteDate": "2026-03-20 18:44"},</v>
+      </c>
+    </row>
+    <row r="776" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A776" s="4">
         <v>775</v>
       </c>
-      <c r="B776" s="2"/>
-      <c r="C776" s="4"/>
-    </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B776" s="7">
+        <v>977972259</v>
+      </c>
+      <c r="C776" s="8">
+        <v>1842</v>
+      </c>
+      <c r="D776" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "977972259", "voteDate": "2026-03-20 18:42"},</v>
+      </c>
+    </row>
+    <row r="777" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A777" s="4">
         <v>776</v>
       </c>
-      <c r="B777" s="2"/>
-      <c r="C777" s="4"/>
-    </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B777" s="7">
+        <v>942298078</v>
+      </c>
+      <c r="C777" s="8">
+        <v>1844</v>
+      </c>
+      <c r="D777" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "942298078", "voteDate": "2026-03-20 18:44"},</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A778" s="4">
         <v>777</v>
       </c>
-      <c r="B778" s="2"/>
-      <c r="C778" s="4"/>
-    </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B778" s="7">
+        <v>941411505</v>
+      </c>
+      <c r="C778" s="8">
+        <v>1847</v>
+      </c>
+      <c r="D778" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "941411505", "voteDate": "2026-03-20 18:47"},</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A779" s="4">
         <v>778</v>
       </c>
-      <c r="B779" s="2"/>
-      <c r="C779" s="4"/>
-    </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B779" s="7">
+        <v>945296100</v>
+      </c>
+      <c r="C779" s="8">
+        <v>1849</v>
+      </c>
+      <c r="D779" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "945296100", "voteDate": "2026-03-20 18:49"},</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A780" s="4">
         <v>779</v>
       </c>
-      <c r="B780" s="2"/>
-      <c r="C780" s="4"/>
-    </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B780" s="7">
+        <v>881021118</v>
+      </c>
+      <c r="C780" s="8">
+        <v>1854</v>
+      </c>
+      <c r="D780" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "881021118", "voteDate": "2026-03-20 18:54"},</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A781" s="4">
         <v>780</v>
       </c>
-      <c r="B781" s="2"/>
-      <c r="C781" s="4"/>
-    </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B781" s="7">
+        <v>937921802</v>
+      </c>
+      <c r="C781" s="8">
+        <v>1828</v>
+      </c>
+      <c r="D781" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "937921802", "voteDate": "2026-03-20 18:28"},</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A782" s="4">
         <v>781</v>
       </c>
-      <c r="B782" s="2"/>
-      <c r="C782" s="4"/>
-    </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B782" s="7">
+        <v>887048181</v>
+      </c>
+      <c r="C782" s="8">
+        <v>1858</v>
+      </c>
+      <c r="D782" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "887048181", "voteDate": "2026-03-20 18:58"},</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A783" s="4">
         <v>782</v>
       </c>
-      <c r="B783" s="2"/>
-      <c r="C783" s="4"/>
-    </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B783" s="7">
+        <v>948490858</v>
+      </c>
+      <c r="C783" s="8">
+        <v>1901</v>
+      </c>
+      <c r="D783" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "948490858", "voteDate": "2026-03-20 19:01"},</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A784" s="4">
         <v>783</v>
       </c>
-      <c r="B784" s="2"/>
-      <c r="C784" s="4"/>
-    </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B784" s="7">
+        <v>701050246</v>
+      </c>
+      <c r="C784" s="8">
+        <v>1857</v>
+      </c>
+      <c r="D784" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "701050246", "voteDate": "2026-03-20 18:57"},</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A785" s="4">
         <v>784</v>
       </c>
-      <c r="B785" s="2"/>
-      <c r="C785" s="4"/>
-    </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B785" s="7">
+        <v>939662891</v>
+      </c>
+      <c r="C785" s="8">
+        <v>1949</v>
+      </c>
+      <c r="D785" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "939662891", "voteDate": "2026-03-20 19:49"},</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A786" s="4">
         <v>785</v>
       </c>
-      <c r="B786" s="2"/>
-      <c r="C786" s="4"/>
-    </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B786" s="7">
+        <v>887048118</v>
+      </c>
+      <c r="C786" s="8">
+        <v>1902</v>
+      </c>
+      <c r="D786" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "887048118", "voteDate": "2026-03-20 19:02"},</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A787" s="4">
         <v>786</v>
       </c>
-      <c r="B787" s="2"/>
-      <c r="C787" s="4"/>
-    </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B787" s="7">
+        <v>904674949</v>
+      </c>
+      <c r="C787" s="8">
+        <v>1849</v>
+      </c>
+      <c r="D787" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "904674949", "voteDate": "2026-03-20 18:49"},</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A788" s="4">
         <v>787</v>
       </c>
-      <c r="B788" s="2"/>
-      <c r="C788" s="4"/>
-    </row>
-    <row r="789" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B788" s="7">
+        <v>992432588</v>
+      </c>
+      <c r="C788" s="8">
+        <v>1852</v>
+      </c>
+      <c r="D788" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "992432588", "voteDate": "2026-03-20 18:52"},</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A789" s="4">
         <v>788</v>
       </c>
-      <c r="B789" s="2"/>
-      <c r="C789" s="4"/>
-    </row>
-    <row r="790" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B789" s="7">
+        <v>951082588</v>
+      </c>
+      <c r="C789" s="8">
+        <v>1853</v>
+      </c>
+      <c r="D789" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "951082588", "voteDate": "2026-03-20 18:53"},</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A790" s="4">
         <v>789</v>
       </c>
-      <c r="B790" s="2"/>
-      <c r="C790" s="4"/>
-    </row>
-    <row r="791" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B790" s="7">
+        <v>943066117</v>
+      </c>
+      <c r="C790" s="8">
+        <v>1903</v>
+      </c>
+      <c r="D790" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "943066117", "voteDate": "2026-03-20 19:03"},</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A791" s="4">
         <v>790</v>
       </c>
-      <c r="B791" s="2"/>
-      <c r="C791" s="4"/>
-    </row>
-    <row r="792" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B791" s="7">
+        <v>934030100</v>
+      </c>
+      <c r="C791" s="8">
+        <v>1903</v>
+      </c>
+      <c r="D791" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "934030100", "voteDate": "2026-03-20 19:03"},</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A792" s="4">
         <v>791</v>
       </c>
-      <c r="B792" s="2"/>
-      <c r="C792" s="4"/>
-    </row>
-    <row r="793" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B792" s="7">
+        <v>916982801</v>
+      </c>
+      <c r="C792" s="8">
+        <v>1858</v>
+      </c>
+      <c r="D792" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "916982801", "voteDate": "2026-03-20 18:58"},</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A793" s="4">
         <v>792</v>
       </c>
-      <c r="B793" s="2"/>
-      <c r="C793" s="4"/>
-    </row>
-    <row r="794" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B793" s="7">
+        <v>934926169</v>
+      </c>
+      <c r="C793" s="8">
+        <v>1902</v>
+      </c>
+      <c r="D793" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "934926169", "voteDate": "2026-03-20 19:02"},</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A794" s="4">
         <v>793</v>
       </c>
-      <c r="B794" s="2"/>
-      <c r="C794" s="4"/>
-    </row>
-    <row r="795" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B794" s="7">
+        <v>908581393</v>
+      </c>
+      <c r="C794" s="8">
+        <v>1859</v>
+      </c>
+      <c r="D794" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "908581393", "voteDate": "2026-03-20 18:59"},</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A795" s="4">
         <v>794</v>
       </c>
-      <c r="B795" s="2"/>
-      <c r="C795" s="4"/>
-    </row>
-    <row r="796" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B795" s="7">
+        <v>930086804</v>
+      </c>
+      <c r="C795" s="8">
+        <v>1902</v>
+      </c>
+      <c r="D795" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "930086804", "voteDate": "2026-03-20 19:02"},</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A796" s="4">
         <v>795</v>
       </c>
-      <c r="B796" s="2"/>
-      <c r="C796" s="4"/>
-    </row>
-    <row r="797" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B796" s="7">
+        <v>880597404</v>
+      </c>
+      <c r="C796" s="8">
+        <v>1858</v>
+      </c>
+      <c r="D796" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "880597404", "voteDate": "2026-03-20 18:58"},</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A797" s="4">
         <v>796</v>
       </c>
-      <c r="B797" s="2"/>
-      <c r="C797" s="4"/>
-    </row>
-    <row r="798" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B797" s="7">
+        <v>939140794</v>
+      </c>
+      <c r="C797" s="8">
+        <v>1901</v>
+      </c>
+      <c r="D797" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "939140794", "voteDate": "2026-03-20 19:01"},</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A798" s="4">
         <v>797</v>
       </c>
-      <c r="B798" s="2"/>
-      <c r="C798" s="4"/>
-    </row>
-    <row r="799" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B798" s="7">
+        <v>972842204</v>
+      </c>
+      <c r="C798" s="8">
+        <v>1854</v>
+      </c>
+      <c r="D798" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "972842204", "voteDate": "2026-03-20 18:54"},</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A799" s="4">
         <v>798</v>
       </c>
-      <c r="B799" s="2"/>
-      <c r="C799" s="4"/>
-    </row>
-    <row r="800" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B799" s="7">
+        <v>885055450</v>
+      </c>
+      <c r="C799" s="8">
+        <v>1903</v>
+      </c>
+      <c r="D799" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "885055450", "voteDate": "2026-03-20 19:03"},</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A800" s="4">
         <v>799</v>
       </c>
-      <c r="B800" s="2"/>
-      <c r="C800" s="4"/>
-    </row>
-    <row r="801" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B800" s="7">
+        <v>936850187</v>
+      </c>
+      <c r="C800" s="8">
+        <v>1906</v>
+      </c>
+      <c r="D800" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "936850187", "voteDate": "2026-03-20 19:06"},</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A801" s="4">
         <v>800</v>
       </c>
-      <c r="B801" s="2"/>
-      <c r="C801" s="4"/>
-    </row>
-    <row r="802" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B801" s="7">
+        <v>887886570</v>
+      </c>
+      <c r="C801" s="8">
+        <v>1908</v>
+      </c>
+      <c r="D801" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "887886570", "voteDate": "2026-03-20 19:08"},</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A802" s="4">
         <v>801</v>
       </c>
-      <c r="B802" s="2"/>
-      <c r="C802" s="4"/>
-    </row>
-    <row r="803" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B802" s="7">
+        <v>940770858</v>
+      </c>
+      <c r="C802" s="8">
+        <v>1910</v>
+      </c>
+      <c r="D802" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "940770858", "voteDate": "2026-03-20 19:10"},</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A803" s="4">
         <v>802</v>
       </c>
-      <c r="B803" s="2"/>
-      <c r="C803" s="4"/>
-    </row>
-    <row r="804" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B803" s="7">
+        <v>900722703</v>
+      </c>
+      <c r="C803" s="8">
+        <v>1911</v>
+      </c>
+      <c r="D803" s="6" t="str">
+        <f t="shared" si="12"/>
+        <v>{"phoneNumber": "900722703", "voteDate": "2026-03-20 19:11"},</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A804" s="4">
         <v>803</v>
       </c>
       <c r="B804" s="2"/>
       <c r="C804" s="4"/>
     </row>
-    <row r="805" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A805" s="4">
         <v>804</v>
       </c>
       <c r="B805" s="2"/>
       <c r="C805" s="4"/>
     </row>
-    <row r="806" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A806" s="4">
         <v>805</v>
       </c>
       <c r="B806" s="2"/>
       <c r="C806" s="4"/>
     </row>
-    <row r="807" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A807" s="4">
         <v>806</v>
       </c>
       <c r="B807" s="2"/>
       <c r="C807" s="4"/>
     </row>
-    <row r="808" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A808" s="4">
         <v>807</v>
       </c>
       <c r="B808" s="2"/>
       <c r="C808" s="4"/>
     </row>
-    <row r="809" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A809" s="4">
         <v>808</v>
       </c>
       <c r="B809" s="2"/>
       <c r="C809" s="4"/>
     </row>
-    <row r="810" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A810" s="4">
         <v>809</v>
       </c>
       <c r="B810" s="2"/>
       <c r="C810" s="4"/>
     </row>
-    <row r="811" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A811" s="4">
         <v>810</v>
       </c>
       <c r="B811" s="2"/>
       <c r="C811" s="4"/>
     </row>
-    <row r="812" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A812" s="4">
         <v>811</v>
       </c>
       <c r="B812" s="2"/>
       <c r="C812" s="4"/>
     </row>
-    <row r="813" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A813" s="4">
         <v>812</v>
       </c>
       <c r="B813" s="2"/>
       <c r="C813" s="4"/>
     </row>
-    <row r="814" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A814" s="4">
         <v>813</v>
       </c>
       <c r="B814" s="2"/>
       <c r="C814" s="4"/>
     </row>
-    <row r="815" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A815" s="4">
         <v>814</v>
       </c>
       <c r="B815" s="2"/>
       <c r="C815" s="4"/>
     </row>
-    <row r="816" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A816" s="4">
         <v>815</v>
       </c>
